--- a/data/credit_bond_all_2026-08-25.xlsx
+++ b/data/credit_bond_all_2026-08-25.xlsx
@@ -2361,8 +2361,12 @@
           <t>1.60 ~ 2.10</t>
         </is>
       </c>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
+      <c r="H10" s="4" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>53.72</v>
+      </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
           <t>1.83</t>
@@ -6327,8 +6331,12 @@
           <t>1.90 ~ 2.90</t>
         </is>
       </c>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
+      <c r="H27" s="4" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="I27" s="4" t="n">
+        <v>127.72</v>
+      </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
           <t>2.36</t>
@@ -15181,8 +15189,12 @@
           <t>1.60 ~ 1.97</t>
         </is>
       </c>
-      <c r="H65" s="3"/>
-      <c r="I65" s="3"/>
+      <c r="H65" s="4" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="I65" s="4" t="n">
+        <v>61.72</v>
+      </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
           <t>1.89</t>

--- a/data/credit_bond_all_2026-08-25.xlsx
+++ b/data/credit_bond_all_2026-08-25.xlsx
@@ -19774,7 +19774,7 @@
     <row r="85" customHeight="true" ht="18.0">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>26招商局港SCP002</t>
+          <t>26广核国际MTN002</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -19784,49 +19784,49 @@
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>012682134.IB</t>
+          <t>102683322.IB</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>0.26Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E85" s="4" t="n">
-        <v>25.0</v>
+        <v>10.0</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>25.0</v>
+        <v>10.0</v>
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.50</t>
+          <t>1.65 ~ 2.05</t>
         </is>
       </c>
       <c r="H85" s="4" t="n">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="I85" s="4" t="n">
-        <v>19.71</v>
+        <v>36.49</v>
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>26招港D1</t>
+          <t>23广核国际MTN001</t>
         </is>
       </c>
       <c r="L85" s="3" t="inlineStr">
         <is>
-          <t>100D</t>
+          <t>2.25Y</t>
         </is>
       </c>
       <c r="M85" s="3" t="inlineStr">
         <is>
-          <t>1.4649</t>
+          <t>1.7218</t>
         </is>
       </c>
       <c r="N85" s="3" t="inlineStr">
@@ -19836,12 +19836,12 @@
       </c>
       <c r="O85" s="3" t="inlineStr">
         <is>
-          <t>招商局港口集团股份有限公司</t>
+          <t>中广核国际有限公司</t>
         </is>
       </c>
       <c r="P85" s="3" t="inlineStr">
         <is>
-          <t>B- 39.64</t>
+          <t>C- 13.33</t>
         </is>
       </c>
       <c r="Q85" s="3" t="inlineStr">
@@ -19851,7 +19851,7 @@
       </c>
       <c r="R85" s="3" t="inlineStr">
         <is>
-          <t>08-24 10:00</t>
+          <t>08-24 09:00</t>
         </is>
       </c>
       <c r="S85" s="3" t="inlineStr">
@@ -19865,17 +19865,19 @@
         </is>
       </c>
       <c r="U85" s="4" t="n">
-        <v>1.668</v>
-      </c>
-      <c r="V85" s="3"/>
+        <v>2.18</v>
+      </c>
+      <c r="V85" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W85" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X85" s="3" t="inlineStr">
         <is>
-          <t>1.44%~1.48%</t>
+          <t>1.79%~1.89%</t>
         </is>
       </c>
       <c r="Y85" s="3" t="inlineStr">
@@ -19886,23 +19888,27 @@
       <c r="Z85" s="3"/>
       <c r="AA85" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>香港特别行政区-新界</t>
         </is>
       </c>
       <c r="AB85" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券计划发行规模为25亿元,拟用于补充发行人本部及下属子公司流动资金以及偿还有息债务。</t>
+          <t>本期中期票据发行金额为人民币10亿元,募集资金将归集至发行人开立的NRA账户。实际募集资金扣除承销费后拟用于偿还发行人境外到期金融机构借款</t>
         </is>
       </c>
       <c r="AC85" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,中信银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD85" s="3"/>
+          <t>中国建设银行股份有限公司,中国工商银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD85" s="3" t="inlineStr">
+        <is>
+          <t>中国广核集团有限公司</t>
+        </is>
+      </c>
       <c r="AE85" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF85" s="3" t="inlineStr">
@@ -19917,7 +19923,7 @@
       </c>
       <c r="AH85" s="3" t="inlineStr">
         <is>
-          <t>招商局港口集团股份有限公司2026年度第二期超短期融资券</t>
+          <t>中广核国际有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI85" s="3" t="inlineStr">
@@ -19927,7 +19933,7 @@
       </c>
       <c r="AJ85" s="3" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2031-08-25</t>
         </is>
       </c>
       <c r="AK85" s="3"/>
@@ -19953,27 +19959,27 @@
       </c>
       <c r="AP85" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ85" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR85" s="3" t="inlineStr">
         <is>
-          <t>港口</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AS85" s="3" t="inlineStr">
         <is>
-          <t>港口</t>
+          <t>其他电力</t>
         </is>
       </c>
       <c r="AT85" s="3" t="inlineStr">
         <is>
-          <t>港口</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU85" s="3" t="inlineStr">
@@ -19983,7 +19989,7 @@
       </c>
       <c r="AV85" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW85" s="3" t="inlineStr">
@@ -20006,7 +20012,7 @@
     <row r="86" customHeight="true" ht="18.0">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>26广核国际MTN002</t>
+          <t>26广核电力MTN005</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -20016,7 +20022,7 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>102683322.IB</t>
+          <t>102683314.IB</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
@@ -20032,33 +20038,33 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>1.65 ~ 2.05</t>
+          <t>1.50 ~ 2.00</t>
         </is>
       </c>
       <c r="H86" s="4" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="I86" s="4" t="n">
-        <v>36.49</v>
+        <v>31.49</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="K86" s="3" t="inlineStr">
         <is>
-          <t>23广核国际MTN001</t>
+          <t>26广核电力MTN002</t>
         </is>
       </c>
       <c r="L86" s="3" t="inlineStr">
         <is>
-          <t>2.25Y</t>
+          <t>2.66Y</t>
         </is>
       </c>
       <c r="M86" s="3" t="inlineStr">
         <is>
-          <t>1.7218</t>
+          <t>1.6458</t>
         </is>
       </c>
       <c r="N86" s="3" t="inlineStr">
@@ -20068,12 +20074,12 @@
       </c>
       <c r="O86" s="3" t="inlineStr">
         <is>
-          <t>中广核国际有限公司</t>
+          <t>中国广核电力股份有限公司</t>
         </is>
       </c>
       <c r="P86" s="3" t="inlineStr">
         <is>
-          <t>C- 13.33</t>
+          <t>C+ 32.57</t>
         </is>
       </c>
       <c r="Q86" s="3" t="inlineStr">
@@ -20104,12 +20110,12 @@
       </c>
       <c r="W86" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X86" s="3" t="inlineStr">
         <is>
-          <t>1.79%~1.89%</t>
+          <t>1.64%~1.74%</t>
         </is>
       </c>
       <c r="Y86" s="3" t="inlineStr">
@@ -20120,24 +20126,20 @@
       <c r="Z86" s="3"/>
       <c r="AA86" s="3" t="inlineStr">
         <is>
-          <t>香港特别行政区-新界</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB86" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额为人民币10亿元,募集资金将归集至发行人开立的NRA账户。实际募集资金扣除承销费后拟用于偿还发行人境外到期金融机构借款</t>
+          <t>发行人本次中期票据发行金额10亿元，所募集资金全部用于偿还发行人子公司贷款本息。</t>
         </is>
       </c>
       <c r="AC86" s="3" t="inlineStr">
         <is>
-          <t>中国建设银行股份有限公司,中国工商银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD86" s="3" t="inlineStr">
-        <is>
-          <t>中国广核集团有限公司</t>
-        </is>
-      </c>
+          <t>中国银行股份有限公司,中国工商银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD86" s="3"/>
       <c r="AE86" s="3" t="inlineStr">
         <is>
           <t>中期票据</t>
@@ -20155,7 +20157,7 @@
       </c>
       <c r="AH86" s="3" t="inlineStr">
         <is>
-          <t>中广核国际有限公司2026年度第二期中期票据</t>
+          <t>中国广核电力股份有限公司2026年度第五期中期票据</t>
         </is>
       </c>
       <c r="AI86" s="3" t="inlineStr">
@@ -20191,7 +20193,7 @@
       </c>
       <c r="AP86" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ86" s="3" t="inlineStr">
@@ -20206,7 +20208,7 @@
       </c>
       <c r="AS86" s="3" t="inlineStr">
         <is>
-          <t>其他电力</t>
+          <t>核电</t>
         </is>
       </c>
       <c r="AT86" s="3" t="inlineStr">
@@ -20221,7 +20223,7 @@
       </c>
       <c r="AV86" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW86" s="3" t="inlineStr">
@@ -20244,7 +20246,7 @@
     <row r="87" customHeight="true" ht="18.0">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>26广核电力MTN005</t>
+          <t>26德阳经开MTN001B</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -20254,7 +20256,7 @@
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>102683314.IB</t>
+          <t>102683296.IB</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
@@ -20263,40 +20265,40 @@
         </is>
       </c>
       <c r="E87" s="4" t="n">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
+          <t>1.80 ~ 2.80</t>
         </is>
       </c>
       <c r="H87" s="4" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="I87" s="4" t="n">
-        <v>31.49</v>
+        <v>66.49</v>
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>26广核电力MTN002</t>
+          <t>25德阳经开MTN001</t>
         </is>
       </c>
       <c r="L87" s="3" t="inlineStr">
         <is>
-          <t>2.66Y</t>
+          <t>3.52Y</t>
         </is>
       </c>
       <c r="M87" s="3" t="inlineStr">
         <is>
-          <t>1.6458</t>
+          <t>2.2598</t>
         </is>
       </c>
       <c r="N87" s="3" t="inlineStr">
@@ -20306,12 +20308,12 @@
       </c>
       <c r="O87" s="3" t="inlineStr">
         <is>
-          <t>中国广核电力股份有限公司</t>
+          <t>德阳经开区发展(控股)集团有限公司</t>
         </is>
       </c>
       <c r="P87" s="3" t="inlineStr">
         <is>
-          <t>C+ 32.57</t>
+          <t>D+ 5.13</t>
         </is>
       </c>
       <c r="Q87" s="3" t="inlineStr">
@@ -20321,7 +20323,7 @@
       </c>
       <c r="R87" s="3" t="inlineStr">
         <is>
-          <t>08-24 09:00</t>
+          <t>08-24 10:00</t>
         </is>
       </c>
       <c r="S87" s="3" t="inlineStr">
@@ -20335,43 +20337,51 @@
         </is>
       </c>
       <c r="U87" s="4" t="n">
-        <v>2.18</v>
+        <v>5.3</v>
       </c>
       <c r="V87" s="4" t="n">
-        <v>1.0</v>
+        <v>1.06</v>
       </c>
       <c r="W87" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8+</t>
         </is>
       </c>
       <c r="X87" s="3" t="inlineStr">
         <is>
-          <t>1.64%~1.74%</t>
+          <t>2.11%~2.21%</t>
         </is>
       </c>
       <c r="Y87" s="3" t="inlineStr">
         <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Z87" s="3" t="inlineStr">
+        <is>
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z87" s="3"/>
       <c r="AA87" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>四川省-德阳市</t>
         </is>
       </c>
       <c r="AB87" s="3" t="inlineStr">
         <is>
-          <t>发行人本次中期票据发行金额10亿元，所募集资金全部用于偿还发行人子公司贷款本息。</t>
+          <t>发行人本期中期票据发行金额为10.00亿元，拟使用募集资金10.00亿元偿还有息债务[21德阳经开MTN001]</t>
         </is>
       </c>
       <c r="AC87" s="3" t="inlineStr">
         <is>
-          <t>中国银行股份有限公司,中国工商银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD87" s="3"/>
+          <t>长江证券股份有限公司,成都银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD87" s="3" t="inlineStr">
+        <is>
+          <t>重庆三峡融资担保集团股份有限公司</t>
+        </is>
+      </c>
       <c r="AE87" s="3" t="inlineStr">
         <is>
           <t>中期票据</t>
@@ -20379,7 +20389,7 @@
       </c>
       <c r="AF87" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG87" s="3" t="inlineStr">
@@ -20389,7 +20399,7 @@
       </c>
       <c r="AH87" s="3" t="inlineStr">
         <is>
-          <t>中国广核电力股份有限公司2026年度第五期中期票据</t>
+          <t>德阳经开区发展(控股)集团有限公司2026年度第一期中期票据(品种二)</t>
         </is>
       </c>
       <c r="AI87" s="3" t="inlineStr">
@@ -20410,7 +20420,7 @@
       </c>
       <c r="AM87" s="3" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="AN87" s="3" t="inlineStr">
@@ -20420,32 +20430,32 @@
       </c>
       <c r="AO87" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP87" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AQ87" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR87" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS87" s="3" t="inlineStr">
         <is>
-          <t>核电</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT87" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU87" s="3" t="inlineStr">
@@ -20455,7 +20465,7 @@
       </c>
       <c r="AV87" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW87" s="3" t="inlineStr">
@@ -20478,7 +20488,7 @@
     <row r="88" customHeight="true" ht="18.0">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>26德阳经开MTN001B</t>
+          <t>26中建八局SCP018</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -20488,49 +20498,49 @@
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>102683296.IB</t>
+          <t>012682137.IB</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.14Y</t>
         </is>
       </c>
       <c r="E88" s="4" t="n">
-        <v>6.0</v>
+        <v>30.0</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>6.0</v>
+        <v>30.0</v>
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.80</t>
+          <t>1.30 ~ 1.46</t>
         </is>
       </c>
       <c r="H88" s="4" t="n">
-        <v>2.05</v>
+        <v>1.46</v>
       </c>
       <c r="I88" s="4" t="n">
-        <v>66.49</v>
+        <v>29.33</v>
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="K88" s="3" t="inlineStr">
         <is>
-          <t>25德阳经开MTN001</t>
+          <t>26中建八局SCP017</t>
         </is>
       </c>
       <c r="L88" s="3" t="inlineStr">
         <is>
-          <t>3.52Y</t>
+          <t>57D</t>
         </is>
       </c>
       <c r="M88" s="3" t="inlineStr">
         <is>
-          <t>2.2598</t>
+          <t>1.4875</t>
         </is>
       </c>
       <c r="N88" s="3" t="inlineStr">
@@ -20540,12 +20550,12 @@
       </c>
       <c r="O88" s="3" t="inlineStr">
         <is>
-          <t>德阳经开区发展(控股)集团有限公司</t>
+          <t>中国建筑第八工程局有限公司</t>
         </is>
       </c>
       <c r="P88" s="3" t="inlineStr">
         <is>
-          <t>D+ 5.13</t>
+          <t>B- 43.48</t>
         </is>
       </c>
       <c r="Q88" s="3" t="inlineStr">
@@ -20555,7 +20565,7 @@
       </c>
       <c r="R88" s="3" t="inlineStr">
         <is>
-          <t>08-24 10:00</t>
+          <t>08-24 09:00</t>
         </is>
       </c>
       <c r="S88" s="3" t="inlineStr">
@@ -20569,59 +20579,49 @@
         </is>
       </c>
       <c r="U88" s="4" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="V88" s="4" t="n">
-        <v>1.06</v>
-      </c>
+        <v>0.35</v>
+      </c>
+      <c r="V88" s="3"/>
       <c r="W88" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X88" s="3" t="inlineStr">
         <is>
-          <t>2.11%~2.21%</t>
+          <t>1.44%~1.48%</t>
         </is>
       </c>
       <c r="Y88" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="Z88" s="3" t="inlineStr">
-        <is>
           <t>AAA</t>
         </is>
       </c>
+      <c r="Z88" s="3"/>
       <c r="AA88" s="3" t="inlineStr">
         <is>
-          <t>四川省-德阳市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB88" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据发行金额为10.00亿元，拟使用募集资金10.00亿元偿还有息债务[21德阳经开MTN001]</t>
+          <t>发行人本期超短期融资券发行金额为30亿元,全部用于偿还有息负债或补充流动资金。</t>
         </is>
       </c>
       <c r="AC88" s="3" t="inlineStr">
         <is>
-          <t>长江证券股份有限公司,成都银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD88" s="3" t="inlineStr">
-        <is>
-          <t>重庆三峡融资担保集团股份有限公司</t>
-        </is>
-      </c>
+          <t>平安银行股份有限公司,浙商银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD88" s="3"/>
       <c r="AE88" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF88" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG88" s="3" t="inlineStr">
@@ -20631,7 +20631,7 @@
       </c>
       <c r="AH88" s="3" t="inlineStr">
         <is>
-          <t>德阳经开区发展(控股)集团有限公司2026年度第一期中期票据(品种二)</t>
+          <t>中国建筑第八工程局有限公司2026年度第十八期超短期融资券</t>
         </is>
       </c>
       <c r="AI88" s="3" t="inlineStr">
@@ -20641,7 +20641,7 @@
       </c>
       <c r="AJ88" s="3" t="inlineStr">
         <is>
-          <t>2031-08-25</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AK88" s="3"/>
@@ -20652,7 +20652,7 @@
       </c>
       <c r="AM88" s="3" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="AN88" s="3" t="inlineStr">
@@ -20662,32 +20662,32 @@
       </c>
       <c r="AO88" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP88" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AQ88" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>建筑施工</t>
         </is>
       </c>
       <c r="AR88" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>综合建筑施工</t>
         </is>
       </c>
       <c r="AS88" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>综合建筑施工</t>
         </is>
       </c>
       <c r="AT88" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>房屋建设</t>
         </is>
       </c>
       <c r="AU88" s="3" t="inlineStr">
@@ -20697,7 +20697,7 @@
       </c>
       <c r="AV88" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW88" s="3" t="inlineStr">
@@ -20720,7 +20720,7 @@
     <row r="89" customHeight="true" ht="18.0">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>26中建八局SCP018</t>
+          <t>26招商局港SCP002</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -20730,49 +20730,49 @@
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>012682137.IB</t>
+          <t>012682134.IB</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>0.14Y</t>
+          <t>0.26Y</t>
         </is>
       </c>
       <c r="E89" s="4" t="n">
-        <v>30.0</v>
+        <v>25.0</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>30.0</v>
+        <v>25.0</v>
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.46</t>
+          <t>1.30 ~ 1.50</t>
         </is>
       </c>
       <c r="H89" s="4" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="I89" s="4" t="n">
-        <v>29.33</v>
+        <v>19.71</v>
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>26中建八局SCP017</t>
+          <t>26招港D1</t>
         </is>
       </c>
       <c r="L89" s="3" t="inlineStr">
         <is>
-          <t>57D</t>
+          <t>100D</t>
         </is>
       </c>
       <c r="M89" s="3" t="inlineStr">
         <is>
-          <t>1.4875</t>
+          <t>1.4649</t>
         </is>
       </c>
       <c r="N89" s="3" t="inlineStr">
@@ -20782,12 +20782,12 @@
       </c>
       <c r="O89" s="3" t="inlineStr">
         <is>
-          <t>中国建筑第八工程局有限公司</t>
+          <t>招商局港口集团股份有限公司</t>
         </is>
       </c>
       <c r="P89" s="3" t="inlineStr">
         <is>
-          <t>B- 43.48</t>
+          <t>B- 39.64</t>
         </is>
       </c>
       <c r="Q89" s="3" t="inlineStr">
@@ -20797,7 +20797,7 @@
       </c>
       <c r="R89" s="3" t="inlineStr">
         <is>
-          <t>08-24 09:00</t>
+          <t>08-24 10:00</t>
         </is>
       </c>
       <c r="S89" s="3" t="inlineStr">
@@ -20811,12 +20811,12 @@
         </is>
       </c>
       <c r="U89" s="4" t="n">
-        <v>0.35</v>
+        <v>1.668</v>
       </c>
       <c r="V89" s="3"/>
       <c r="W89" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X89" s="3" t="inlineStr">
@@ -20832,17 +20832,17 @@
       <c r="Z89" s="3"/>
       <c r="AA89" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB89" s="3" t="inlineStr">
         <is>
-          <t>发行人本期超短期融资券发行金额为30亿元,全部用于偿还有息负债或补充流动资金。</t>
+          <t>本期超短期融资券计划发行规模为25亿元,拟用于补充发行人本部及下属子公司流动资金以及偿还有息债务。</t>
         </is>
       </c>
       <c r="AC89" s="3" t="inlineStr">
         <is>
-          <t>平安银行股份有限公司,浙商银行股份有限公司</t>
+          <t>兴业银行股份有限公司,中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD89" s="3"/>
@@ -20863,7 +20863,7 @@
       </c>
       <c r="AH89" s="3" t="inlineStr">
         <is>
-          <t>中国建筑第八工程局有限公司2026年度第十八期超短期融资券</t>
+          <t>招商局港口集团股份有限公司2026年度第二期超短期融资券</t>
         </is>
       </c>
       <c r="AI89" s="3" t="inlineStr">
@@ -20873,7 +20873,7 @@
       </c>
       <c r="AJ89" s="3" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="AK89" s="3"/>
@@ -20899,27 +20899,27 @@
       </c>
       <c r="AP89" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ89" s="3" t="inlineStr">
         <is>
-          <t>建筑施工</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR89" s="3" t="inlineStr">
         <is>
-          <t>综合建筑施工</t>
+          <t>港口</t>
         </is>
       </c>
       <c r="AS89" s="3" t="inlineStr">
         <is>
-          <t>综合建筑施工</t>
+          <t>港口</t>
         </is>
       </c>
       <c r="AT89" s="3" t="inlineStr">
         <is>
-          <t>房屋建设</t>
+          <t>港口</t>
         </is>
       </c>
       <c r="AU89" s="3" t="inlineStr">

--- a/data/credit_bond_all_2026-08-25.xlsx
+++ b/data/credit_bond_all_2026-08-25.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-08-27" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-08-28" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>C- 19.22</t>
+          <t>C- 20.06</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>B- 43.31</t>
+          <t>B- 44.93</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -1085,7 +1085,7 @@
       <c r="AK4" s="3"/>
       <c r="AL4" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AM4" s="3" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>C- 23.33</t>
+          <t>C- 23.57</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
@@ -1416,7 +1416,7 @@
         <v>20.0</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>20.0</v>
+        <v>0.0</v>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>C 25.92</t>
+          <t>C 28.96</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>B- 40.61</t>
+          <t>B- 40.14</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>A- 61.10</t>
+          <t>B+ 59.04</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>C 26.55</t>
+          <t>C 29.27</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>E 0.00</t>
+          <t>C- 10.29</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>A- 61.10</t>
+          <t>B+ 59.04</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
@@ -3087,7 +3087,7 @@
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>D- 2.50</t>
+          <t>D 5.00</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>C- 19.30</t>
+          <t>C- 18.80</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>B- 42.06</t>
+          <t>B- 43.87</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
@@ -3789,7 +3789,7 @@
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>B- 39.08</t>
+          <t>B- 39.14</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
@@ -4023,7 +4023,7 @@
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>B- 48.78</t>
+          <t>B- 46.05</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
@@ -4261,7 +4261,7 @@
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>C+ 32.53</t>
+          <t>C+ 34.78</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>C- 21.26</t>
+          <t>C- 23.97</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>B- 39.08</t>
+          <t>B- 39.14</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
@@ -4965,7 +4965,7 @@
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>D 5.00</t>
+          <t>C 26.25</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.01</t>
+          <t>B- 36.40</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>C- 21.67</t>
+          <t>B- 40.00</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
@@ -5679,7 +5679,7 @@
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>C 25.92</t>
+          <t>C 28.96</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
@@ -5913,7 +5913,7 @@
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>C- 19.93</t>
+          <t>C- 20.43</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
@@ -6147,7 +6147,7 @@
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t>C- 20.65</t>
+          <t>C- 23.76</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t>B- 42.80</t>
+          <t>B- 39.46</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
@@ -6627,7 +6627,7 @@
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>C- 21.22</t>
+          <t>C- 23.11</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
@@ -6865,7 +6865,7 @@
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>A- 61.10</t>
+          <t>B+ 59.04</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
@@ -7187,7 +7187,7 @@
       <c r="AK30" s="3"/>
       <c r="AL30" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AM30" s="3" t="inlineStr">
@@ -7327,7 +7327,7 @@
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>D- 0.57</t>
+          <t>E 0.00</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
@@ -7419,7 +7419,7 @@
       <c r="AK31" s="3"/>
       <c r="AL31" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AM31" s="3" t="inlineStr">
@@ -7559,7 +7559,7 @@
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>C- 24.60</t>
+          <t>C- 24.73</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
@@ -8711,7 +8711,7 @@
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.6300</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
@@ -8721,7 +8721,7 @@
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>B- 43.21</t>
+          <t>B- 45.60</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
@@ -8945,7 +8945,7 @@
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5900/1.5800</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
@@ -8955,7 +8955,7 @@
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>A 76.15</t>
+          <t>A- 66.57</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
@@ -9179,7 +9179,7 @@
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7800/1.7100</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
@@ -9189,7 +9189,7 @@
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>B- 39.11</t>
+          <t>B- 42.59</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
@@ -9427,7 +9427,7 @@
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t>C 26.67</t>
+          <t>C 29.58</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
@@ -9651,7 +9651,7 @@
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7400/1.6000</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
@@ -9661,7 +9661,7 @@
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t>B- 36.29</t>
+          <t>C+ 34.03</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
@@ -9897,7 +9897,7 @@
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t>C- 13.02</t>
+          <t>C- 20.77</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
@@ -10121,7 +10121,7 @@
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/2.2300</t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
@@ -10131,7 +10131,7 @@
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t>C- 22.00</t>
+          <t>C 29.50</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
@@ -10353,7 +10353,7 @@
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.1000/--</t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t>C- 19.93</t>
+          <t>C- 20.43</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
@@ -10587,7 +10587,7 @@
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.9400/--</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
@@ -10597,7 +10597,7 @@
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t>D+ 8.99</t>
+          <t>C- 12.87</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
@@ -10833,7 +10833,7 @@
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t>B- 42.80</t>
+          <t>B- 39.46</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
@@ -11057,7 +11057,11 @@
           <t>瑞士银行有限公司</t>
         </is>
       </c>
-      <c r="P47" s="3"/>
+      <c r="P47" s="3" t="inlineStr">
+        <is>
+          <t>E 0.00</t>
+        </is>
+      </c>
       <c r="Q47" s="3" t="inlineStr">
         <is>
           <t>2026-08-25</t>
@@ -11259,7 +11263,7 @@
       </c>
       <c r="N48" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8800/1.8600</t>
         </is>
       </c>
       <c r="O48" s="3" t="inlineStr">
@@ -11269,7 +11273,7 @@
       </c>
       <c r="P48" s="3" t="inlineStr">
         <is>
-          <t>C 28.58</t>
+          <t>C 29.25</t>
         </is>
       </c>
       <c r="Q48" s="3" t="inlineStr">
@@ -11503,7 +11507,7 @@
       </c>
       <c r="P49" s="3" t="inlineStr">
         <is>
-          <t>D- 3.00</t>
+          <t>C+ 32.35</t>
         </is>
       </c>
       <c r="Q49" s="3" t="inlineStr">
@@ -11729,7 +11733,7 @@
       </c>
       <c r="N50" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8700/--</t>
         </is>
       </c>
       <c r="O50" s="3" t="inlineStr">
@@ -11739,7 +11743,7 @@
       </c>
       <c r="P50" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.09</t>
+          <t>C- 25.00</t>
         </is>
       </c>
       <c r="Q50" s="3" t="inlineStr">
@@ -11971,7 +11975,7 @@
       </c>
       <c r="P51" s="3" t="inlineStr">
         <is>
-          <t>C- 24.01</t>
+          <t>C 26.06</t>
         </is>
       </c>
       <c r="Q51" s="3" t="inlineStr">
@@ -12136,7 +12140,7 @@
     <row r="52" customHeight="true" ht="18.0">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>26同安05</t>
+          <t>26经金K1</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -12146,49 +12150,49 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>283709.SH</t>
+          <t>520428.SZ</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E52" s="4" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>2.00 ~ 3.00</t>
         </is>
       </c>
       <c r="H52" s="4" t="n">
-        <v>1.67</v>
+        <v>2.35</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>41.67</v>
+        <v>96.28</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>26同安04</t>
+          <t>25经金Z1</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>2.91Y</t>
+          <t>1.68Y+2.00Y</t>
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>1.7484</t>
+          <t>2.0607</t>
         </is>
       </c>
       <c r="N52" s="3" t="inlineStr">
@@ -12198,12 +12202,12 @@
       </c>
       <c r="O52" s="3" t="inlineStr">
         <is>
-          <t>同安控股有限责任公司</t>
+          <t>西安经开金融控股有限公司</t>
         </is>
       </c>
       <c r="P52" s="3" t="inlineStr">
         <is>
-          <t>B 50.51</t>
+          <t>C- 11.94</t>
         </is>
       </c>
       <c r="Q52" s="3" t="inlineStr">
@@ -12213,7 +12217,7 @@
       </c>
       <c r="R52" s="3" t="inlineStr">
         <is>
-          <t>08-25 16:00</t>
+          <t>08-25 15:00</t>
         </is>
       </c>
       <c r="S52" s="3" t="inlineStr">
@@ -12227,13 +12231,17 @@
         </is>
       </c>
       <c r="U52" s="4" t="n">
-        <v>5.25</v>
+        <v>3.1032</v>
       </c>
       <c r="V52" s="3"/>
-      <c r="W52" s="3"/>
+      <c r="W52" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="X52" s="3" t="inlineStr">
         <is>
-          <t>1.78%~1.88%</t>
+          <t>2.74%~2.84%</t>
         </is>
       </c>
       <c r="Y52" s="3" t="inlineStr">
@@ -12244,17 +12252,17 @@
       <c r="Z52" s="3"/>
       <c r="AA52" s="3" t="inlineStr">
         <is>
-          <t>安徽省-安庆市</t>
+          <t>陕西省-西安市</t>
         </is>
       </c>
       <c r="AB52" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还到期公司债券本金或置换偿还公司债券本金的自有资金。[23 同安04]</t>
+          <t>本期债券募集资金拟将3.10亿元用于科技创新类股权投资(含创业投资基金、政府出资产业投资基金等符合国家相关规定的基金出资)</t>
         </is>
       </c>
       <c r="AC52" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,华安证券股份有限公司</t>
+          <t>五矿证券有限公司,中泰证券股份有限公司</t>
         </is>
       </c>
       <c r="AD52" s="3"/>
@@ -12270,12 +12278,12 @@
       </c>
       <c r="AG52" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH52" s="3" t="inlineStr">
         <is>
-          <t>同安控股有限责任公司2026年面向专业投资者非公开发行公司债券(第五期)</t>
+          <t>西安经开金融控股有限公司2026年面向专业投资者非公开发行科技创新公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI52" s="3" t="inlineStr">
@@ -12285,7 +12293,7 @@
       </c>
       <c r="AJ52" s="3" t="inlineStr">
         <is>
-          <t>2029-08-27</t>
+          <t>2031-08-27</t>
         </is>
       </c>
       <c r="AK52" s="3"/>
@@ -12306,32 +12314,32 @@
       </c>
       <c r="AO52" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP52" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ52" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR52" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>金融控股</t>
         </is>
       </c>
       <c r="AS52" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>金融控股</t>
         </is>
       </c>
       <c r="AT52" s="3" t="inlineStr">
         <is>
-          <t>纺织制造</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU52" s="3" t="inlineStr">
@@ -12364,7 +12372,7 @@
     <row r="53" customHeight="true" ht="18.0">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>26金瓯01</t>
+          <t>26豫桥05</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -12374,7 +12382,7 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>524984.SZ</t>
+          <t>283658.SH</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
@@ -12383,55 +12391,55 @@
         </is>
       </c>
       <c r="E53" s="4" t="n">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
+          <t>1.80 ~ 3.50</t>
         </is>
       </c>
       <c r="H53" s="4" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="I53" s="4" t="n">
-        <v>44.67</v>
+        <v>94.67</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>--</t>
         </is>
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>25金瓯Y1</t>
+          <t>26河南路桥MTN001</t>
         </is>
       </c>
       <c r="L53" s="3" t="inlineStr">
         <is>
-          <t>1.64Y+N</t>
+          <t>2.97Y</t>
         </is>
       </c>
       <c r="M53" s="3" t="inlineStr">
         <is>
-          <t>2.0902</t>
+          <t>2.3646</t>
         </is>
       </c>
       <c r="N53" s="3" t="inlineStr">
         <is>
-          <t>2.2000/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O53" s="3" t="inlineStr">
         <is>
-          <t>光大金瓯资产管理有限公司</t>
+          <t>河南省路桥建设集团有限公司</t>
         </is>
       </c>
       <c r="P53" s="3" t="inlineStr">
         <is>
-          <t>C 30.00</t>
+          <t>C- 21.39</t>
         </is>
       </c>
       <c r="Q53" s="3" t="inlineStr">
@@ -12455,41 +12463,41 @@
         </is>
       </c>
       <c r="U53" s="4" t="n">
-        <v>4.61</v>
+        <v>3.45</v>
       </c>
       <c r="V53" s="3"/>
       <c r="W53" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>7-</t>
         </is>
       </c>
       <c r="X53" s="3"/>
       <c r="Y53" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z53" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Z53" s="3"/>
       <c r="AA53" s="3" t="inlineStr">
         <is>
-          <t>浙江省-温州市</t>
+          <t>河南省</t>
         </is>
       </c>
       <c r="AB53" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟将不超过10亿元用于偿还公司有息债务。其中,拟将不超过10亿元用于偿还发行人到期或赎回的公司债券(含置换偿还公司债券的自有资金)[23金瓯Y1]</t>
+          <t>本期公司债券的募集资金扣除相关发行费用后,拟用于偿还到期公司债券本金[24豫桥01,24豫桥04]</t>
         </is>
       </c>
       <c r="AC53" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,光大证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD53" s="3"/>
+          <t>东方证券股份有限公司,第一创业证券承销保荐有限责任公司</t>
+        </is>
+      </c>
+      <c r="AD53" s="3" t="inlineStr">
+        <is>
+          <t>中证信用融资担保有限公司</t>
+        </is>
+      </c>
       <c r="AE53" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -12497,22 +12505,22 @@
       </c>
       <c r="AF53" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG53" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH53" s="3" t="inlineStr">
         <is>
-          <t>光大金瓯资产管理有限公司2026年面向专业投资者公开发行公司债券(第一期)</t>
+          <t>河南省路桥建设集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI53" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ53" s="3" t="inlineStr">
@@ -12538,32 +12546,32 @@
       </c>
       <c r="AO53" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP53" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AQ53" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>建筑施工</t>
         </is>
       </c>
       <c r="AR53" s="3" t="inlineStr">
         <is>
-          <t>资产管理</t>
+          <t>专业工程</t>
         </is>
       </c>
       <c r="AS53" s="3" t="inlineStr">
         <is>
-          <t>资产管理</t>
+          <t>市政路桥</t>
         </is>
       </c>
       <c r="AT53" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU53" s="3" t="inlineStr">
@@ -12573,7 +12581,7 @@
       </c>
       <c r="AV53" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW53" s="3" t="inlineStr">
@@ -12596,7 +12604,7 @@
     <row r="54" customHeight="true" ht="18.0">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>26化学K4</t>
+          <t>26甘能K1</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -12606,7 +12614,7 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>245898.SH</t>
+          <t>524983.SZ</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
@@ -12615,40 +12623,40 @@
         </is>
       </c>
       <c r="E54" s="4" t="n">
-        <v>7.5</v>
+        <v>8.0</v>
       </c>
       <c r="F54" s="4" t="n">
         <v>8.0</v>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.80 ~ 2.50</t>
         </is>
       </c>
       <c r="H54" s="4" t="n">
-        <v>1.77</v>
+        <v>1.98</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>38.28</v>
+        <v>59.28</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>26化学K2</t>
+          <t>25甘能01</t>
         </is>
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>4.81Y</t>
+          <t>1.88Y</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>1.7324</t>
+          <t>1.7369</t>
         </is>
       </c>
       <c r="N54" s="3" t="inlineStr">
@@ -12658,12 +12666,12 @@
       </c>
       <c r="O54" s="3" t="inlineStr">
         <is>
-          <t>中国化学工程集团有限公司</t>
+          <t>甘肃能化股份有限公司</t>
         </is>
       </c>
       <c r="P54" s="3" t="inlineStr">
         <is>
-          <t>C- 22.39</t>
+          <t>E 0.00</t>
         </is>
       </c>
       <c r="Q54" s="3" t="inlineStr">
@@ -12673,7 +12681,7 @@
       </c>
       <c r="R54" s="3" t="inlineStr">
         <is>
-          <t>08-25 16:00</t>
+          <t>08-25 15:00</t>
         </is>
       </c>
       <c r="S54" s="3" t="inlineStr">
@@ -12687,17 +12695,17 @@
         </is>
       </c>
       <c r="U54" s="4" t="n">
-        <v>3.38</v>
+        <v>1.5</v>
       </c>
       <c r="V54" s="3"/>
       <c r="W54" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X54" s="3" t="inlineStr">
         <is>
-          <t>1.71%~1.81%</t>
+          <t>1.89%~1.99%</t>
         </is>
       </c>
       <c r="Y54" s="3" t="inlineStr">
@@ -12705,24 +12713,20 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z54" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z54" s="3"/>
       <c r="AA54" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>甘肃省-兰州市</t>
         </is>
       </c>
       <c r="AB54" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟将用于生产性支出,包括项目建设、偿还有息债务、补充流动资金或其他符合法律法规的用途。</t>
+          <t>本期债券的募集资金在扣除发行费用后,拟全部用于偿还有息负债[能化转债]</t>
         </is>
       </c>
       <c r="AC54" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,中信建投证券股份有限公司</t>
+          <t>国泰海通证券股份有限公司,中信证券股份有限公司,中信建投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD54" s="3"/>
@@ -12733,17 +12737,17 @@
       </c>
       <c r="AF54" s="3" t="inlineStr">
         <is>
-          <t>中央国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG54" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH54" s="3" t="inlineStr">
         <is>
-          <t>中国化学工程集团有限公司2026年面向专业投资者公开发行科技创新公司债券(第二期)(品种二)</t>
+          <t>甘肃能化股份有限公司2026年面向专业投资者公开发行科技创新公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI54" s="3" t="inlineStr">
@@ -12764,7 +12768,7 @@
       </c>
       <c r="AM54" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AN54" s="3" t="inlineStr">
@@ -12779,27 +12783,27 @@
       </c>
       <c r="AP54" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ54" s="3" t="inlineStr">
         <is>
-          <t>建筑施工</t>
+          <t>化石能源</t>
         </is>
       </c>
       <c r="AR54" s="3" t="inlineStr">
         <is>
-          <t>专业工程</t>
+          <t>煤炭</t>
         </is>
       </c>
       <c r="AS54" s="3" t="inlineStr">
         <is>
-          <t>其他专业工程</t>
+          <t>煤炭采掘</t>
         </is>
       </c>
       <c r="AT54" s="3" t="inlineStr">
         <is>
-          <t>石油化工</t>
+          <t>煤炭开采</t>
         </is>
       </c>
       <c r="AU54" s="3" t="inlineStr">
@@ -12832,7 +12836,7 @@
     <row r="55" customHeight="true" ht="18.0">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>26核电K4</t>
+          <t>26同安05</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -12842,7 +12846,7 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>245919.SH</t>
+          <t>283709.SH</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
@@ -12851,55 +12855,55 @@
         </is>
       </c>
       <c r="E55" s="4" t="n">
-        <v>25.0</v>
+        <v>3.2</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>25.0</v>
+        <v>3.2</v>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>1.10 ~ 2.10</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H55" s="4" t="n">
-        <v>1.51</v>
+        <v>1.67</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>25.67</v>
+        <v>41.67</v>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>26核电K3</t>
+          <t>26同安04</t>
         </is>
       </c>
       <c r="L55" s="3" t="inlineStr">
         <is>
-          <t>2.89Y</t>
+          <t>2.91Y</t>
         </is>
       </c>
       <c r="M55" s="3" t="inlineStr">
         <is>
-          <t>1.5902</t>
+          <t>1.7484</t>
         </is>
       </c>
       <c r="N55" s="3" t="inlineStr">
         <is>
-          <t>1.6300/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O55" s="3" t="inlineStr">
         <is>
-          <t>中国核能电力股份有限公司</t>
+          <t>同安控股有限责任公司</t>
         </is>
       </c>
       <c r="P55" s="3" t="inlineStr">
         <is>
-          <t>C+ 31.14</t>
+          <t>B- 48.82</t>
         </is>
       </c>
       <c r="Q55" s="3" t="inlineStr">
@@ -12909,7 +12913,7 @@
       </c>
       <c r="R55" s="3" t="inlineStr">
         <is>
-          <t>08-25 15:00</t>
+          <t>08-25 16:00</t>
         </is>
       </c>
       <c r="S55" s="3" t="inlineStr">
@@ -12923,42 +12927,34 @@
         </is>
       </c>
       <c r="U55" s="4" t="n">
-        <v>3.36</v>
+        <v>5.25</v>
       </c>
       <c r="V55" s="3"/>
-      <c r="W55" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="W55" s="3"/>
       <c r="X55" s="3" t="inlineStr">
         <is>
-          <t>1.56%~1.66%</t>
+          <t>1.78%~1.88%</t>
         </is>
       </c>
       <c r="Y55" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z55" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z55" s="3"/>
       <c r="AA55" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>安徽省-安庆市</t>
         </is>
       </c>
       <c r="AB55" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后将全部用于生产性支出,包括科技创新领域相关支出、偿还公司债务、补充流动资金等符合法律法规要求的用途。</t>
+          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还到期公司债券本金或置换偿还公司债券本金的自有资金。[23 同安04]</t>
         </is>
       </c>
       <c r="AC55" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,华泰联合证券有限责任公司,中国国际金融股份有限公司,国泰海通证券股份有限公司,中信证券股份有限公司</t>
+          <t>中信建投证券股份有限公司,华安证券股份有限公司</t>
         </is>
       </c>
       <c r="AD55" s="3"/>
@@ -12969,7 +12965,7 @@
       </c>
       <c r="AF55" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG55" s="3" t="inlineStr">
@@ -12979,12 +12975,12 @@
       </c>
       <c r="AH55" s="3" t="inlineStr">
         <is>
-          <t>中国核能电力股份有限公司2026年面向专业投资者公开发行科技创新公司债券(第四期)</t>
+          <t>同安控股有限责任公司2026年面向专业投资者非公开发行公司债券(第五期)</t>
         </is>
       </c>
       <c r="AI55" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ55" s="3" t="inlineStr">
@@ -13010,32 +13006,32 @@
       </c>
       <c r="AO55" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP55" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ55" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR55" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS55" s="3" t="inlineStr">
         <is>
-          <t>核电</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT55" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>纺织制造</t>
         </is>
       </c>
       <c r="AU55" s="3" t="inlineStr">
@@ -13068,7 +13064,7 @@
     <row r="56" customHeight="true" ht="18.0">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>26罗投控03</t>
+          <t>26金瓯01</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -13078,62 +13074,64 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>520441.SZ</t>
+          <t>524984.SZ</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E56" s="4" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="F56" s="3"/>
+        <v>10.0</v>
+      </c>
+      <c r="F56" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.50 ~ 2.00</t>
         </is>
       </c>
       <c r="H56" s="4" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="I56" s="4" t="n">
-        <v>37.28</v>
+        <v>44.67</v>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>26罗投控K2</t>
+          <t>25金瓯Y1</t>
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>2.60Y+2.00Y</t>
+          <t>1.64Y+N</t>
         </is>
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>1.6613</t>
+          <t>2.0902</t>
         </is>
       </c>
       <c r="N56" s="3" t="inlineStr">
         <is>
-          <t>--/1.6700</t>
+          <t>2.2000/--</t>
         </is>
       </c>
       <c r="O56" s="3" t="inlineStr">
         <is>
-          <t>深圳市罗湖投资控股有限公司</t>
+          <t>光大金瓯资产管理有限公司</t>
         </is>
       </c>
       <c r="P56" s="3" t="inlineStr">
         <is>
-          <t>C 25.95</t>
+          <t>C- 20.00</t>
         </is>
       </c>
       <c r="Q56" s="3" t="inlineStr">
@@ -13153,42 +13151,42 @@
       </c>
       <c r="T56" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="U56" s="4" t="n">
-        <v>3.9</v>
+        <v>4.61</v>
       </c>
       <c r="V56" s="3"/>
       <c r="W56" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
-        </is>
-      </c>
-      <c r="X56" s="3" t="inlineStr">
-        <is>
-          <t>1.69%~1.79%</t>
-        </is>
-      </c>
+          <t>6+</t>
+        </is>
+      </c>
+      <c r="X56" s="3"/>
       <c r="Y56" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z56" s="3"/>
+      <c r="Z56" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA56" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>浙江省-温州市</t>
         </is>
       </c>
       <c r="AB56" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟使用2亿元用于偿还有息负债,剩余部分用于补充流动资金。</t>
+          <t>本期债券募集资金扣除发行费用后,拟将不超过10亿元用于偿还公司有息债务。其中,拟将不超过10亿元用于偿还发行人到期或赎回的公司债券(含置换偿还公司债券的自有资金)[23金瓯Y1]</t>
         </is>
       </c>
       <c r="AC56" s="3" t="inlineStr">
         <is>
-          <t>国信证券股份有限公司,中银国际证券股份有限公司</t>
+          <t>中信建投证券股份有限公司,光大证券股份有限公司</t>
         </is>
       </c>
       <c r="AD56" s="3"/>
@@ -13199,7 +13197,7 @@
       </c>
       <c r="AF56" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG56" s="3" t="inlineStr">
@@ -13209,17 +13207,17 @@
       </c>
       <c r="AH56" s="3" t="inlineStr">
         <is>
-          <t>深圳市罗湖投资控股有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
+          <t>光大金瓯资产管理有限公司2026年面向专业投资者公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI56" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ56" s="3" t="inlineStr">
         <is>
-          <t>2031-08-28</t>
+          <t>2029-08-27</t>
         </is>
       </c>
       <c r="AK56" s="3"/>
@@ -13230,37 +13228,37 @@
       </c>
       <c r="AM56" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AN56" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AO56" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP56" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ56" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR56" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>资产管理</t>
         </is>
       </c>
       <c r="AS56" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>资产管理</t>
         </is>
       </c>
       <c r="AT56" s="3" t="inlineStr">
@@ -13270,7 +13268,7 @@
       </c>
       <c r="AU56" s="3" t="inlineStr">
         <is>
-          <t>2029-08-28</t>
+          <t/>
         </is>
       </c>
       <c r="AV56" s="3" t="inlineStr">
@@ -13280,7 +13278,7 @@
       </c>
       <c r="AW56" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX56" s="3" t="inlineStr">
@@ -13298,7 +13296,7 @@
     <row r="57" customHeight="true" ht="18.0">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>26西经发</t>
+          <t>26化学K4</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -13308,7 +13306,7 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>245975.SH</t>
+          <t>245898.SH</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
@@ -13320,52 +13318,52 @@
         <v>7.5</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>7.5</v>
+        <v>8.0</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2.30 ~ 3.50</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H57" s="4" t="n">
-        <v>2.55</v>
+        <v>1.77</v>
       </c>
       <c r="I57" s="4" t="n">
-        <v>116.28</v>
+        <v>38.28</v>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>26经发F2</t>
+          <t>26化学K2</t>
         </is>
       </c>
       <c r="L57" s="3" t="inlineStr">
         <is>
-          <t>4.91Y</t>
+          <t>4.81Y</t>
         </is>
       </c>
       <c r="M57" s="3" t="inlineStr">
         <is>
-          <t>2.8636</t>
+          <t>1.7324</t>
         </is>
       </c>
       <c r="N57" s="3" t="inlineStr">
         <is>
-          <t>--/2.6500</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O57" s="3" t="inlineStr">
         <is>
-          <t>西安经发集团有限责任公司</t>
+          <t>中国化学工程集团有限公司</t>
         </is>
       </c>
       <c r="P57" s="3" t="inlineStr">
         <is>
-          <t>C- 22.74</t>
+          <t>C- 24.39</t>
         </is>
       </c>
       <c r="Q57" s="3" t="inlineStr">
@@ -13375,7 +13373,7 @@
       </c>
       <c r="R57" s="3" t="inlineStr">
         <is>
-          <t>08-25 15:00</t>
+          <t>08-25 16:00</t>
         </is>
       </c>
       <c r="S57" s="3" t="inlineStr">
@@ -13389,34 +13387,42 @@
         </is>
       </c>
       <c r="U57" s="4" t="n">
-        <v>2.26</v>
+        <v>3.38</v>
       </c>
       <c r="V57" s="3"/>
       <c r="W57" s="3" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="X57" s="3"/>
+          <t>4+</t>
+        </is>
+      </c>
+      <c r="X57" s="3" t="inlineStr">
+        <is>
+          <t>1.71%~1.81%</t>
+        </is>
+      </c>
       <c r="Y57" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z57" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z57" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA57" s="3" t="inlineStr">
         <is>
-          <t>陕西省-西安市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB57" s="3" t="inlineStr">
         <is>
-          <t>本次债券发行规模为7.50亿元,募集资金扣除发行费用后,拟用于偿还到期公司债券本金[21西经发]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟将用于生产性支出,包括项目建设、偿还有息债务、补充流动资金或其他符合法律法规的用途。</t>
         </is>
       </c>
       <c r="AC57" s="3" t="inlineStr">
         <is>
-          <t>天风证券股份有限公司,五矿证券有限公司</t>
+          <t>中信证券股份有限公司,中信建投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD57" s="3"/>
@@ -13427,7 +13433,7 @@
       </c>
       <c r="AF57" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>中央国有企业</t>
         </is>
       </c>
       <c r="AG57" s="3" t="inlineStr">
@@ -13437,7 +13443,7 @@
       </c>
       <c r="AH57" s="3" t="inlineStr">
         <is>
-          <t>西安经发集团有限责任公司2026年面向专业投资者公开发行公司债券</t>
+          <t>中国化学工程集团有限公司2026年面向专业投资者公开发行科技创新公司债券(第二期)(品种二)</t>
         </is>
       </c>
       <c r="AI57" s="3" t="inlineStr">
@@ -13468,32 +13474,32 @@
       </c>
       <c r="AO57" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP57" s="3" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ57" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>建筑施工</t>
         </is>
       </c>
       <c r="AR57" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>专业工程</t>
         </is>
       </c>
       <c r="AS57" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>其他专业工程</t>
         </is>
       </c>
       <c r="AT57" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>石油化工</t>
         </is>
       </c>
       <c r="AU57" s="3" t="inlineStr">
@@ -13526,7 +13532,7 @@
     <row r="58" customHeight="true" ht="18.0">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>26甘能K1</t>
+          <t>26核电K4</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -13536,62 +13542,64 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>524983.SZ</t>
+          <t>245919.SH</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E58" s="4" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="F58" s="3"/>
+        <v>25.0</v>
+      </c>
+      <c r="F58" s="4" t="n">
+        <v>25.0</v>
+      </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.50</t>
+          <t>1.10 ~ 2.10</t>
         </is>
       </c>
       <c r="H58" s="4" t="n">
-        <v>1.98</v>
+        <v>1.51</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>59.28</v>
+        <v>25.67</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>25甘能01</t>
+          <t>26核电K3</t>
         </is>
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>1.88Y</t>
+          <t>2.89Y</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>1.7369</t>
+          <t>1.5902</t>
         </is>
       </c>
       <c r="N58" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6300/--</t>
         </is>
       </c>
       <c r="O58" s="3" t="inlineStr">
         <is>
-          <t>甘肃能化股份有限公司</t>
+          <t>中国核能电力股份有限公司</t>
         </is>
       </c>
       <c r="P58" s="3" t="inlineStr">
         <is>
-          <t>E 0.00</t>
+          <t>C 27.38</t>
         </is>
       </c>
       <c r="Q58" s="3" t="inlineStr">
@@ -13614,16 +13622,18 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="U58" s="3"/>
+      <c r="U58" s="4" t="n">
+        <v>3.36</v>
+      </c>
       <c r="V58" s="3"/>
       <c r="W58" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X58" s="3" t="inlineStr">
         <is>
-          <t>1.89%~1.99%</t>
+          <t>1.56%~1.66%</t>
         </is>
       </c>
       <c r="Y58" s="3" t="inlineStr">
@@ -13631,20 +13641,24 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z58" s="3"/>
+      <c r="Z58" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA58" s="3" t="inlineStr">
         <is>
-          <t>甘肃省-兰州市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB58" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金在扣除发行费用后,拟全部用于偿还有息负债[能化转债]</t>
+          <t>本期债券募集资金扣除发行费用后将全部用于生产性支出,包括科技创新领域相关支出、偿还公司债务、补充流动资金等符合法律法规要求的用途。</t>
         </is>
       </c>
       <c r="AC58" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,中信证券股份有限公司,中信建投证券股份有限公司</t>
+          <t>中信建投证券股份有限公司,华泰联合证券有限责任公司,中国国际金融股份有限公司,国泰海通证券股份有限公司,中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD58" s="3"/>
@@ -13655,17 +13669,17 @@
       </c>
       <c r="AF58" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG58" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH58" s="3" t="inlineStr">
         <is>
-          <t>甘肃能化股份有限公司2026年面向专业投资者公开发行科技创新公司债券(第一期)</t>
+          <t>中国核能电力股份有限公司2026年面向专业投资者公开发行科技创新公司债券(第四期)</t>
         </is>
       </c>
       <c r="AI58" s="3" t="inlineStr">
@@ -13675,7 +13689,7 @@
       </c>
       <c r="AJ58" s="3" t="inlineStr">
         <is>
-          <t>2031-08-27</t>
+          <t>2029-08-27</t>
         </is>
       </c>
       <c r="AK58" s="3"/>
@@ -13701,27 +13715,27 @@
       </c>
       <c r="AP58" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ58" s="3" t="inlineStr">
         <is>
-          <t>化石能源</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR58" s="3" t="inlineStr">
         <is>
-          <t>煤炭</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AS58" s="3" t="inlineStr">
         <is>
-          <t>煤炭采掘</t>
+          <t>核电</t>
         </is>
       </c>
       <c r="AT58" s="3" t="inlineStr">
         <is>
-          <t>煤炭开采</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU58" s="3" t="inlineStr">
@@ -13754,7 +13768,7 @@
     <row r="59" customHeight="true" ht="18.0">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>26浔交02</t>
+          <t>26罗投控03</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -13764,62 +13778,62 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>283756.SH</t>
+          <t>520441.SZ</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>5+2</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>5.2</v>
+        <v>3.0</v>
       </c>
       <c r="F59" s="3"/>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.80</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H59" s="4" t="n">
-        <v>2.14</v>
+        <v>1.76</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>62.52</v>
+        <v>37.28</v>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>26浔交01</t>
+          <t>26罗投控K2</t>
         </is>
       </c>
       <c r="L59" s="3" t="inlineStr">
         <is>
-          <t>4.84Y+2.00Y</t>
+          <t>2.60Y+2.00Y</t>
         </is>
       </c>
       <c r="M59" s="3" t="inlineStr">
         <is>
-          <t>2.1623</t>
+          <t>1.6613</t>
         </is>
       </c>
       <c r="N59" s="3" t="inlineStr">
         <is>
-          <t>2.1700/--</t>
+          <t>--/1.6700</t>
         </is>
       </c>
       <c r="O59" s="3" t="inlineStr">
         <is>
-          <t>湖州市南浔区交通投资集团有限公司</t>
+          <t>深圳市罗湖投资控股有限公司</t>
         </is>
       </c>
       <c r="P59" s="3" t="inlineStr">
         <is>
-          <t>C- 23.43</t>
+          <t>C+ 32.70</t>
         </is>
       </c>
       <c r="Q59" s="3" t="inlineStr">
@@ -13839,40 +13853,42 @@
       </c>
       <c r="T59" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="U59" s="3"/>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="U59" s="4" t="n">
+        <v>3.9</v>
+      </c>
       <c r="V59" s="3"/>
       <c r="W59" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X59" s="3" t="inlineStr">
         <is>
-          <t>2.15%~2.25%</t>
+          <t>1.69%~1.79%</t>
         </is>
       </c>
       <c r="Y59" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z59" s="3"/>
       <c r="AA59" s="3" t="inlineStr">
         <is>
-          <t>浙江省-湖州市</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB59" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟用于偿还回售的公司债券本金[23浔交02]</t>
+          <t>本期债券募集资金扣除发行费用后,拟使用2亿元用于偿还有息负债,剩余部分用于补充流动资金。</t>
         </is>
       </c>
       <c r="AC59" s="3" t="inlineStr">
         <is>
-          <t>东方证券股份有限公司,华鑫证券有限责任公司,浙商证券股份有限公司</t>
+          <t>国信证券股份有限公司,中银国际证券股份有限公司</t>
         </is>
       </c>
       <c r="AD59" s="3"/>
@@ -13888,12 +13904,12 @@
       </c>
       <c r="AG59" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH59" s="3" t="inlineStr">
         <is>
-          <t>湖州市南浔区交通投资集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>深圳市罗湖投资控股有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI59" s="3" t="inlineStr">
@@ -13903,14 +13919,10 @@
       </c>
       <c r="AJ59" s="3" t="inlineStr">
         <is>
-          <t>2033-08-27</t>
-        </is>
-      </c>
-      <c r="AK59" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2031-08-28</t>
+        </is>
+      </c>
+      <c r="AK59" s="3"/>
       <c r="AL59" s="3" t="inlineStr">
         <is>
           <t/>
@@ -13923,42 +13935,42 @@
       </c>
       <c r="AN59" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AO59" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP59" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ59" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR59" s="3" t="inlineStr">
         <is>
-          <t>其他交运基础设施</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS59" s="3" t="inlineStr">
         <is>
-          <t>其他交运基础设施</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT59" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU59" s="3" t="inlineStr">
         <is>
-          <t>2031-08-27</t>
+          <t>2029-08-28</t>
         </is>
       </c>
       <c r="AV59" s="3" t="inlineStr">
@@ -13986,7 +13998,7 @@
     <row r="60" customHeight="true" ht="18.0">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>26富港01</t>
+          <t>26西经发</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -13996,64 +14008,64 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>283735.SH</t>
+          <t>245975.SH</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E60" s="4" t="n">
-        <v>5.0</v>
+        <v>7.5</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>5.0</v>
+        <v>7.5</v>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.50</t>
+          <t>2.30 ~ 3.50</t>
         </is>
       </c>
       <c r="H60" s="4" t="n">
-        <v>1.83</v>
+        <v>2.55</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>57.67</v>
+        <v>116.28</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>25富港01</t>
+          <t>26经发F2</t>
         </is>
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>2.20Y</t>
+          <t>4.91Y</t>
         </is>
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>1.8022</t>
+          <t>2.8636</t>
         </is>
       </c>
       <c r="N60" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/2.6500</t>
         </is>
       </c>
       <c r="O60" s="3" t="inlineStr">
         <is>
-          <t>富港建设集团有限公司</t>
+          <t>西安经发集团有限责任公司</t>
         </is>
       </c>
       <c r="P60" s="3" t="inlineStr">
         <is>
-          <t>C- 11.03</t>
+          <t>C- 20.04</t>
         </is>
       </c>
       <c r="Q60" s="3" t="inlineStr">
@@ -14077,7 +14089,7 @@
         </is>
       </c>
       <c r="U60" s="4" t="n">
-        <v>2.88</v>
+        <v>2.26</v>
       </c>
       <c r="V60" s="3"/>
       <c r="W60" s="3" t="inlineStr">
@@ -14088,30 +14100,26 @@
       <c r="X60" s="3"/>
       <c r="Y60" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z60" s="3"/>
       <c r="AA60" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南通市</t>
+          <t>陕西省-西安市</t>
         </is>
       </c>
       <c r="AB60" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟将全部用于偿还即将到期的公司债券本金[23富港01]</t>
+          <t>本次债券发行规模为7.50亿元,募集资金扣除发行费用后,拟用于偿还到期公司债券本金[21西经发]</t>
         </is>
       </c>
       <c r="AC60" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,中信建投证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD60" s="3" t="inlineStr">
-        <is>
-          <t>江苏皋开投资发展集团有限公司</t>
-        </is>
-      </c>
+          <t>天风证券股份有限公司,五矿证券有限公司</t>
+        </is>
+      </c>
+      <c r="AD60" s="3"/>
       <c r="AE60" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -14129,17 +14137,17 @@
       </c>
       <c r="AH60" s="3" t="inlineStr">
         <is>
-          <t>富港建设集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>西安经发集团有限责任公司2026年面向专业投资者公开发行公司债券</t>
         </is>
       </c>
       <c r="AI60" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ60" s="3" t="inlineStr">
         <is>
-          <t>2029-08-27</t>
+          <t>2031-08-27</t>
         </is>
       </c>
       <c r="AK60" s="3"/>
@@ -14150,7 +14158,7 @@
       </c>
       <c r="AM60" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AN60" s="3" t="inlineStr">
@@ -14160,7 +14168,7 @@
       </c>
       <c r="AO60" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP60" s="3" t="inlineStr">
@@ -14175,12 +14183,12 @@
       </c>
       <c r="AR60" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS60" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT60" s="3" t="inlineStr">
@@ -14195,7 +14203,7 @@
       </c>
       <c r="AV60" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW60" s="3" t="inlineStr">
@@ -14218,7 +14226,7 @@
     <row r="61" customHeight="true" ht="18.0">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>26豫桥05</t>
+          <t>26浔交02</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -14228,118 +14236,122 @@
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>283658.SH</t>
+          <t>283756.SH</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5+2</t>
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>6.0</v>
-      </c>
-      <c r="F61" s="3"/>
+        <v>5.2</v>
+      </c>
+      <c r="F61" s="4" t="n">
+        <v>5.2</v>
+      </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 3.50</t>
+          <t>1.80 ~ 2.80</t>
         </is>
       </c>
       <c r="H61" s="4" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>94.67</v>
+        <v>62.52</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="K61" s="3" t="inlineStr">
+        <is>
+          <t>26浔交01</t>
+        </is>
+      </c>
+      <c r="L61" s="3" t="inlineStr">
+        <is>
+          <t>4.84Y+2.00Y</t>
+        </is>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>2.1623</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
+          <t>2.1700/--</t>
+        </is>
+      </c>
+      <c r="O61" s="3" t="inlineStr">
+        <is>
+          <t>湖州市南浔区交通投资集团有限公司</t>
+        </is>
+      </c>
+      <c r="P61" s="3" t="inlineStr">
+        <is>
+          <t>C- 21.79</t>
+        </is>
+      </c>
+      <c r="Q61" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="R61" s="3" t="inlineStr">
+        <is>
+          <t>08-25 15:00</t>
+        </is>
+      </c>
+      <c r="S61" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K61" s="3" t="inlineStr">
-        <is>
-          <t>26河南路桥MTN001</t>
-        </is>
-      </c>
-      <c r="L61" s="3" t="inlineStr">
-        <is>
-          <t>2.97Y</t>
-        </is>
-      </c>
-      <c r="M61" s="3" t="inlineStr">
-        <is>
-          <t>2.3646</t>
-        </is>
-      </c>
-      <c r="N61" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O61" s="3" t="inlineStr">
-        <is>
-          <t>河南省路桥建设集团有限公司</t>
-        </is>
-      </c>
-      <c r="P61" s="3" t="inlineStr">
-        <is>
-          <t>C 25.37</t>
-        </is>
-      </c>
-      <c r="Q61" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="R61" s="3" t="inlineStr">
-        <is>
-          <t>08-25 15:00</t>
-        </is>
-      </c>
-      <c r="S61" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T61" s="3" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="U61" s="3"/>
+      <c r="U61" s="4" t="n">
+        <v>4.15</v>
+      </c>
       <c r="V61" s="3"/>
       <c r="W61" s="3" t="inlineStr">
         <is>
-          <t>7-</t>
-        </is>
-      </c>
-      <c r="X61" s="3"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X61" s="3" t="inlineStr">
+        <is>
+          <t>2.15%~2.25%</t>
+        </is>
+      </c>
       <c r="Y61" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z61" s="3"/>
       <c r="AA61" s="3" t="inlineStr">
         <is>
-          <t>河南省</t>
+          <t>浙江省-湖州市</t>
         </is>
       </c>
       <c r="AB61" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券的募集资金扣除相关发行费用后,拟用于偿还到期公司债券本金[24豫桥01,24豫桥04]</t>
+          <t>本期债券募集资金扣除发行费用后,拟用于偿还回售的公司债券本金[23浔交02]</t>
         </is>
       </c>
       <c r="AC61" s="3" t="inlineStr">
         <is>
-          <t>东方证券股份有限公司,第一创业证券承销保荐有限责任公司</t>
-        </is>
-      </c>
-      <c r="AD61" s="3" t="inlineStr">
-        <is>
-          <t>中证信用融资担保有限公司</t>
-        </is>
-      </c>
+          <t>东方证券股份有限公司,华鑫证券有限责任公司,浙商证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD61" s="3"/>
       <c r="AE61" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -14357,7 +14369,7 @@
       </c>
       <c r="AH61" s="3" t="inlineStr">
         <is>
-          <t>河南省路桥建设集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>湖州市南浔区交通投资集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI61" s="3" t="inlineStr">
@@ -14367,10 +14379,14 @@
       </c>
       <c r="AJ61" s="3" t="inlineStr">
         <is>
-          <t>2029-08-27</t>
-        </is>
-      </c>
-      <c r="AK61" s="3"/>
+          <t>2033-08-27</t>
+        </is>
+      </c>
+      <c r="AK61" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL61" s="3" t="inlineStr">
         <is>
           <t/>
@@ -14378,7 +14394,7 @@
       </c>
       <c r="AM61" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AN61" s="3" t="inlineStr">
@@ -14393,22 +14409,22 @@
       </c>
       <c r="AP61" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ61" s="3" t="inlineStr">
         <is>
-          <t>建筑施工</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR61" s="3" t="inlineStr">
         <is>
-          <t>专业工程</t>
+          <t>其他交运基础设施</t>
         </is>
       </c>
       <c r="AS61" s="3" t="inlineStr">
         <is>
-          <t>市政路桥</t>
+          <t>其他交运基础设施</t>
         </is>
       </c>
       <c r="AT61" s="3" t="inlineStr">
@@ -14418,17 +14434,17 @@
       </c>
       <c r="AU61" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2031-08-27</t>
         </is>
       </c>
       <c r="AV61" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW61" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX61" s="3" t="inlineStr">
@@ -14446,7 +14462,7 @@
     <row r="62" customHeight="true" ht="18.0">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>26镇海01</t>
+          <t>26富港01</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -14456,7 +14472,7 @@
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>283373.SH</t>
+          <t>283735.SH</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
@@ -14467,36 +14483,38 @@
       <c r="E62" s="4" t="n">
         <v>5.0</v>
       </c>
-      <c r="F62" s="3"/>
+      <c r="F62" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.70 ~ 2.50</t>
         </is>
       </c>
       <c r="H62" s="4" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>49.67</v>
+        <v>57.67</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>24镇海02</t>
+          <t>25富港01</t>
         </is>
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>2.92Y</t>
+          <t>2.20Y</t>
         </is>
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
-          <t>1.7747</t>
+          <t>1.8022</t>
         </is>
       </c>
       <c r="N62" s="3" t="inlineStr">
@@ -14506,12 +14524,12 @@
       </c>
       <c r="O62" s="3" t="inlineStr">
         <is>
-          <t>宁波市镇开集团有限公司</t>
+          <t>富港建设集团有限公司</t>
         </is>
       </c>
       <c r="P62" s="3" t="inlineStr">
         <is>
-          <t>E 0.00</t>
+          <t>D+ 8.26</t>
         </is>
       </c>
       <c r="Q62" s="3" t="inlineStr">
@@ -14531,39 +14549,45 @@
       </c>
       <c r="T62" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="U62" s="3"/>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="U62" s="4" t="n">
+        <v>2.88</v>
+      </c>
       <c r="V62" s="3"/>
       <c r="W62" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X62" s="3"/>
       <c r="Y62" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z62" s="3"/>
       <c r="AA62" s="3" t="inlineStr">
         <is>
-          <t>浙江省-宁波市</t>
+          <t>江苏省-南通市</t>
         </is>
       </c>
       <c r="AB62" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,用于偿还到期的“23镇海债”公司债券本金[23镇海债]</t>
+          <t>本期债券募集资金扣除发行费用后,拟将全部用于偿还即将到期的公司债券本金[23富港01]</t>
         </is>
       </c>
       <c r="AC62" s="3" t="inlineStr">
         <is>
-          <t>甬兴证券有限公司</t>
-        </is>
-      </c>
-      <c r="AD62" s="3"/>
+          <t>国泰海通证券股份有限公司,中信建投证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD62" s="3" t="inlineStr">
+        <is>
+          <t>江苏皋开投资发展集团有限公司</t>
+        </is>
+      </c>
       <c r="AE62" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -14581,7 +14605,7 @@
       </c>
       <c r="AH62" s="3" t="inlineStr">
         <is>
-          <t>宁波市镇开集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>富港建设集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI62" s="3" t="inlineStr">
@@ -14591,7 +14615,7 @@
       </c>
       <c r="AJ62" s="3" t="inlineStr">
         <is>
-          <t>2029-08-28</t>
+          <t>2029-08-27</t>
         </is>
       </c>
       <c r="AK62" s="3"/>
@@ -14607,17 +14631,17 @@
       </c>
       <c r="AN62" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AO62" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP62" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AQ62" s="3" t="inlineStr">
@@ -14647,7 +14671,7 @@
       </c>
       <c r="AV62" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW62" s="3" t="inlineStr">
@@ -14670,7 +14694,7 @@
     <row r="63" customHeight="true" ht="18.0">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>26城铁01</t>
+          <t>26镇海01</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -14680,49 +14704,47 @@
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>283762.SH</t>
+          <t>283373.SH</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E63" s="4" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="F63" s="4" t="n">
-        <v>8.0</v>
-      </c>
+        <v>5.0</v>
+      </c>
+      <c r="F63" s="3"/>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H63" s="4" t="n">
-        <v>2.08</v>
+        <v>1.75</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>69.28</v>
+        <v>49.67</v>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>25城铁02</t>
+          <t>24镇海02</t>
         </is>
       </c>
       <c r="L63" s="3" t="inlineStr">
         <is>
-          <t>3.87Y</t>
+          <t>2.92Y</t>
         </is>
       </c>
       <c r="M63" s="3" t="inlineStr">
         <is>
-          <t>1.8769</t>
+          <t>1.7747</t>
         </is>
       </c>
       <c r="N63" s="3" t="inlineStr">
@@ -14732,12 +14754,12 @@
       </c>
       <c r="O63" s="3" t="inlineStr">
         <is>
-          <t>无锡沪宁城铁惠山站区投资开发建设有限公司</t>
+          <t>宁波市镇开集团有限公司</t>
         </is>
       </c>
       <c r="P63" s="3" t="inlineStr">
         <is>
-          <t>C- 22.90</t>
+          <t>E 0.00</t>
         </is>
       </c>
       <c r="Q63" s="3" t="inlineStr">
@@ -14757,42 +14779,36 @@
       </c>
       <c r="T63" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="U63" s="4" t="n">
-        <v>1.65</v>
-      </c>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="U63" s="3"/>
       <c r="V63" s="3"/>
       <c r="W63" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
-        </is>
-      </c>
-      <c r="X63" s="3" t="inlineStr">
-        <is>
-          <t>1.86%~1.96%</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X63" s="3"/>
       <c r="Y63" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z63" s="3"/>
       <c r="AA63" s="3" t="inlineStr">
         <is>
-          <t>江苏省-无锡市</t>
+          <t>浙江省-宁波市</t>
         </is>
       </c>
       <c r="AB63" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金不超过8亿元,在不考虑发行费用的情况下,拟用于偿还存量公司债券本金[23城铁债]</t>
+          <t>本期公司债券募集资金扣除发行费用后,用于偿还到期的“23镇海债”公司债券本金[23镇海债]</t>
         </is>
       </c>
       <c r="AC63" s="3" t="inlineStr">
         <is>
-          <t>天风证券股份有限公司,国联民生证券承销保荐有限公司</t>
+          <t>甬兴证券有限公司</t>
         </is>
       </c>
       <c r="AD63" s="3"/>
@@ -14813,7 +14829,7 @@
       </c>
       <c r="AH63" s="3" t="inlineStr">
         <is>
-          <t>无锡沪宁城铁惠山站区投资开发建设有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>宁波市镇开集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI63" s="3" t="inlineStr">
@@ -14823,7 +14839,7 @@
       </c>
       <c r="AJ63" s="3" t="inlineStr">
         <is>
-          <t>2031-08-27</t>
+          <t>2029-08-28</t>
         </is>
       </c>
       <c r="AK63" s="3"/>
@@ -14839,17 +14855,17 @@
       </c>
       <c r="AN63" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AO63" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP63" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ63" s="3" t="inlineStr">
@@ -14902,7 +14918,7 @@
     <row r="64" customHeight="true" ht="18.0">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>26经金K1</t>
+          <t>26城铁01</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -14912,7 +14928,7 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>520428.SZ</t>
+          <t>283762.SH</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
@@ -14921,38 +14937,40 @@
         </is>
       </c>
       <c r="E64" s="4" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="F64" s="3"/>
+        <v>8.0</v>
+      </c>
+      <c r="F64" s="4" t="n">
+        <v>8.0</v>
+      </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 3.00</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="H64" s="4" t="n">
-        <v>2.35</v>
+        <v>2.08</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>96.28</v>
+        <v>69.28</v>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>25经金Z1</t>
+          <t>25城铁02</t>
         </is>
       </c>
       <c r="L64" s="3" t="inlineStr">
         <is>
-          <t>1.68Y+2.00Y</t>
+          <t>3.87Y</t>
         </is>
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
-          <t>2.0607</t>
+          <t>1.8769</t>
         </is>
       </c>
       <c r="N64" s="3" t="inlineStr">
@@ -14962,12 +14980,12 @@
       </c>
       <c r="O64" s="3" t="inlineStr">
         <is>
-          <t>西安经开金融控股有限公司</t>
+          <t>无锡沪宁城铁惠山站区投资开发建设有限公司</t>
         </is>
       </c>
       <c r="P64" s="3" t="inlineStr">
         <is>
-          <t>C- 14.12</t>
+          <t>C- 17.88</t>
         </is>
       </c>
       <c r="Q64" s="3" t="inlineStr">
@@ -14991,38 +15009,38 @@
         </is>
       </c>
       <c r="U64" s="4" t="n">
-        <v>3.1</v>
+        <v>1.65</v>
       </c>
       <c r="V64" s="3"/>
       <c r="W64" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X64" s="3" t="inlineStr">
         <is>
-          <t>2.74%~2.84%</t>
+          <t>1.86%~1.96%</t>
         </is>
       </c>
       <c r="Y64" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z64" s="3"/>
       <c r="AA64" s="3" t="inlineStr">
         <is>
-          <t>陕西省-西安市</t>
+          <t>江苏省-无锡市</t>
         </is>
       </c>
       <c r="AB64" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金拟将3.10亿元用于科技创新类股权投资(含创业投资基金、政府出资产业投资基金等符合国家相关规定的基金出资)</t>
+          <t>本期债券募集资金不超过8亿元,在不考虑发行费用的情况下,拟用于偿还存量公司债券本金[23城铁债]</t>
         </is>
       </c>
       <c r="AC64" s="3" t="inlineStr">
         <is>
-          <t>五矿证券有限公司,中泰证券股份有限公司</t>
+          <t>天风证券股份有限公司,国联民生证券承销保荐有限公司</t>
         </is>
       </c>
       <c r="AD64" s="3"/>
@@ -15038,12 +15056,12 @@
       </c>
       <c r="AG64" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH64" s="3" t="inlineStr">
         <is>
-          <t>西安经开金融控股有限公司2026年面向专业投资者非公开发行科技创新公司债券(第一期)</t>
+          <t>无锡沪宁城铁惠山站区投资开发建设有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI64" s="3" t="inlineStr">
@@ -15074,32 +15092,32 @@
       </c>
       <c r="AO64" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP64" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ64" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR64" s="3" t="inlineStr">
         <is>
-          <t>金融控股</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS64" s="3" t="inlineStr">
         <is>
-          <t>金融控股</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT64" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU64" s="3" t="inlineStr">
@@ -15199,7 +15217,7 @@
       </c>
       <c r="P65" s="3" t="inlineStr">
         <is>
-          <t>C- 22.07</t>
+          <t>C- 20.90</t>
         </is>
       </c>
       <c r="Q65" s="3" t="inlineStr">
@@ -15287,7 +15305,7 @@
       <c r="AK65" s="3"/>
       <c r="AL65" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AM65" s="3" t="inlineStr">
@@ -15427,7 +15445,7 @@
       </c>
       <c r="P66" s="3" t="inlineStr">
         <is>
-          <t>B- 40.24</t>
+          <t>B- 38.66</t>
         </is>
       </c>
       <c r="Q66" s="3" t="inlineStr">
@@ -15663,7 +15681,7 @@
       </c>
       <c r="P67" s="3" t="inlineStr">
         <is>
-          <t>B- 36.12</t>
+          <t>C+ 31.25</t>
         </is>
       </c>
       <c r="Q67" s="3" t="inlineStr">
@@ -15755,7 +15773,7 @@
       <c r="AK67" s="3"/>
       <c r="AL67" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AM67" s="3" t="inlineStr">
@@ -15849,7 +15867,9 @@
       <c r="E68" s="4" t="n">
         <v>14.5</v>
       </c>
-      <c r="F68" s="3"/>
+      <c r="F68" s="4" t="n">
+        <v>14.5</v>
+      </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
           <t>1.50 ~ 2.50</t>
@@ -15916,7 +15936,9 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="U68" s="3"/>
+      <c r="U68" s="4" t="n">
+        <v>4.48</v>
+      </c>
       <c r="V68" s="3"/>
       <c r="W68" s="3" t="inlineStr">
         <is>
@@ -16117,7 +16139,7 @@
       </c>
       <c r="P69" s="3" t="inlineStr">
         <is>
-          <t>C- 24.01</t>
+          <t>C 26.06</t>
         </is>
       </c>
       <c r="Q69" s="3" t="inlineStr">
@@ -16347,7 +16369,7 @@
       </c>
       <c r="P70" s="3" t="inlineStr">
         <is>
-          <t>C- 20.26</t>
+          <t>C 25.47</t>
         </is>
       </c>
       <c r="Q70" s="3" t="inlineStr">
@@ -16585,7 +16607,7 @@
       </c>
       <c r="P71" s="3" t="inlineStr">
         <is>
-          <t>A- 68.57</t>
+          <t>A- 65.71</t>
         </is>
       </c>
       <c r="Q71" s="3" t="inlineStr">
@@ -16815,7 +16837,7 @@
       </c>
       <c r="P72" s="3" t="inlineStr">
         <is>
-          <t>E 0.00</t>
+          <t>C 29.94</t>
         </is>
       </c>
       <c r="Q72" s="3" t="inlineStr">
@@ -17049,7 +17071,7 @@
       </c>
       <c r="P73" s="3" t="inlineStr">
         <is>
-          <t>B- 40.61</t>
+          <t>B- 40.14</t>
         </is>
       </c>
       <c r="Q73" s="3" t="inlineStr">
@@ -17283,7 +17305,7 @@
       </c>
       <c r="P74" s="3" t="inlineStr">
         <is>
-          <t>B- 48.98</t>
+          <t>B- 49.82</t>
         </is>
       </c>
       <c r="Q74" s="3" t="inlineStr">
@@ -17521,7 +17543,7 @@
       </c>
       <c r="P75" s="3" t="inlineStr">
         <is>
-          <t>B- 43.21</t>
+          <t>B- 45.60</t>
         </is>
       </c>
       <c r="Q75" s="3" t="inlineStr">
@@ -17755,7 +17777,7 @@
       </c>
       <c r="P76" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.45</t>
+          <t>B- 36.08</t>
         </is>
       </c>
       <c r="Q76" s="3" t="inlineStr">
@@ -17847,7 +17869,7 @@
       <c r="AK76" s="3"/>
       <c r="AL76" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AM76" s="3" t="inlineStr">
@@ -17987,7 +18009,7 @@
       </c>
       <c r="P77" s="3" t="inlineStr">
         <is>
-          <t>E 0.00</t>
+          <t>C 30.00</t>
         </is>
       </c>
       <c r="Q77" s="3" t="inlineStr">
@@ -18215,7 +18237,7 @@
       </c>
       <c r="P78" s="3" t="inlineStr">
         <is>
-          <t>D+ 7.00</t>
+          <t>C- 17.00</t>
         </is>
       </c>
       <c r="Q78" s="3" t="inlineStr">
@@ -18445,7 +18467,7 @@
       </c>
       <c r="P79" s="3" t="inlineStr">
         <is>
-          <t>D+ 5.91</t>
+          <t>D+ 7.36</t>
         </is>
       </c>
       <c r="Q79" s="3" t="inlineStr">
@@ -18679,7 +18701,7 @@
       </c>
       <c r="P80" s="3" t="inlineStr">
         <is>
-          <t>C- 18.25</t>
+          <t>C+ 32.00</t>
         </is>
       </c>
       <c r="Q80" s="3" t="inlineStr">
@@ -18917,7 +18939,7 @@
       </c>
       <c r="P81" s="3" t="inlineStr">
         <is>
-          <t>C- 17.36</t>
+          <t>C- 17.52</t>
         </is>
       </c>
       <c r="Q81" s="3" t="inlineStr">
@@ -19155,7 +19177,7 @@
       </c>
       <c r="P82" s="3" t="inlineStr">
         <is>
-          <t>C- 14.63</t>
+          <t>C- 15.75</t>
         </is>
       </c>
       <c r="Q82" s="3" t="inlineStr">
@@ -19393,7 +19415,7 @@
       </c>
       <c r="P83" s="3" t="inlineStr">
         <is>
-          <t>D 5.00</t>
+          <t>C 26.25</t>
         </is>
       </c>
       <c r="Q83" s="3" t="inlineStr">
@@ -19631,7 +19653,7 @@
       </c>
       <c r="P84" s="3" t="inlineStr">
         <is>
-          <t>D- 2.50</t>
+          <t>D+ 6.50</t>
         </is>
       </c>
       <c r="Q84" s="3" t="inlineStr">
@@ -19861,7 +19883,7 @@
       </c>
       <c r="P85" s="3" t="inlineStr">
         <is>
-          <t>D+ 6.85</t>
+          <t>C- 14.37</t>
         </is>
       </c>
       <c r="Q85" s="3" t="inlineStr">
@@ -20095,7 +20117,7 @@
       </c>
       <c r="P86" s="3" t="inlineStr">
         <is>
-          <t>C- 24.30</t>
+          <t>C- 22.46</t>
         </is>
       </c>
       <c r="Q86" s="3" t="inlineStr">
@@ -20333,7 +20355,7 @@
       </c>
       <c r="P87" s="3" t="inlineStr">
         <is>
-          <t>C- 24.01</t>
+          <t>C- 24.16</t>
         </is>
       </c>
       <c r="Q87" s="3" t="inlineStr">
@@ -20567,7 +20589,7 @@
       </c>
       <c r="P88" s="3" t="inlineStr">
         <is>
-          <t>C- 20.65</t>
+          <t>C- 23.76</t>
         </is>
       </c>
       <c r="Q88" s="3" t="inlineStr">
@@ -20805,7 +20827,7 @@
       </c>
       <c r="P89" s="3" t="inlineStr">
         <is>
-          <t>C+ 32.13</t>
+          <t>C+ 33.90</t>
         </is>
       </c>
       <c r="Q89" s="3" t="inlineStr">
@@ -21037,7 +21059,7 @@
       </c>
       <c r="P90" s="3" t="inlineStr">
         <is>
-          <t>C- 19.25</t>
+          <t>C- 20.27</t>
         </is>
       </c>
       <c r="Q90" s="3" t="inlineStr">
@@ -21261,7 +21283,7 @@
       </c>
       <c r="N91" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5100/1.5000</t>
         </is>
       </c>
       <c r="O91" s="3" t="inlineStr">
@@ -21271,7 +21293,7 @@
       </c>
       <c r="P91" s="3" t="inlineStr">
         <is>
-          <t>C- 22.56</t>
+          <t>C- 24.55</t>
         </is>
       </c>
       <c r="Q91" s="3" t="inlineStr">
@@ -21505,7 +21527,7 @@
       </c>
       <c r="P92" s="3" t="inlineStr">
         <is>
-          <t>B- 36.05</t>
+          <t>C+ 32.62</t>
         </is>
       </c>
       <c r="Q92" s="3" t="inlineStr">
@@ -21739,7 +21761,7 @@
       </c>
       <c r="P93" s="3" t="inlineStr">
         <is>
-          <t>B- 46.48</t>
+          <t>B- 44.25</t>
         </is>
       </c>
       <c r="Q93" s="3" t="inlineStr">
@@ -21967,7 +21989,7 @@
       </c>
       <c r="N94" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/2.7000</t>
         </is>
       </c>
       <c r="O94" s="3" t="inlineStr">
@@ -21977,7 +21999,7 @@
       </c>
       <c r="P94" s="3" t="inlineStr">
         <is>
-          <t>D- 2.00</t>
+          <t>D- 2.60</t>
         </is>
       </c>
       <c r="Q94" s="3" t="inlineStr">
@@ -22207,7 +22229,7 @@
       </c>
       <c r="P95" s="3" t="inlineStr">
         <is>
-          <t>C- 23.75</t>
+          <t>C 25.20</t>
         </is>
       </c>
       <c r="Q95" s="3" t="inlineStr">
@@ -22443,7 +22465,7 @@
       </c>
       <c r="P96" s="3" t="inlineStr">
         <is>
-          <t>C+ 31.95</t>
+          <t>B- 37.20</t>
         </is>
       </c>
       <c r="Q96" s="3" t="inlineStr">
@@ -22675,7 +22697,7 @@
       </c>
       <c r="P97" s="3" t="inlineStr">
         <is>
-          <t>C+ 31.95</t>
+          <t>B- 37.20</t>
         </is>
       </c>
       <c r="Q97" s="3" t="inlineStr">
@@ -22897,7 +22919,7 @@
       </c>
       <c r="N98" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6900/--</t>
         </is>
       </c>
       <c r="O98" s="3" t="inlineStr">
@@ -22907,7 +22929,7 @@
       </c>
       <c r="P98" s="3" t="inlineStr">
         <is>
-          <t>C- 22.39</t>
+          <t>C- 24.39</t>
         </is>
       </c>
       <c r="Q98" s="3" t="inlineStr">
@@ -23133,7 +23155,7 @@
       </c>
       <c r="N99" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.9600/--</t>
         </is>
       </c>
       <c r="O99" s="3" t="inlineStr">
@@ -23143,7 +23165,7 @@
       </c>
       <c r="P99" s="3" t="inlineStr">
         <is>
-          <t>C 26.14</t>
+          <t>C- 23.19</t>
         </is>
       </c>
       <c r="Q99" s="3" t="inlineStr">

--- a/data/credit_bond_all_2026-08-25.xlsx
+++ b/data/credit_bond_all_2026-08-25.xlsx
@@ -15614,7 +15614,7 @@
     <row r="67" customHeight="true" ht="18.0">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>26虞交03</t>
+          <t>26锡科01</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -15624,64 +15624,64 @@
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>283772.SH</t>
+          <t>283757.SH</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E67" s="4" t="n">
-        <v>3.0</v>
+        <v>14.5</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>3.0</v>
+        <v>14.5</v>
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H67" s="4" t="n">
-        <v>1.96</v>
+        <v>1.79</v>
       </c>
       <c r="I67" s="4" t="n">
-        <v>57.28</v>
+        <v>53.67</v>
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>26虞交01</t>
+          <t>25临投01</t>
         </is>
       </c>
       <c r="L67" s="3" t="inlineStr">
         <is>
-          <t>2.66Y+2.00Y</t>
+          <t>3.49Y</t>
         </is>
       </c>
       <c r="M67" s="3" t="inlineStr">
         <is>
-          <t>1.7488</t>
+          <t>1.8118</t>
         </is>
       </c>
       <c r="N67" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.7600</t>
         </is>
       </c>
       <c r="O67" s="3" t="inlineStr">
         <is>
-          <t>绍兴上虞交通集团有限公司</t>
+          <t>无锡锡东科技投资控股有限公司</t>
         </is>
       </c>
       <c r="P67" s="3" t="inlineStr">
         <is>
-          <t>C+ 31.25</t>
+          <t>E 0.00</t>
         </is>
       </c>
       <c r="Q67" s="3" t="inlineStr">
@@ -15691,7 +15691,7 @@
       </c>
       <c r="R67" s="3" t="inlineStr">
         <is>
-          <t>08-25 16:00</t>
+          <t>08-25 15:00</t>
         </is>
       </c>
       <c r="S67" s="3" t="inlineStr">
@@ -15701,21 +15701,21 @@
       </c>
       <c r="T67" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="U67" s="4" t="n">
-        <v>2.77</v>
+        <v>4.48</v>
       </c>
       <c r="V67" s="3"/>
       <c r="W67" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X67" s="3" t="inlineStr">
         <is>
-          <t>1.82%~1.92%</t>
+          <t>1.77%~1.87%</t>
         </is>
       </c>
       <c r="Y67" s="3" t="inlineStr">
@@ -15726,17 +15726,17 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3" t="inlineStr">
         <is>
-          <t>浙江省-绍兴市</t>
+          <t>江苏省-无锡市</t>
         </is>
       </c>
       <c r="AB67" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟将3亿元用于偿还到期公司债券本金[23虞交02]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟将14.50亿元全部用于偿还到期公司债券本金[23锡东02]</t>
         </is>
       </c>
       <c r="AC67" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,天风证券股份有限公司</t>
+          <t>东吴证券股份有限公司,兴业证券股份有限公司,国信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD67" s="3"/>
@@ -15757,7 +15757,7 @@
       </c>
       <c r="AH67" s="3" t="inlineStr">
         <is>
-          <t>绍兴上虞交通集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>无锡锡东科技投资控股有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI67" s="3" t="inlineStr">
@@ -15767,13 +15767,13 @@
       </c>
       <c r="AJ67" s="3" t="inlineStr">
         <is>
-          <t>2031-08-26</t>
+          <t>2029-08-27</t>
         </is>
       </c>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t/>
         </is>
       </c>
       <c r="AM67" s="3" t="inlineStr">
@@ -15783,17 +15783,17 @@
       </c>
       <c r="AN67" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AO67" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP67" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>7*无效</t>
         </is>
       </c>
       <c r="AQ67" s="3" t="inlineStr">
@@ -15803,12 +15803,12 @@
       </c>
       <c r="AR67" s="3" t="inlineStr">
         <is>
-          <t>其他交运基础设施</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS67" s="3" t="inlineStr">
         <is>
-          <t>其他交运基础设施</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT67" s="3" t="inlineStr">
@@ -15846,7 +15846,7 @@
     <row r="68" customHeight="true" ht="18.0">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>26锡科01</t>
+          <t>26济建01(取消发行)</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -15856,64 +15856,58 @@
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>283757.SH</t>
+          <t>DY283677.SH</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E68" s="4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="F68" s="4" t="n">
-        <v>14.5</v>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="F68" s="3"/>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
-        </is>
-      </c>
-      <c r="H68" s="4" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="I68" s="4" t="n">
-        <v>53.67</v>
-      </c>
+          <t>1.40 ~ 2.40</t>
+        </is>
+      </c>
+      <c r="H68" s="3"/>
+      <c r="I68" s="3"/>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>--</t>
         </is>
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>25临投01</t>
+          <t>24济南城建PPN001</t>
         </is>
       </c>
       <c r="L68" s="3" t="inlineStr">
         <is>
-          <t>3.49Y</t>
+          <t>2.92Y</t>
         </is>
       </c>
       <c r="M68" s="3" t="inlineStr">
         <is>
-          <t>1.8118</t>
+          <t>1.7508</t>
         </is>
       </c>
       <c r="N68" s="3" t="inlineStr">
         <is>
-          <t>--/1.7600</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O68" s="3" t="inlineStr">
         <is>
-          <t>无锡锡东科技投资控股有限公司</t>
+          <t>济南城市建设集团有限公司</t>
         </is>
       </c>
       <c r="P68" s="3" t="inlineStr">
         <is>
-          <t>E 0.00</t>
+          <t>C 26.06</t>
         </is>
       </c>
       <c r="Q68" s="3" t="inlineStr">
@@ -15936,39 +15930,37 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="U68" s="4" t="n">
-        <v>4.48</v>
-      </c>
+      <c r="U68" s="3"/>
       <c r="V68" s="3"/>
       <c r="W68" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X68" s="3" t="inlineStr">
         <is>
-          <t>1.77%~1.87%</t>
+          <t>1.86%~1.96%</t>
         </is>
       </c>
       <c r="Y68" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z68" s="3"/>
       <c r="AA68" s="3" t="inlineStr">
         <is>
-          <t>江苏省-无锡市</t>
+          <t>山东省-济南市</t>
         </is>
       </c>
       <c r="AB68" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟将14.50亿元全部用于偿还到期公司债券本金[23锡东02]</t>
+          <t>本期债券发行规模为不超过人民币5亿元(含5亿元),全部用于偿还公司债券本金[23济建04]</t>
         </is>
       </c>
       <c r="AC68" s="3" t="inlineStr">
         <is>
-          <t>东吴证券股份有限公司,兴业证券股份有限公司,国信证券股份有限公司</t>
+          <t>国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD68" s="3"/>
@@ -15989,7 +15981,7 @@
       </c>
       <c r="AH68" s="3" t="inlineStr">
         <is>
-          <t>无锡锡东科技投资控股有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>济南城市建设集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种一)(取消发行)</t>
         </is>
       </c>
       <c r="AI68" s="3" t="inlineStr">
@@ -15999,7 +15991,7 @@
       </c>
       <c r="AJ68" s="3" t="inlineStr">
         <is>
-          <t>2029-08-27</t>
+          <t>2031-08-27</t>
         </is>
       </c>
       <c r="AK68" s="3"/>
@@ -16020,27 +16012,27 @@
       </c>
       <c r="AO68" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP68" s="3" t="inlineStr">
         <is>
-          <t>7*无效</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ68" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR68" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS68" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT68" s="3" t="inlineStr">
@@ -16078,92 +16070,102 @@
     <row r="69" customHeight="true" ht="18.0">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>26济建01(取消发行)</t>
+          <t>26福州地铁SCP003</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>08-25 19:00</t>
+          <t>08-25 18:00</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>DY283677.SH</t>
+          <t>012682152.IB</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E69" s="4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F69" s="3"/>
+        <v>9.0</v>
+      </c>
+      <c r="F69" s="4" t="n">
+        <v>9.0</v>
+      </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
-        </is>
-      </c>
-      <c r="H69" s="3"/>
-      <c r="I69" s="3"/>
+          <t>1.20 ~ 1.70</t>
+        </is>
+      </c>
+      <c r="H69" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I69" s="4" t="n">
+        <v>36.44</v>
+      </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="K69" s="3" t="inlineStr">
+        <is>
+          <t>26福州地铁SCP002</t>
+        </is>
+      </c>
+      <c r="L69" s="3" t="inlineStr">
+        <is>
+          <t>200D</t>
+        </is>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>1.5118</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="inlineStr">
+        <is>
+          <t>--/1.5100</t>
+        </is>
+      </c>
+      <c r="O69" s="3" t="inlineStr">
+        <is>
+          <t>福州地铁集团有限公司</t>
+        </is>
+      </c>
+      <c r="P69" s="3" t="inlineStr">
+        <is>
+          <t>C 25.47</t>
+        </is>
+      </c>
+      <c r="Q69" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="R69" s="3" t="inlineStr">
+        <is>
+          <t>08-25 09:00</t>
+        </is>
+      </c>
+      <c r="S69" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K69" s="3" t="inlineStr">
-        <is>
-          <t>24济南城建PPN001</t>
-        </is>
-      </c>
-      <c r="L69" s="3" t="inlineStr">
-        <is>
-          <t>2.92Y</t>
-        </is>
-      </c>
-      <c r="M69" s="3" t="inlineStr">
-        <is>
-          <t>1.7508</t>
-        </is>
-      </c>
-      <c r="N69" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O69" s="3" t="inlineStr">
-        <is>
-          <t>济南城市建设集团有限公司</t>
-        </is>
-      </c>
-      <c r="P69" s="3" t="inlineStr">
-        <is>
-          <t>C 26.06</t>
-        </is>
-      </c>
-      <c r="Q69" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="R69" s="3" t="inlineStr">
-        <is>
-          <t>08-25 15:00</t>
-        </is>
-      </c>
-      <c r="S69" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T69" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="U69" s="3"/>
-      <c r="V69" s="3"/>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="U69" s="4" t="n">
+        <v>4.1889</v>
+      </c>
+      <c r="V69" s="4" t="n">
+        <v>4.6</v>
+      </c>
       <c r="W69" s="3" t="inlineStr">
         <is>
           <t>4+</t>
@@ -16171,7 +16173,7 @@
       </c>
       <c r="X69" s="3" t="inlineStr">
         <is>
-          <t>1.86%~1.96%</t>
+          <t>1.45%~1.49%</t>
         </is>
       </c>
       <c r="Y69" s="3" t="inlineStr">
@@ -16182,23 +16184,23 @@
       <c r="Z69" s="3"/>
       <c r="AA69" s="3" t="inlineStr">
         <is>
-          <t>山东省-济南市</t>
+          <t>福建省-福州市</t>
         </is>
       </c>
       <c r="AB69" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模为不超过人民币5亿元(含5亿元),全部用于偿还公司债券本金[23济建04]</t>
+          <t>本期超短期融资券募集资金9.00亿元,期限270天,拟用于归还到期债券。[25福州地铁SCP005]</t>
         </is>
       </c>
       <c r="AC69" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司</t>
+          <t>中信银行股份有限公司,中国建设银行股份有限公司</t>
         </is>
       </c>
       <c r="AD69" s="3"/>
       <c r="AE69" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF69" s="3" t="inlineStr">
@@ -16208,28 +16210,32 @@
       </c>
       <c r="AG69" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH69" s="3" t="inlineStr">
         <is>
-          <t>济南城市建设集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种一)(取消发行)</t>
+          <t>福州地铁集团有限公司2026年度第三期超短期融资券</t>
         </is>
       </c>
       <c r="AI69" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ69" s="3" t="inlineStr">
         <is>
-          <t>2031-08-27</t>
-        </is>
-      </c>
-      <c r="AK69" s="3"/>
+          <t>2027-05-23</t>
+        </is>
+      </c>
+      <c r="AK69" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL69" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AM69" s="3" t="inlineStr">
@@ -16239,37 +16245,37 @@
       </c>
       <c r="AN69" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="AO69" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP69" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ69" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR69" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AS69" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AT69" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>公交</t>
         </is>
       </c>
       <c r="AU69" s="3" t="inlineStr">
@@ -16302,7 +16308,7 @@
     <row r="70" customHeight="true" ht="18.0">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>26福州地铁SCP003</t>
+          <t>26常山集团PPN001</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -16312,64 +16318,64 @@
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>012682152.IB</t>
+          <t>032680255.IB</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E70" s="4" t="n">
-        <v>9.0</v>
+        <v>5.0</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>9.0</v>
+        <v>5.0</v>
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 1.70</t>
+          <t>1.80 ~ 2.80</t>
         </is>
       </c>
       <c r="H70" s="4" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="I70" s="4" t="n">
-        <v>36.44</v>
+        <v>96.39</v>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>26福州地铁SCP002</t>
+          <t>25常山K2</t>
         </is>
       </c>
       <c r="L70" s="3" t="inlineStr">
         <is>
-          <t>200D</t>
+          <t>2.15Y+2.00Y</t>
         </is>
       </c>
       <c r="M70" s="3" t="inlineStr">
         <is>
-          <t>1.5118</t>
+          <t>2.3546</t>
         </is>
       </c>
       <c r="N70" s="3" t="inlineStr">
         <is>
-          <t>--/1.5100</t>
+          <t>2.3000/--</t>
         </is>
       </c>
       <c r="O70" s="3" t="inlineStr">
         <is>
-          <t>福州地铁集团有限公司</t>
+          <t>石家庄常山纺织集团有限责任公司</t>
         </is>
       </c>
       <c r="P70" s="3" t="inlineStr">
         <is>
-          <t>C 25.47</t>
+          <t>A- 65.71</t>
         </is>
       </c>
       <c r="Q70" s="3" t="inlineStr">
@@ -16379,7 +16385,7 @@
       </c>
       <c r="R70" s="3" t="inlineStr">
         <is>
-          <t>08-25 09:00</t>
+          <t>08-25 15:00</t>
         </is>
       </c>
       <c r="S70" s="3" t="inlineStr">
@@ -16392,47 +16398,43 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="U70" s="4" t="n">
-        <v>4.1889</v>
-      </c>
-      <c r="V70" s="4" t="n">
-        <v>4.6</v>
-      </c>
+      <c r="U70" s="3"/>
+      <c r="V70" s="3"/>
       <c r="W70" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X70" s="3" t="inlineStr">
         <is>
-          <t>1.45%~1.49%</t>
+          <t>2.50%~2.60%</t>
         </is>
       </c>
       <c r="Y70" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z70" s="3"/>
       <c r="AA70" s="3" t="inlineStr">
         <is>
-          <t>福建省-福州市</t>
+          <t>河北省-石家庄市</t>
         </is>
       </c>
       <c r="AB70" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券募集资金9.00亿元,期限270天,拟用于归还到期债券。[25福州地铁SCP005]</t>
+          <t>发行人本期定向债务融资工具发行规模为5.00亿元,扣除承销费用后拟全部用于偿还发行人及其子公司有息债务</t>
         </is>
       </c>
       <c r="AC70" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,中国建设银行股份有限公司</t>
+          <t>国泰海通证券股份有限公司,中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD70" s="3"/>
       <c r="AE70" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF70" s="3" t="inlineStr">
@@ -16447,22 +16449,22 @@
       </c>
       <c r="AH70" s="3" t="inlineStr">
         <is>
-          <t>福州地铁集团有限公司2026年度第三期超短期融资券</t>
+          <t>石家庄常山纺织集团有限责任公司2026年度第一期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI70" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ70" s="3" t="inlineStr">
         <is>
-          <t>2027-05-23</t>
+          <t>2028-08-26</t>
         </is>
       </c>
       <c r="AK70" s="3" t="inlineStr">
         <is>
-          <t>休1</t>
+          <t>休2</t>
         </is>
       </c>
       <c r="AL70" s="3" t="inlineStr">
@@ -16482,32 +16484,28 @@
       </c>
       <c r="AO70" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP70" s="3" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP70" s="3"/>
       <c r="AQ70" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR70" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>产业集团</t>
         </is>
       </c>
       <c r="AS70" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>产业集团</t>
         </is>
       </c>
       <c r="AT70" s="3" t="inlineStr">
         <is>
-          <t>公交</t>
+          <t>计算机应用</t>
         </is>
       </c>
       <c r="AU70" s="3" t="inlineStr">
@@ -16540,7 +16538,7 @@
     <row r="71" customHeight="true" ht="18.0">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>26常山集团PPN001</t>
+          <t>26宿迁高新MTN001</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -16550,64 +16548,64 @@
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>032680255.IB</t>
+          <t>102683333.IB</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E71" s="4" t="n">
-        <v>5.0</v>
+        <v>3.81</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>5.0</v>
+        <v>3.81</v>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.80</t>
+          <t>1.60 ~ 2.50</t>
         </is>
       </c>
       <c r="H71" s="4" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="I71" s="4" t="n">
-        <v>96.39</v>
+        <v>46.28</v>
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>25常山K2</t>
+          <t>24宿迁高新PPN001</t>
         </is>
       </c>
       <c r="L71" s="3" t="inlineStr">
         <is>
-          <t>2.15Y+2.00Y</t>
+          <t>307D</t>
         </is>
       </c>
       <c r="M71" s="3" t="inlineStr">
         <is>
-          <t>2.3546</t>
+          <t>1.7413</t>
         </is>
       </c>
       <c r="N71" s="3" t="inlineStr">
         <is>
-          <t>2.3000/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O71" s="3" t="inlineStr">
         <is>
-          <t>石家庄常山纺织集团有限责任公司</t>
+          <t>宿迁高新开发投资有限公司</t>
         </is>
       </c>
       <c r="P71" s="3" t="inlineStr">
         <is>
-          <t>A- 65.71</t>
+          <t>C 29.94</t>
         </is>
       </c>
       <c r="Q71" s="3" t="inlineStr">
@@ -16617,7 +16615,7 @@
       </c>
       <c r="R71" s="3" t="inlineStr">
         <is>
-          <t>08-25 15:00</t>
+          <t>08-25 09:00</t>
         </is>
       </c>
       <c r="S71" s="3" t="inlineStr">
@@ -16630,43 +16628,47 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="U71" s="3"/>
-      <c r="V71" s="3"/>
+      <c r="U71" s="4" t="n">
+        <v>2.2415</v>
+      </c>
+      <c r="V71" s="4" t="n">
+        <v>3.33</v>
+      </c>
       <c r="W71" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X71" s="3" t="inlineStr">
         <is>
-          <t>2.50%~2.60%</t>
+          <t>1.90%~2.00%</t>
         </is>
       </c>
       <c r="Y71" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z71" s="3"/>
       <c r="AA71" s="3" t="inlineStr">
         <is>
-          <t>河北省-石家庄市</t>
+          <t>江苏省-宿迁市</t>
         </is>
       </c>
       <c r="AB71" s="3" t="inlineStr">
         <is>
-          <t>发行人本期定向债务融资工具发行规模为5.00亿元,扣除承销费用后拟全部用于偿还发行人及其子公司有息债务</t>
+          <t>本次中期票据注册金额3.81亿元,本期发行金额3.81亿元,全部用于偿还发行人存量债务融资工具[21宿迁高新MTN001]</t>
         </is>
       </c>
       <c r="AC71" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,中信银行股份有限公司</t>
+          <t>南京银行股份有限公司</t>
         </is>
       </c>
       <c r="AD71" s="3"/>
       <c r="AE71" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF71" s="3" t="inlineStr">
@@ -16681,24 +16683,20 @@
       </c>
       <c r="AH71" s="3" t="inlineStr">
         <is>
-          <t>石家庄常山纺织集团有限责任公司2026年度第一期定向债务融资工具</t>
+          <t>宿迁高新开发投资有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI71" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ71" s="3" t="inlineStr">
         <is>
-          <t>2028-08-26</t>
-        </is>
-      </c>
-      <c r="AK71" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2031-08-26</t>
+        </is>
+      </c>
+      <c r="AK71" s="3"/>
       <c r="AL71" s="3" t="inlineStr">
         <is>
           <t>2026-08-27</t>
@@ -16716,33 +16714,37 @@
       </c>
       <c r="AO71" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP71" s="3"/>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP71" s="3" t="inlineStr">
+        <is>
+          <t>6.5*无效</t>
+        </is>
+      </c>
       <c r="AQ71" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR71" s="3" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS71" s="3" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT71" s="3" t="inlineStr">
         <is>
-          <t>计算机应用</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU71" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-08-26</t>
         </is>
       </c>
       <c r="AV71" s="3" t="inlineStr">
@@ -16752,7 +16754,7 @@
       </c>
       <c r="AW71" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX71" s="3" t="inlineStr">
@@ -16770,7 +16772,7 @@
     <row r="72" customHeight="true" ht="18.0">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>26宿迁高新MTN001</t>
+          <t>26之江城投PPN001A</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -16780,7 +16782,7 @@
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>102683333.IB</t>
+          <t>032680490.IB</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
@@ -16789,55 +16791,55 @@
         </is>
       </c>
       <c r="E72" s="4" t="n">
-        <v>3.81</v>
+        <v>5.0</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>3.81</v>
+        <v>5.0</v>
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.50</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H72" s="4" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="I72" s="4" t="n">
-        <v>46.28</v>
+        <v>36.28</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>24宿迁高新PPN001</t>
+          <t>24之江03</t>
         </is>
       </c>
       <c r="L72" s="3" t="inlineStr">
         <is>
-          <t>307D</t>
+          <t>2.82Y</t>
         </is>
       </c>
       <c r="M72" s="3" t="inlineStr">
         <is>
-          <t>1.7413</t>
+          <t>1.6945</t>
         </is>
       </c>
       <c r="N72" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.7500</t>
         </is>
       </c>
       <c r="O72" s="3" t="inlineStr">
         <is>
-          <t>宿迁高新开发投资有限公司</t>
+          <t>杭州之江城市建设投资集团有限公司</t>
         </is>
       </c>
       <c r="P72" s="3" t="inlineStr">
         <is>
-          <t>C 29.94</t>
+          <t>B- 40.14</t>
         </is>
       </c>
       <c r="Q72" s="3" t="inlineStr">
@@ -16847,7 +16849,7 @@
       </c>
       <c r="R72" s="3" t="inlineStr">
         <is>
-          <t>08-25 09:00</t>
+          <t>08-25 15:00</t>
         </is>
       </c>
       <c r="S72" s="3" t="inlineStr">
@@ -16861,46 +16863,46 @@
         </is>
       </c>
       <c r="U72" s="4" t="n">
-        <v>2.2415</v>
+        <v>4.56</v>
       </c>
       <c r="V72" s="4" t="n">
-        <v>3.33</v>
+        <v>11.5</v>
       </c>
       <c r="W72" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X72" s="3" t="inlineStr">
         <is>
-          <t>1.90%~2.00%</t>
+          <t>1.72%~1.82%</t>
         </is>
       </c>
       <c r="Y72" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z72" s="3"/>
       <c r="AA72" s="3" t="inlineStr">
         <is>
-          <t>江苏省-宿迁市</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB72" s="3" t="inlineStr">
         <is>
-          <t>本次中期票据注册金额3.81亿元,本期发行金额3.81亿元,全部用于偿还发行人存量债务融资工具[21宿迁高新MTN001]</t>
+          <t>发行人本期债务融资工具注册金额为10.00亿元,均用于偿还“21之江城投PPN001”的债务融资工具本金[21之江城投PPN001]</t>
         </is>
       </c>
       <c r="AC72" s="3" t="inlineStr">
         <is>
-          <t>南京银行股份有限公司</t>
+          <t>中信建投证券股份有限公司,国泰海通证券股份有限公司,东方证券股份有限公司</t>
         </is>
       </c>
       <c r="AD72" s="3"/>
       <c r="AE72" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF72" s="3" t="inlineStr">
@@ -16915,12 +16917,12 @@
       </c>
       <c r="AH72" s="3" t="inlineStr">
         <is>
-          <t>宿迁高新开发投资有限公司2026年度第一期中期票据</t>
+          <t>杭州之江城市建设投资集团有限公司2026年度第一期定向债务融资工具(品种一)</t>
         </is>
       </c>
       <c r="AI72" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ72" s="3" t="inlineStr">
@@ -16946,12 +16948,12 @@
       </c>
       <c r="AO72" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP72" s="3" t="inlineStr">
         <is>
-          <t>6.5*无效</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ72" s="3" t="inlineStr">
@@ -16961,12 +16963,12 @@
       </c>
       <c r="AR72" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>其他基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS72" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>其他基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT72" s="3" t="inlineStr">
@@ -17004,7 +17006,7 @@
     <row r="73" customHeight="true" ht="18.0">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>26之江城投PPN001A</t>
+          <t>26吉林高速MTN007</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -17014,7 +17016,7 @@
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>032680490.IB</t>
+          <t>102683337.IB</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
@@ -17023,55 +17025,55 @@
         </is>
       </c>
       <c r="E73" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.50 ~ 1.90</t>
         </is>
       </c>
       <c r="H73" s="4" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="I73" s="4" t="n">
-        <v>36.28</v>
+        <v>33.28</v>
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>24之江03</t>
+          <t>26吉林高速MTN006</t>
         </is>
       </c>
       <c r="L73" s="3" t="inlineStr">
         <is>
-          <t>2.82Y</t>
+          <t>2.98Y+2.00Y</t>
         </is>
       </c>
       <c r="M73" s="3" t="inlineStr">
         <is>
-          <t>1.6945</t>
+          <t>1.7744</t>
         </is>
       </c>
       <c r="N73" s="3" t="inlineStr">
         <is>
-          <t>--/1.7500</t>
+          <t>1.7500/1.7400</t>
         </is>
       </c>
       <c r="O73" s="3" t="inlineStr">
         <is>
-          <t>杭州之江城市建设投资集团有限公司</t>
+          <t>吉林省高速公路集团有限公司</t>
         </is>
       </c>
       <c r="P73" s="3" t="inlineStr">
         <is>
-          <t>B- 40.14</t>
+          <t>B- 49.82</t>
         </is>
       </c>
       <c r="Q73" s="3" t="inlineStr">
@@ -17081,7 +17083,7 @@
       </c>
       <c r="R73" s="3" t="inlineStr">
         <is>
-          <t>08-25 15:00</t>
+          <t>08-25 09:00</t>
         </is>
       </c>
       <c r="S73" s="3" t="inlineStr">
@@ -17095,19 +17097,19 @@
         </is>
       </c>
       <c r="U73" s="4" t="n">
-        <v>4.56</v>
+        <v>4.78</v>
       </c>
       <c r="V73" s="4" t="n">
-        <v>11.5</v>
+        <v>1.6</v>
       </c>
       <c r="W73" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X73" s="3" t="inlineStr">
         <is>
-          <t>1.72%~1.82%</t>
+          <t>1.70%~1.80%</t>
         </is>
       </c>
       <c r="Y73" s="3" t="inlineStr">
@@ -17115,26 +17117,30 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z73" s="3"/>
+      <c r="Z73" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA73" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
+          <t>吉林省</t>
         </is>
       </c>
       <c r="AB73" s="3" t="inlineStr">
         <is>
-          <t>发行人本期债务融资工具注册金额为10.00亿元,均用于偿还“21之江城投PPN001”的债务融资工具本金[21之江城投PPN001]</t>
+          <t>本期中期票据基础发行规模为0亿元，发行金额上限为10亿元，拟全部用于偿还发行人有息债务本息。</t>
         </is>
       </c>
       <c r="AC73" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,国泰海通证券股份有限公司,东方证券股份有限公司</t>
+          <t>华夏银行股份有限公司,上海浦东发展银行股份有限公司</t>
         </is>
       </c>
       <c r="AD73" s="3"/>
       <c r="AE73" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF73" s="3" t="inlineStr">
@@ -17149,12 +17155,12 @@
       </c>
       <c r="AH73" s="3" t="inlineStr">
         <is>
-          <t>杭州之江城市建设投资集团有限公司2026年度第一期定向债务融资工具(品种一)</t>
+          <t>吉林省高速公路集团有限公司2026年度第七期中期票据</t>
         </is>
       </c>
       <c r="AI73" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ73" s="3" t="inlineStr">
@@ -17180,12 +17186,12 @@
       </c>
       <c r="AO73" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP73" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ73" s="3" t="inlineStr">
@@ -17195,17 +17201,17 @@
       </c>
       <c r="AR73" s="3" t="inlineStr">
         <is>
-          <t>其他基础设施投融资建设</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AS73" s="3" t="inlineStr">
         <is>
-          <t>其他基础设施投融资建设</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AT73" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU73" s="3" t="inlineStr">
@@ -17238,7 +17244,7 @@
     <row r="74" customHeight="true" ht="18.0">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>26吉林高速MTN007</t>
+          <t>26桂林银行绿债01A</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -17248,64 +17254,64 @@
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>102683337.IB</t>
+          <t>222680017.IB</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E74" s="4" t="n">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.90</t>
+          <t>1.40 ~ 1.90</t>
         </is>
       </c>
       <c r="H74" s="4" t="n">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="I74" s="4" t="n">
-        <v>33.28</v>
+        <v>37.67</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>26吉林高速MTN006</t>
+          <t>25桂林银行绿色债02</t>
         </is>
       </c>
       <c r="L74" s="3" t="inlineStr">
         <is>
-          <t>2.98Y+2.00Y</t>
+          <t>2.23Y</t>
         </is>
       </c>
       <c r="M74" s="3" t="inlineStr">
         <is>
-          <t>1.7744</t>
+          <t>1.6141</t>
         </is>
       </c>
       <c r="N74" s="3" t="inlineStr">
         <is>
-          <t>1.7500/1.7400</t>
+          <t>--/1.6300</t>
         </is>
       </c>
       <c r="O74" s="3" t="inlineStr">
         <is>
-          <t>吉林省高速公路集团有限公司</t>
+          <t>桂林银行股份有限公司</t>
         </is>
       </c>
       <c r="P74" s="3" t="inlineStr">
         <is>
-          <t>B- 49.82</t>
+          <t>B- 45.60</t>
         </is>
       </c>
       <c r="Q74" s="3" t="inlineStr">
@@ -17325,15 +17331,11 @@
       </c>
       <c r="T74" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="U74" s="4" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="V74" s="4" t="n">
-        <v>1.6</v>
-      </c>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="U74" s="3"/>
+      <c r="V74" s="3"/>
       <c r="W74" s="3" t="inlineStr">
         <is>
           <t>5-</t>
@@ -17341,7 +17343,7 @@
       </c>
       <c r="X74" s="3" t="inlineStr">
         <is>
-          <t>1.70%~1.80%</t>
+          <t>1.69%~1.79%</t>
         </is>
       </c>
       <c r="Y74" s="3" t="inlineStr">
@@ -17356,23 +17358,23 @@
       </c>
       <c r="AA74" s="3" t="inlineStr">
         <is>
-          <t>吉林省</t>
+          <t>广西壮族自治区-桂林市</t>
         </is>
       </c>
       <c r="AB74" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据基础发行规模为0亿元，发行金额上限为10亿元，拟全部用于偿还发行人有息债务本息。</t>
+          <t>本期债券发行所募集资金将依据适用法律和监管部门的批准,用于投放《绿色金融支持项目目录(2025年版)》支持的绿色产业项目相关贷款,优先支持同时符合《生物多样性金融目录[试用稿]》的项目。</t>
         </is>
       </c>
       <c r="AC74" s="3" t="inlineStr">
         <is>
-          <t>华夏银行股份有限公司,上海浦东发展银行股份有限公司</t>
+          <t>中信证券股份有限公司,中国国际金融股份有限公司,国泰海通证券股份有限公司,中信建投证券股份有限公司,申万宏源证券有限公司,国开证券股份有限公司</t>
         </is>
       </c>
       <c r="AD74" s="3"/>
       <c r="AE74" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>商业银行普通债券</t>
         </is>
       </c>
       <c r="AF74" s="3" t="inlineStr">
@@ -17387,7 +17389,7 @@
       </c>
       <c r="AH74" s="3" t="inlineStr">
         <is>
-          <t>吉林省高速公路集团有限公司2026年度第七期中期票据</t>
+          <t>桂林银行股份有限公司2026年绿色金融债券(第一期)(品种一)</t>
         </is>
       </c>
       <c r="AI74" s="3" t="inlineStr">
@@ -17397,28 +17399,28 @@
       </c>
       <c r="AJ74" s="3" t="inlineStr">
         <is>
-          <t>2031-08-26</t>
+          <t>2029-08-27</t>
         </is>
       </c>
       <c r="AK74" s="3"/>
       <c r="AL74" s="3" t="inlineStr">
         <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AM74" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AN74" s="3" t="inlineStr">
+        <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="AM74" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="AN74" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
       <c r="AO74" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP74" s="3" t="inlineStr">
@@ -17428,27 +17430,27 @@
       </c>
       <c r="AQ74" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AR74" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AS74" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>城商行</t>
         </is>
       </c>
       <c r="AT74" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AU74" s="3" t="inlineStr">
         <is>
-          <t>2029-08-26</t>
+          <t/>
         </is>
       </c>
       <c r="AV74" s="3" t="inlineStr">
@@ -17458,7 +17460,7 @@
       </c>
       <c r="AW74" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX74" s="3" t="inlineStr">
@@ -17476,74 +17478,74 @@
     <row r="75" customHeight="true" ht="18.0">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>26桂林银行绿债01A</t>
+          <t>26蓉高04</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>08-25 18:00</t>
+          <t>08-25 19:00</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>222680017.IB</t>
+          <t>245886.SH</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5+5</t>
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.90</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H75" s="4" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="I75" s="4" t="n">
-        <v>37.67</v>
+        <v>6.85</v>
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>25桂林银行绿色债02</t>
+          <t>26蓉高03</t>
         </is>
       </c>
       <c r="L75" s="3" t="inlineStr">
         <is>
-          <t>2.23Y</t>
+          <t>4.91Y+5.00Y</t>
         </is>
       </c>
       <c r="M75" s="3" t="inlineStr">
         <is>
-          <t>1.6141</t>
+          <t>1.7882</t>
         </is>
       </c>
       <c r="N75" s="3" t="inlineStr">
         <is>
-          <t>--/1.6300</t>
+          <t>1.8300/--</t>
         </is>
       </c>
       <c r="O75" s="3" t="inlineStr">
         <is>
-          <t>桂林银行股份有限公司</t>
+          <t>成都高新投资集团有限公司</t>
         </is>
       </c>
       <c r="P75" s="3" t="inlineStr">
         <is>
-          <t>B- 45.60</t>
+          <t>B- 36.08</t>
         </is>
       </c>
       <c r="Q75" s="3" t="inlineStr">
@@ -17553,7 +17555,7 @@
       </c>
       <c r="R75" s="3" t="inlineStr">
         <is>
-          <t>08-25 09:00</t>
+          <t>08-25 15:00</t>
         </is>
       </c>
       <c r="S75" s="3" t="inlineStr">
@@ -17563,19 +17565,21 @@
       </c>
       <c r="T75" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="U75" s="3"/>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="U75" s="4" t="n">
+        <v>7.13</v>
+      </c>
       <c r="V75" s="3"/>
       <c r="W75" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X75" s="3" t="inlineStr">
         <is>
-          <t>1.69%~1.79%</t>
+          <t>1.75%~1.85%</t>
         </is>
       </c>
       <c r="Y75" s="3" t="inlineStr">
@@ -17583,30 +17587,26 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z75" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z75" s="3"/>
       <c r="AA75" s="3" t="inlineStr">
         <is>
-          <t>广西壮族自治区-桂林市</t>
+          <t>四川省-成都市</t>
         </is>
       </c>
       <c r="AB75" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行所募集资金将依据适用法律和监管部门的批准,用于投放《绿色金融支持项目目录(2025年版)》支持的绿色产业项目相关贷款,优先支持同时符合《生物多样性金融目录[试用稿]》的项目。</t>
+          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还回售的公司债券21蓉高03的本金。[21蓉高03]</t>
         </is>
       </c>
       <c r="AC75" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,中国国际金融股份有限公司,国泰海通证券股份有限公司,中信建投证券股份有限公司,申万宏源证券有限公司,国开证券股份有限公司</t>
+          <t>国泰海通证券股份有限公司,国投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD75" s="3"/>
       <c r="AE75" s="3" t="inlineStr">
         <is>
-          <t>商业银行普通债券</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF75" s="3" t="inlineStr">
@@ -17616,12 +17616,12 @@
       </c>
       <c r="AG75" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH75" s="3" t="inlineStr">
         <is>
-          <t>桂林银行股份有限公司2026年绿色金融债券(第一期)(品种一)</t>
+          <t>成都高新投资集团有限公司2026年面向专业投资者公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI75" s="3" t="inlineStr">
@@ -17631,58 +17631,58 @@
       </c>
       <c r="AJ75" s="3" t="inlineStr">
         <is>
-          <t>2029-08-27</t>
+          <t>2036-08-26</t>
         </is>
       </c>
       <c r="AK75" s="3"/>
       <c r="AL75" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AM75" s="3" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AN75" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="AO75" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP75" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.5*无效</t>
         </is>
       </c>
       <c r="AQ75" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR75" s="3" t="inlineStr">
         <is>
-          <t>商业银行</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS75" s="3" t="inlineStr">
         <is>
-          <t>城商行</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT75" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU75" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2031-08-26</t>
         </is>
       </c>
       <c r="AV75" s="3" t="inlineStr">
@@ -17692,7 +17692,7 @@
       </c>
       <c r="AW75" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX75" s="3" t="inlineStr">
@@ -17710,74 +17710,74 @@
     <row r="76" customHeight="true" ht="18.0">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>26蓉高04</t>
+          <t>26心连心MTN001(科创债)</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>08-25 19:00</t>
+          <t>08-25 18:00</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>245886.SH</t>
+          <t>102683346.IB</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>5+5</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E76" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="H76" s="4" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="I76" s="4" t="n">
-        <v>6.85</v>
+        <v>94.67</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>26蓉高03</t>
+          <t>24连云工投MTN001</t>
         </is>
       </c>
       <c r="L76" s="3" t="inlineStr">
         <is>
-          <t>4.91Y+5.00Y</t>
+          <t>3.09Y</t>
         </is>
       </c>
       <c r="M76" s="3" t="inlineStr">
         <is>
-          <t>1.7882</t>
+          <t>2.0090</t>
         </is>
       </c>
       <c r="N76" s="3" t="inlineStr">
         <is>
-          <t>1.8300/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O76" s="3" t="inlineStr">
         <is>
-          <t>成都高新投资集团有限公司</t>
+          <t>河南心连心化学工业集团股份有限公司</t>
         </is>
       </c>
       <c r="P76" s="3" t="inlineStr">
         <is>
-          <t>B- 36.08</t>
+          <t>C 30.00</t>
         </is>
       </c>
       <c r="Q76" s="3" t="inlineStr">
@@ -17801,59 +17801,55 @@
         </is>
       </c>
       <c r="U76" s="4" t="n">
-        <v>7.13</v>
+        <v>1.42</v>
       </c>
       <c r="V76" s="3"/>
       <c r="W76" s="3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X76" s="3" t="inlineStr">
-        <is>
-          <t>1.75%~1.85%</t>
-        </is>
-      </c>
+          <t>6-</t>
+        </is>
+      </c>
+      <c r="X76" s="3"/>
       <c r="Y76" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z76" s="3"/>
       <c r="AA76" s="3" t="inlineStr">
         <is>
-          <t>四川省-成都市</t>
+          <t>河南省-新乡市</t>
         </is>
       </c>
       <c r="AB76" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还回售的公司债券21蓉高03的本金。[21蓉高03]</t>
+          <t>发行人本期中期票据发行金额5亿元,本次发行扣除发行费用后,募集资金拟全部用于偿还发行人本部及合并范围内下属子公司的存量有息债务</t>
         </is>
       </c>
       <c r="AC76" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,国投证券股份有限公司</t>
+          <t>国泰海通证券股份有限公司,渤海银行股份有限公司,交通银行股份有限公司,中国民生银行股份有限公司,中国工商银行股份有限公司,招商银行股份有限公司,华夏银行股份有限公司,中国建设银行股份有限公司</t>
         </is>
       </c>
       <c r="AD76" s="3"/>
       <c r="AE76" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF76" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG76" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH76" s="3" t="inlineStr">
         <is>
-          <t>成都高新投资集团有限公司2026年面向专业投资者公开发行公司债券(第三期)</t>
+          <t>河南心连心化学工业集团股份有限公司2026年度第一期科技创新债券(乡村振兴)</t>
         </is>
       </c>
       <c r="AI76" s="3" t="inlineStr">
@@ -17863,13 +17859,17 @@
       </c>
       <c r="AJ76" s="3" t="inlineStr">
         <is>
-          <t>2036-08-26</t>
-        </is>
-      </c>
-      <c r="AK76" s="3"/>
+          <t>2029-08-26</t>
+        </is>
+      </c>
+      <c r="AK76" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL76" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AM76" s="3" t="inlineStr">
@@ -17887,34 +17887,30 @@
           <t>产业</t>
         </is>
       </c>
-      <c r="AP76" s="3" t="inlineStr">
-        <is>
-          <t>6.5*无效</t>
-        </is>
-      </c>
+      <c r="AP76" s="3"/>
       <c r="AQ76" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>化工制造</t>
         </is>
       </c>
       <c r="AR76" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>化学制品</t>
         </is>
       </c>
       <c r="AS76" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>化学制品</t>
         </is>
       </c>
       <c r="AT76" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>化学制品</t>
         </is>
       </c>
       <c r="AU76" s="3" t="inlineStr">
         <is>
-          <t>2031-08-26</t>
+          <t/>
         </is>
       </c>
       <c r="AV76" s="3" t="inlineStr">
@@ -17924,7 +17920,7 @@
       </c>
       <c r="AW76" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX76" s="3" t="inlineStr">
@@ -17942,7 +17938,7 @@
     <row r="77" customHeight="true" ht="18.0">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>26心连心MTN001(科创债)</t>
+          <t>26新疆城建CP002</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -17952,49 +17948,49 @@
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>102683346.IB</t>
+          <t>042680299.IB</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>1Y</t>
         </is>
       </c>
       <c r="E77" s="4" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.70 ~ 2.70</t>
         </is>
       </c>
       <c r="H77" s="4" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="I77" s="4" t="n">
-        <v>94.67</v>
+        <v>54.7</v>
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>24连云工投MTN001</t>
+          <t>26新疆城建CP001</t>
         </is>
       </c>
       <c r="L77" s="3" t="inlineStr">
         <is>
-          <t>3.09Y</t>
+          <t>319D</t>
         </is>
       </c>
       <c r="M77" s="3" t="inlineStr">
         <is>
-          <t>2.0090</t>
+          <t>1.7946</t>
         </is>
       </c>
       <c r="N77" s="3" t="inlineStr">
@@ -18004,12 +18000,12 @@
       </c>
       <c r="O77" s="3" t="inlineStr">
         <is>
-          <t>河南心连心化学工业集团股份有限公司</t>
+          <t>新疆城建(集团)股份有限公司</t>
         </is>
       </c>
       <c r="P77" s="3" t="inlineStr">
         <is>
-          <t>C 30.00</t>
+          <t>C- 17.00</t>
         </is>
       </c>
       <c r="Q77" s="3" t="inlineStr">
@@ -18019,7 +18015,7 @@
       </c>
       <c r="R77" s="3" t="inlineStr">
         <is>
-          <t>08-25 15:00</t>
+          <t>08-25 09:00</t>
         </is>
       </c>
       <c r="S77" s="3" t="inlineStr">
@@ -18033,45 +18029,47 @@
         </is>
       </c>
       <c r="U77" s="4" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V77" s="3"/>
-      <c r="W77" s="3" t="inlineStr">
-        <is>
-          <t>6-</t>
-        </is>
-      </c>
-      <c r="X77" s="3"/>
+        <v>1.85</v>
+      </c>
+      <c r="V77" s="4" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="W77" s="3"/>
+      <c r="X77" s="3" t="inlineStr">
+        <is>
+          <t>1.82%~1.86%</t>
+        </is>
+      </c>
       <c r="Y77" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z77" s="3"/>
       <c r="AA77" s="3" t="inlineStr">
         <is>
-          <t>河南省-新乡市</t>
+          <t>新疆维吾尔自治区-乌鲁木齐市</t>
         </is>
       </c>
       <c r="AB77" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据发行金额5亿元,本次发行扣除发行费用后,募集资金拟全部用于偿还发行人本部及合并范围内下属子公司的存量有息债务</t>
+          <t>本次短期融资券发行金额为2亿元,募集资金用于偿还发行人本部银行贷款。</t>
         </is>
       </c>
       <c r="AC77" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,渤海银行股份有限公司,交通银行股份有限公司,中国民生银行股份有限公司,中国工商银行股份有限公司,招商银行股份有限公司,华夏银行股份有限公司,中国建设银行股份有限公司</t>
+          <t>华夏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD77" s="3"/>
       <c r="AE77" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>短期融资券(CP)</t>
         </is>
       </c>
       <c r="AF77" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG77" s="3" t="inlineStr">
@@ -18081,7 +18079,7 @@
       </c>
       <c r="AH77" s="3" t="inlineStr">
         <is>
-          <t>河南心连心化学工业集团股份有限公司2026年度第一期科技创新债券(乡村振兴)</t>
+          <t>新疆城建(集团)股份有限公司2026年度第二期短期融资券</t>
         </is>
       </c>
       <c r="AI77" s="3" t="inlineStr">
@@ -18091,14 +18089,10 @@
       </c>
       <c r="AJ77" s="3" t="inlineStr">
         <is>
-          <t>2029-08-26</t>
-        </is>
-      </c>
-      <c r="AK77" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2027-08-26</t>
+        </is>
+      </c>
+      <c r="AK77" s="3"/>
       <c r="AL77" s="3" t="inlineStr">
         <is>
           <t>2026-08-27</t>
@@ -18119,25 +18113,29 @@
           <t>产业</t>
         </is>
       </c>
-      <c r="AP77" s="3"/>
+      <c r="AP77" s="3" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
       <c r="AQ77" s="3" t="inlineStr">
         <is>
-          <t>化工制造</t>
+          <t>建筑施工</t>
         </is>
       </c>
       <c r="AR77" s="3" t="inlineStr">
         <is>
-          <t>化学制品</t>
+          <t>综合建筑施工</t>
         </is>
       </c>
       <c r="AS77" s="3" t="inlineStr">
         <is>
-          <t>化学制品</t>
+          <t>综合建筑施工</t>
         </is>
       </c>
       <c r="AT77" s="3" t="inlineStr">
         <is>
-          <t>化学制品</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU77" s="3" t="inlineStr">
@@ -18170,7 +18168,7 @@
     <row r="78" customHeight="true" ht="18.0">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>26新疆城建CP002</t>
+          <t>26保利久联CP003</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -18180,49 +18178,49 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>042680299.IB</t>
+          <t>042680298.IB</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>1Y</t>
+          <t>0.49Y</t>
         </is>
       </c>
       <c r="E78" s="4" t="n">
-        <v>2.0</v>
+        <v>1.5</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>2.0</v>
+        <v>1.5</v>
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
+          <t>2.64 ~ 3.64</t>
         </is>
       </c>
       <c r="H78" s="4" t="n">
-        <v>1.75</v>
+        <v>3.6</v>
       </c>
       <c r="I78" s="4" t="n">
-        <v>54.7</v>
+        <v>239.89</v>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="K78" s="3" t="inlineStr">
         <is>
-          <t>26新疆城建CP001</t>
+          <t>25保利久联MTN001</t>
         </is>
       </c>
       <c r="L78" s="3" t="inlineStr">
         <is>
-          <t>319D</t>
+          <t>190D</t>
         </is>
       </c>
       <c r="M78" s="3" t="inlineStr">
         <is>
-          <t>1.7946</t>
+          <t>3.6560</t>
         </is>
       </c>
       <c r="N78" s="3" t="inlineStr">
@@ -18232,12 +18230,12 @@
       </c>
       <c r="O78" s="3" t="inlineStr">
         <is>
-          <t>新疆城建(集团)股份有限公司</t>
+          <t>保利久联控股集团有限责任公司</t>
         </is>
       </c>
       <c r="P78" s="3" t="inlineStr">
         <is>
-          <t>C- 17.00</t>
+          <t>D+ 7.36</t>
         </is>
       </c>
       <c r="Q78" s="3" t="inlineStr">
@@ -18261,36 +18259,40 @@
         </is>
       </c>
       <c r="U78" s="4" t="n">
-        <v>1.85</v>
+        <v>1.4</v>
       </c>
       <c r="V78" s="4" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="W78" s="3"/>
+        <v>5.0</v>
+      </c>
+      <c r="W78" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="X78" s="3" t="inlineStr">
         <is>
-          <t>1.82%~1.86%</t>
+          <t>3.65%~3.69%</t>
         </is>
       </c>
       <c r="Y78" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z78" s="3"/>
       <c r="AA78" s="3" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区-乌鲁木齐市</t>
+          <t>贵州省-贵阳市</t>
         </is>
       </c>
       <c r="AB78" s="3" t="inlineStr">
         <is>
-          <t>本次短期融资券发行金额为2亿元,募集资金用于偿还发行人本部银行贷款。</t>
+          <t>本期短期融资券发行金额1.50亿元，全部用于偿还发行人有息债务[25保利久联CP003（科创债）]</t>
         </is>
       </c>
       <c r="AC78" s="3" t="inlineStr">
         <is>
-          <t>华夏银行股份有限公司</t>
+          <t>贵阳银行股份有限公司</t>
         </is>
       </c>
       <c r="AD78" s="3"/>
@@ -18301,7 +18303,7 @@
       </c>
       <c r="AF78" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG78" s="3" t="inlineStr">
@@ -18311,7 +18313,7 @@
       </c>
       <c r="AH78" s="3" t="inlineStr">
         <is>
-          <t>新疆城建(集团)股份有限公司2026年度第二期短期融资券</t>
+          <t>保利久联控股集团有限责任公司2026年度第三期短期融资券</t>
         </is>
       </c>
       <c r="AI78" s="3" t="inlineStr">
@@ -18321,7 +18323,7 @@
       </c>
       <c r="AJ78" s="3" t="inlineStr">
         <is>
-          <t>2027-08-26</t>
+          <t>2027-02-22</t>
         </is>
       </c>
       <c r="AK78" s="3"/>
@@ -18347,27 +18349,27 @@
       </c>
       <c r="AP78" s="3" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ78" s="3" t="inlineStr">
         <is>
-          <t>建筑施工</t>
+          <t>化工制造</t>
         </is>
       </c>
       <c r="AR78" s="3" t="inlineStr">
         <is>
-          <t>综合建筑施工</t>
+          <t>化学制品</t>
         </is>
       </c>
       <c r="AS78" s="3" t="inlineStr">
         <is>
-          <t>综合建筑施工</t>
+          <t>化学制品</t>
         </is>
       </c>
       <c r="AT78" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>化学制品</t>
         </is>
       </c>
       <c r="AU78" s="3" t="inlineStr">
@@ -18400,7 +18402,7 @@
     <row r="79" customHeight="true" ht="18.0">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>26保利久联CP003</t>
+          <t>26蓉城交通SCP001</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -18410,64 +18412,64 @@
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>042680298.IB</t>
+          <t>012682146.IB</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>0.49Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E79" s="4" t="n">
-        <v>1.5</v>
+        <v>2.0</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>1.5</v>
+        <v>2.0</v>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2.64 ~ 3.64</t>
+          <t>1.30 ~ 1.90</t>
         </is>
       </c>
       <c r="H79" s="4" t="n">
-        <v>3.6</v>
+        <v>1.52</v>
       </c>
       <c r="I79" s="4" t="n">
-        <v>239.89</v>
+        <v>38.44</v>
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>25保利久联MTN001</t>
+          <t>24成都公交GN002</t>
         </is>
       </c>
       <c r="L79" s="3" t="inlineStr">
         <is>
-          <t>190D</t>
+          <t>349D</t>
         </is>
       </c>
       <c r="M79" s="3" t="inlineStr">
         <is>
-          <t>3.6560</t>
+          <t>1.5802</t>
         </is>
       </c>
       <c r="N79" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6000/1.5600</t>
         </is>
       </c>
       <c r="O79" s="3" t="inlineStr">
         <is>
-          <t>保利久联控股集团有限责任公司</t>
+          <t>成都市公共交通集团有限公司</t>
         </is>
       </c>
       <c r="P79" s="3" t="inlineStr">
         <is>
-          <t>D+ 7.36</t>
+          <t>C+ 32.00</t>
         </is>
       </c>
       <c r="Q79" s="3" t="inlineStr">
@@ -18491,19 +18493,19 @@
         </is>
       </c>
       <c r="U79" s="4" t="n">
-        <v>1.4</v>
+        <v>3.05</v>
       </c>
       <c r="V79" s="4" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="W79" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X79" s="3" t="inlineStr">
         <is>
-          <t>3.65%~3.69%</t>
+          <t>1.57%~1.61%</t>
         </is>
       </c>
       <c r="Y79" s="3" t="inlineStr">
@@ -18514,28 +18516,28 @@
       <c r="Z79" s="3"/>
       <c r="AA79" s="3" t="inlineStr">
         <is>
-          <t>贵州省-贵阳市</t>
+          <t>四川省-成都市</t>
         </is>
       </c>
       <c r="AB79" s="3" t="inlineStr">
         <is>
-          <t>本期短期融资券发行金额1.50亿元，全部用于偿还发行人有息债务[25保利久联CP003（科创债）]</t>
+          <t>发行人本期发行金额2亿元,拟用于偿还发行人到期的有息债务</t>
         </is>
       </c>
       <c r="AC79" s="3" t="inlineStr">
         <is>
-          <t>贵阳银行股份有限公司</t>
+          <t>招商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD79" s="3"/>
       <c r="AE79" s="3" t="inlineStr">
         <is>
-          <t>短期融资券(CP)</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF79" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG79" s="3" t="inlineStr">
@@ -18545,7 +18547,7 @@
       </c>
       <c r="AH79" s="3" t="inlineStr">
         <is>
-          <t>保利久联控股集团有限责任公司2026年度第三期短期融资券</t>
+          <t>成都市公共交通集团有限公司2026年度第一期超短期融资券</t>
         </is>
       </c>
       <c r="AI79" s="3" t="inlineStr">
@@ -18555,10 +18557,14 @@
       </c>
       <c r="AJ79" s="3" t="inlineStr">
         <is>
-          <t>2027-02-22</t>
-        </is>
-      </c>
-      <c r="AK79" s="3"/>
+          <t>2027-05-23</t>
+        </is>
+      </c>
+      <c r="AK79" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL79" s="3" t="inlineStr">
         <is>
           <t>2026-08-27</t>
@@ -18576,32 +18582,32 @@
       </c>
       <c r="AO79" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP79" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ79" s="3" t="inlineStr">
         <is>
-          <t>化工制造</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR79" s="3" t="inlineStr">
         <is>
-          <t>化学制品</t>
+          <t>其他公用</t>
         </is>
       </c>
       <c r="AS79" s="3" t="inlineStr">
         <is>
-          <t>化学制品</t>
+          <t>其他公用</t>
         </is>
       </c>
       <c r="AT79" s="3" t="inlineStr">
         <is>
-          <t>化学制品</t>
+          <t>公交</t>
         </is>
       </c>
       <c r="AU79" s="3" t="inlineStr">
@@ -18634,7 +18640,7 @@
     <row r="80" customHeight="true" ht="18.0">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>26蓉城交通SCP001</t>
+          <t>26海润城发MTN001</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -18644,64 +18650,64 @@
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>012682146.IB</t>
+          <t>102683336.IB</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E80" s="4" t="n">
-        <v>2.0</v>
+        <v>2.2</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>2.0</v>
+        <v>2.2</v>
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.90</t>
+          <t>1.60 ~ 2.20</t>
         </is>
       </c>
       <c r="H80" s="4" t="n">
-        <v>1.52</v>
+        <v>1.7</v>
       </c>
       <c r="I80" s="4" t="n">
-        <v>38.44</v>
+        <v>44.67</v>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>24成都公交GN002</t>
+          <t>24海润G4</t>
         </is>
       </c>
       <c r="L80" s="3" t="inlineStr">
         <is>
-          <t>349D</t>
+          <t>1.22Y</t>
         </is>
       </c>
       <c r="M80" s="3" t="inlineStr">
         <is>
-          <t>1.5802</t>
+          <t>1.6247</t>
         </is>
       </c>
       <c r="N80" s="3" t="inlineStr">
         <is>
-          <t>1.6000/1.5600</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O80" s="3" t="inlineStr">
         <is>
-          <t>成都市公共交通集团有限公司</t>
+          <t>江苏海润城市发展集团有限公司</t>
         </is>
       </c>
       <c r="P80" s="3" t="inlineStr">
         <is>
-          <t>C+ 32.00</t>
+          <t>C- 17.52</t>
         </is>
       </c>
       <c r="Q80" s="3" t="inlineStr">
@@ -18725,19 +18731,17 @@
         </is>
       </c>
       <c r="U80" s="4" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="V80" s="4" t="n">
-        <v>1.0</v>
-      </c>
+        <v>5.2727</v>
+      </c>
+      <c r="V80" s="3"/>
       <c r="W80" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X80" s="3" t="inlineStr">
         <is>
-          <t>1.57%~1.61%</t>
+          <t>1.65%~1.75%</t>
         </is>
       </c>
       <c r="Y80" s="3" t="inlineStr">
@@ -18748,23 +18752,23 @@
       <c r="Z80" s="3"/>
       <c r="AA80" s="3" t="inlineStr">
         <is>
-          <t>四川省-成都市</t>
+          <t>江苏省-南通市</t>
         </is>
       </c>
       <c r="AB80" s="3" t="inlineStr">
         <is>
-          <t>发行人本期发行金额2亿元,拟用于偿还发行人到期的有息债务</t>
+          <t>发行人本期中期票据发行金额为2.2亿元,募集资金用于偿还发行人存量债务融资工具本金[25海润城发SCP005]</t>
         </is>
       </c>
       <c r="AC80" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司</t>
+          <t>南京银行股份有限公司</t>
         </is>
       </c>
       <c r="AD80" s="3"/>
       <c r="AE80" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF80" s="3" t="inlineStr">
@@ -18779,7 +18783,7 @@
       </c>
       <c r="AH80" s="3" t="inlineStr">
         <is>
-          <t>成都市公共交通集团有限公司2026年度第一期超短期融资券</t>
+          <t>江苏海润城市发展集团有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI80" s="3" t="inlineStr">
@@ -18789,7 +18793,7 @@
       </c>
       <c r="AJ80" s="3" t="inlineStr">
         <is>
-          <t>2027-05-23</t>
+          <t>2029-08-26</t>
         </is>
       </c>
       <c r="AK80" s="3" t="inlineStr">
@@ -18819,27 +18823,27 @@
       </c>
       <c r="AP80" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ80" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR80" s="3" t="inlineStr">
         <is>
-          <t>其他公用</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS80" s="3" t="inlineStr">
         <is>
-          <t>其他公用</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT80" s="3" t="inlineStr">
         <is>
-          <t>公交</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU80" s="3" t="inlineStr">
@@ -18867,12 +18871,14 @@
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="AZ80" s="3"/>
+      <c r="AZ80" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="81" customHeight="true" ht="18.0">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>26海润城发MTN001</t>
+          <t>26桂国控SCP005</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -18882,49 +18888,49 @@
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>102683336.IB</t>
+          <t>012682149.IB</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E81" s="4" t="n">
-        <v>2.2</v>
+        <v>7.0</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>2.2</v>
+        <v>7.0</v>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.20</t>
+          <t>1.39 ~ 1.69</t>
         </is>
       </c>
       <c r="H81" s="4" t="n">
-        <v>1.7</v>
+        <v>1.46</v>
       </c>
       <c r="I81" s="4" t="n">
-        <v>44.67</v>
+        <v>32.44</v>
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>24海润G4</t>
+          <t>24农垦MTN002A</t>
         </is>
       </c>
       <c r="L81" s="3" t="inlineStr">
         <is>
-          <t>1.22Y</t>
+          <t>324D</t>
         </is>
       </c>
       <c r="M81" s="3" t="inlineStr">
         <is>
-          <t>1.6247</t>
+          <t>1.6104</t>
         </is>
       </c>
       <c r="N81" s="3" t="inlineStr">
@@ -18934,12 +18940,12 @@
       </c>
       <c r="O81" s="3" t="inlineStr">
         <is>
-          <t>江苏海润城市发展集团有限公司</t>
+          <t>广西国控资本运营集团有限责任公司</t>
         </is>
       </c>
       <c r="P81" s="3" t="inlineStr">
         <is>
-          <t>C- 17.52</t>
+          <t>C- 15.75</t>
         </is>
       </c>
       <c r="Q81" s="3" t="inlineStr">
@@ -18963,44 +18969,46 @@
         </is>
       </c>
       <c r="U81" s="4" t="n">
-        <v>5.2727</v>
-      </c>
-      <c r="V81" s="3"/>
+        <v>4.5143</v>
+      </c>
+      <c r="V81" s="4" t="n">
+        <v>1.08</v>
+      </c>
       <c r="W81" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X81" s="3" t="inlineStr">
         <is>
-          <t>1.65%~1.75%</t>
+          <t>1.56%~1.60%</t>
         </is>
       </c>
       <c r="Y81" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z81" s="3"/>
       <c r="AA81" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南通市</t>
+          <t>广西壮族自治区</t>
         </is>
       </c>
       <c r="AB81" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据发行金额为2.2亿元,募集资金用于偿还发行人存量债务融资工具本金[25海润城发SCP005]</t>
+          <t>本期债务融资工具募集资金全部用于归还发行人本部及下属公司的有息债务</t>
         </is>
       </c>
       <c r="AC81" s="3" t="inlineStr">
         <is>
-          <t>南京银行股份有限公司</t>
+          <t>上海浦东发展银行股份有限公司,交通银行股份有限公司</t>
         </is>
       </c>
       <c r="AD81" s="3"/>
       <c r="AE81" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF81" s="3" t="inlineStr">
@@ -19015,7 +19023,7 @@
       </c>
       <c r="AH81" s="3" t="inlineStr">
         <is>
-          <t>江苏海润城市发展集团有限公司2026年度第一期中期票据</t>
+          <t>广西国控资本运营集团有限责任公司2026年度第五期超短期融资券</t>
         </is>
       </c>
       <c r="AI81" s="3" t="inlineStr">
@@ -19025,7 +19033,7 @@
       </c>
       <c r="AJ81" s="3" t="inlineStr">
         <is>
-          <t>2029-08-26</t>
+          <t>2027-05-23</t>
         </is>
       </c>
       <c r="AK81" s="3" t="inlineStr">
@@ -19050,34 +19058,34 @@
       </c>
       <c r="AO81" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP81" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ81" s="3" t="inlineStr">
         <is>
+          <t>农林牧渔</t>
+        </is>
+      </c>
+      <c r="AR81" s="3" t="inlineStr">
+        <is>
+          <t>综合农林牧渔</t>
+        </is>
+      </c>
+      <c r="AS81" s="3" t="inlineStr">
+        <is>
+          <t>综合农林牧渔</t>
+        </is>
+      </c>
+      <c r="AT81" s="3" t="inlineStr">
+        <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="AR81" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS81" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AT81" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
       <c r="AU81" s="3" t="inlineStr">
         <is>
           <t/>
@@ -19103,14 +19111,12 @@
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="AZ81" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ81" s="3"/>
     </row>
     <row r="82" customHeight="true" ht="18.0">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>26桂国控SCP005</t>
+          <t>26铁塔股份MTN004</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -19120,64 +19126,64 @@
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>012682149.IB</t>
+          <t>102683331.IB</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E82" s="4" t="n">
-        <v>7.0</v>
+        <v>40.0</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>7.0</v>
+        <v>40.0</v>
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>1.39 ~ 1.69</t>
+          <t>1.40 ~ 1.90</t>
         </is>
       </c>
       <c r="H82" s="4" t="n">
-        <v>1.46</v>
+        <v>1.56</v>
       </c>
       <c r="I82" s="4" t="n">
-        <v>32.44</v>
+        <v>30.67</v>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t>24农垦MTN002A</t>
+          <t>26铁塔股份MTN001</t>
         </is>
       </c>
       <c r="L82" s="3" t="inlineStr">
         <is>
-          <t>324D</t>
+          <t>2.66Y</t>
         </is>
       </c>
       <c r="M82" s="3" t="inlineStr">
         <is>
-          <t>1.6104</t>
+          <t>1.6451</t>
         </is>
       </c>
       <c r="N82" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6600/1.6400</t>
         </is>
       </c>
       <c r="O82" s="3" t="inlineStr">
         <is>
-          <t>广西国控资本运营集团有限责任公司</t>
+          <t>中国铁塔股份有限公司</t>
         </is>
       </c>
       <c r="P82" s="3" t="inlineStr">
         <is>
-          <t>C- 15.75</t>
+          <t>C 26.25</t>
         </is>
       </c>
       <c r="Q82" s="3" t="inlineStr">
@@ -19201,19 +19207,19 @@
         </is>
       </c>
       <c r="U82" s="4" t="n">
-        <v>4.5143</v>
+        <v>1.575</v>
       </c>
       <c r="V82" s="4" t="n">
-        <v>1.08</v>
+        <v>1.0</v>
       </c>
       <c r="W82" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X82" s="3" t="inlineStr">
         <is>
-          <t>1.56%~1.60%</t>
+          <t>1.60%~1.70%</t>
         </is>
       </c>
       <c r="Y82" s="3" t="inlineStr">
@@ -19224,28 +19230,28 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3" t="inlineStr">
         <is>
-          <t>广西壮族自治区</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB82" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具募集资金全部用于归还发行人本部及下属公司的有息债务</t>
+          <t>本期中期票据发行金额40亿元,募集资金14.85亿元拟将用于偿还有息债务,25.15亿元拟将用于补充流动资金。</t>
         </is>
       </c>
       <c r="AC82" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司,交通银行股份有限公司</t>
+          <t>招商银行股份有限公司,中国工商银行股份有限公司,中国建设银行股份有限公司</t>
         </is>
       </c>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF82" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG82" s="3" t="inlineStr">
@@ -19255,7 +19261,7 @@
       </c>
       <c r="AH82" s="3" t="inlineStr">
         <is>
-          <t>广西国控资本运营集团有限责任公司2026年度第五期超短期融资券</t>
+          <t>中国铁塔股份有限公司2026年度第四期中期票据</t>
         </is>
       </c>
       <c r="AI82" s="3" t="inlineStr">
@@ -19265,7 +19271,7 @@
       </c>
       <c r="AJ82" s="3" t="inlineStr">
         <is>
-          <t>2027-05-23</t>
+          <t>2029-08-26</t>
         </is>
       </c>
       <c r="AK82" s="3" t="inlineStr">
@@ -19295,27 +19301,27 @@
       </c>
       <c r="AP82" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AQ82" s="3" t="inlineStr">
         <is>
-          <t>农林牧渔</t>
+          <t>电子设备制造</t>
         </is>
       </c>
       <c r="AR82" s="3" t="inlineStr">
         <is>
-          <t>综合农林牧渔</t>
+          <t>通信设备</t>
         </is>
       </c>
       <c r="AS82" s="3" t="inlineStr">
         <is>
-          <t>综合农林牧渔</t>
+          <t>通信设备</t>
         </is>
       </c>
       <c r="AT82" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>通信设备</t>
         </is>
       </c>
       <c r="AU82" s="3" t="inlineStr">
@@ -19348,7 +19354,7 @@
     <row r="83" customHeight="true" ht="18.0">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>26铁塔股份MTN004</t>
+          <t>26浙江经投MTN002</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -19358,7 +19364,7 @@
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>102683331.IB</t>
+          <t>102683330.IB</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
@@ -19367,14 +19373,14 @@
         </is>
       </c>
       <c r="E83" s="4" t="n">
-        <v>40.0</v>
+        <v>1.4</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>40.0</v>
+        <v>1.4</v>
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.90</t>
+          <t>1.40 ~ 2.00</t>
         </is>
       </c>
       <c r="H83" s="4" t="n">
@@ -19385,37 +19391,37 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>26铁塔股份MTN001</t>
+          <t>24鲁资K1</t>
         </is>
       </c>
       <c r="L83" s="3" t="inlineStr">
         <is>
-          <t>2.66Y</t>
+          <t>3.00Y</t>
         </is>
       </c>
       <c r="M83" s="3" t="inlineStr">
         <is>
-          <t>1.6451</t>
+          <t>1.6616</t>
         </is>
       </c>
       <c r="N83" s="3" t="inlineStr">
         <is>
-          <t>1.6600/1.6400</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O83" s="3" t="inlineStr">
         <is>
-          <t>中国铁塔股份有限公司</t>
+          <t>浙江省经济建设投资有限公司</t>
         </is>
       </c>
       <c r="P83" s="3" t="inlineStr">
         <is>
-          <t>C 26.25</t>
+          <t>D+ 6.50</t>
         </is>
       </c>
       <c r="Q83" s="3" t="inlineStr">
@@ -19439,19 +19445,19 @@
         </is>
       </c>
       <c r="U83" s="4" t="n">
-        <v>1.575</v>
+        <v>2.55</v>
       </c>
       <c r="V83" s="4" t="n">
         <v>1.0</v>
       </c>
       <c r="W83" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X83" s="3" t="inlineStr">
         <is>
-          <t>1.60%~1.70%</t>
+          <t>1.51%~1.61%</t>
         </is>
       </c>
       <c r="Y83" s="3" t="inlineStr">
@@ -19460,19 +19466,15 @@
         </is>
       </c>
       <c r="Z83" s="3"/>
-      <c r="AA83" s="3" t="inlineStr">
-        <is>
-          <t>北京市</t>
-        </is>
-      </c>
+      <c r="AA83" s="3"/>
       <c r="AB83" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额40亿元,募集资金14.85亿元拟将用于偿还有息债务,25.15亿元拟将用于补充流动资金。</t>
+          <t>发行人本期发行金额1.4亿元,募集资金拟用于偿还发行人的有息债务1.4亿元</t>
         </is>
       </c>
       <c r="AC83" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司,中国工商银行股份有限公司,中国建设银行股份有限公司</t>
+          <t>上海浦东发展银行股份有限公司,南京银行股份有限公司</t>
         </is>
       </c>
       <c r="AD83" s="3"/>
@@ -19483,7 +19485,7 @@
       </c>
       <c r="AF83" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG83" s="3" t="inlineStr">
@@ -19493,7 +19495,7 @@
       </c>
       <c r="AH83" s="3" t="inlineStr">
         <is>
-          <t>中国铁塔股份有限公司2026年度第四期中期票据</t>
+          <t>浙江省经济建设投资有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI83" s="3" t="inlineStr">
@@ -19518,7 +19520,7 @@
       </c>
       <c r="AM83" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="AN83" s="3" t="inlineStr">
@@ -19528,32 +19530,28 @@
       </c>
       <c r="AO83" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP83" s="3" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP83" s="3"/>
       <c r="AQ83" s="3" t="inlineStr">
         <is>
-          <t>电子设备制造</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR83" s="3" t="inlineStr">
         <is>
-          <t>通信设备</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS83" s="3" t="inlineStr">
         <is>
-          <t>通信设备</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT83" s="3" t="inlineStr">
         <is>
-          <t>通信设备</t>
+          <t>元件</t>
         </is>
       </c>
       <c r="AU83" s="3" t="inlineStr">
@@ -19586,7 +19584,7 @@
     <row r="84" customHeight="true" ht="18.0">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>26浙江经投MTN002</t>
+          <t>26鄂州城投MTN001</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -19596,64 +19594,64 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>102683330.IB</t>
+          <t>102683358.IB</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E84" s="4" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.00</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="H84" s="4" t="n">
-        <v>1.56</v>
+        <v>2.13</v>
       </c>
       <c r="I84" s="4" t="n">
-        <v>30.67</v>
+        <v>74.28</v>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="K84" s="3" t="inlineStr">
         <is>
-          <t>24鲁资K1</t>
+          <t>25鄂州城投MTN002</t>
         </is>
       </c>
       <c r="L84" s="3" t="inlineStr">
         <is>
-          <t>3.00Y</t>
+          <t>4.08Y</t>
         </is>
       </c>
       <c r="M84" s="3" t="inlineStr">
         <is>
-          <t>1.6616</t>
+          <t>2.0866</t>
         </is>
       </c>
       <c r="N84" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.1200/--</t>
         </is>
       </c>
       <c r="O84" s="3" t="inlineStr">
         <is>
-          <t>浙江省经济建设投资有限公司</t>
+          <t>鄂州市城市建设投资有限公司</t>
         </is>
       </c>
       <c r="P84" s="3" t="inlineStr">
         <is>
-          <t>D+ 6.50</t>
+          <t>C- 14.37</t>
         </is>
       </c>
       <c r="Q84" s="3" t="inlineStr">
@@ -19663,7 +19661,7 @@
       </c>
       <c r="R84" s="3" t="inlineStr">
         <is>
-          <t>08-25 09:00</t>
+          <t>08-25 15:00</t>
         </is>
       </c>
       <c r="S84" s="3" t="inlineStr">
@@ -19677,36 +19675,40 @@
         </is>
       </c>
       <c r="U84" s="4" t="n">
-        <v>2.55</v>
+        <v>3.875</v>
       </c>
       <c r="V84" s="4" t="n">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
       <c r="W84" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X84" s="3" t="inlineStr">
         <is>
-          <t>1.51%~1.61%</t>
+          <t>2.11%~2.21%</t>
         </is>
       </c>
       <c r="Y84" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z84" s="3"/>
-      <c r="AA84" s="3"/>
+      <c r="AA84" s="3" t="inlineStr">
+        <is>
+          <t>湖北省-鄂州市</t>
+        </is>
+      </c>
       <c r="AB84" s="3" t="inlineStr">
         <is>
-          <t>发行人本期发行金额1.4亿元,募集资金拟用于偿还发行人的有息债务1.4亿元</t>
+          <t>本期中期票据发行规模为2.40亿元,拟偿还的非金融企业债务融资工具本金[24鄂州城投MTN001]</t>
         </is>
       </c>
       <c r="AC84" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司,南京银行股份有限公司</t>
+          <t>国泰海通证券股份有限公司,申万宏源证券有限公司</t>
         </is>
       </c>
       <c r="AD84" s="3"/>
@@ -19727,7 +19729,7 @@
       </c>
       <c r="AH84" s="3" t="inlineStr">
         <is>
-          <t>浙江省经济建设投资有限公司2026年度第二期中期票据</t>
+          <t>鄂州市城市建设投资有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI84" s="3" t="inlineStr">
@@ -19737,14 +19739,10 @@
       </c>
       <c r="AJ84" s="3" t="inlineStr">
         <is>
-          <t>2029-08-26</t>
-        </is>
-      </c>
-      <c r="AK84" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-08-26</t>
+        </is>
+      </c>
+      <c r="AK84" s="3"/>
       <c r="AL84" s="3" t="inlineStr">
         <is>
           <t>2026-08-27</t>
@@ -19752,7 +19750,7 @@
       </c>
       <c r="AM84" s="3" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AN84" s="3" t="inlineStr">
@@ -19762,10 +19760,14 @@
       </c>
       <c r="AO84" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP84" s="3"/>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP84" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="AQ84" s="3" t="inlineStr">
         <is>
           <t>综合</t>
@@ -19773,17 +19775,17 @@
       </c>
       <c r="AR84" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS84" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT84" s="3" t="inlineStr">
         <is>
-          <t>元件</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU84" s="3" t="inlineStr">
@@ -19816,7 +19818,7 @@
     <row r="85" customHeight="true" ht="18.0">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>26鄂州城投MTN001</t>
+          <t>26环球租赁MTN002</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -19826,64 +19828,64 @@
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>102683358.IB</t>
+          <t>102683348.IB</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E85" s="4" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.50 ~ 1.73</t>
         </is>
       </c>
       <c r="H85" s="4" t="n">
-        <v>2.13</v>
+        <v>1.73</v>
       </c>
       <c r="I85" s="4" t="n">
-        <v>74.28</v>
+        <v>49.39</v>
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>25鄂州城投MTN002</t>
+          <t>25环球租赁MTN002</t>
         </is>
       </c>
       <c r="L85" s="3" t="inlineStr">
         <is>
-          <t>4.08Y</t>
+          <t>2.00Y</t>
         </is>
       </c>
       <c r="M85" s="3" t="inlineStr">
         <is>
-          <t>2.0866</t>
+          <t>1.7483</t>
         </is>
       </c>
       <c r="N85" s="3" t="inlineStr">
         <is>
-          <t>2.1200/--</t>
+          <t>1.7700/1.7000</t>
         </is>
       </c>
       <c r="O85" s="3" t="inlineStr">
         <is>
-          <t>鄂州市城市建设投资有限公司</t>
+          <t>中国环球租赁有限公司</t>
         </is>
       </c>
       <c r="P85" s="3" t="inlineStr">
         <is>
-          <t>C- 14.37</t>
+          <t>C- 22.46</t>
         </is>
       </c>
       <c r="Q85" s="3" t="inlineStr">
@@ -19893,7 +19895,7 @@
       </c>
       <c r="R85" s="3" t="inlineStr">
         <is>
-          <t>08-25 15:00</t>
+          <t>08-25 10:00</t>
         </is>
       </c>
       <c r="S85" s="3" t="inlineStr">
@@ -19907,40 +19909,38 @@
         </is>
       </c>
       <c r="U85" s="4" t="n">
-        <v>3.875</v>
-      </c>
-      <c r="V85" s="4" t="n">
-        <v>8.0</v>
-      </c>
+        <v>1.28</v>
+      </c>
+      <c r="V85" s="3"/>
       <c r="W85" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X85" s="3" t="inlineStr">
         <is>
-          <t>2.11%~2.21%</t>
+          <t>1.68%~1.78%</t>
         </is>
       </c>
       <c r="Y85" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z85" s="3"/>
       <c r="AA85" s="3" t="inlineStr">
         <is>
-          <t>湖北省-鄂州市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB85" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行规模为2.40亿元,拟偿还的非金融企业债务融资工具本金[24鄂州城投MTN001]</t>
+          <t>本期中期票据发行金额为2.5亿元,用于偿还发行人存量债务融资工具[25环球租赁SCP014]</t>
         </is>
       </c>
       <c r="AC85" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,申万宏源证券有限公司</t>
+          <t>天津银行股份有限公司,中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD85" s="3"/>
@@ -19951,7 +19951,7 @@
       </c>
       <c r="AF85" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG85" s="3" t="inlineStr">
@@ -19961,7 +19961,7 @@
       </c>
       <c r="AH85" s="3" t="inlineStr">
         <is>
-          <t>鄂州市城市建设投资有限公司2026年度第一期中期票据</t>
+          <t>中国环球租赁有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI85" s="3" t="inlineStr">
@@ -19971,10 +19971,14 @@
       </c>
       <c r="AJ85" s="3" t="inlineStr">
         <is>
-          <t>2031-08-26</t>
-        </is>
-      </c>
-      <c r="AK85" s="3"/>
+          <t>2028-08-26</t>
+        </is>
+      </c>
+      <c r="AK85" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL85" s="3" t="inlineStr">
         <is>
           <t>2026-08-27</t>
@@ -19992,32 +19996,32 @@
       </c>
       <c r="AO85" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP85" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ85" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR85" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AS85" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AT85" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU85" s="3" t="inlineStr">
@@ -20045,12 +20049,14 @@
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="AZ85" s="3"/>
+      <c r="AZ85" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="86" customHeight="true" ht="18.0">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>26环球租赁MTN002</t>
+          <t>26唐山工业MTN002</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -20060,64 +20066,64 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>102683348.IB</t>
+          <t>102683351.IB</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E86" s="4" t="n">
-        <v>2.5</v>
+        <v>5.0</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>2.5</v>
+        <v>5.0</v>
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.73</t>
+          <t>2.00 ~ 3.00</t>
         </is>
       </c>
       <c r="H86" s="4" t="n">
-        <v>1.73</v>
+        <v>2.35</v>
       </c>
       <c r="I86" s="4" t="n">
-        <v>49.39</v>
+        <v>109.67</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="K86" s="3" t="inlineStr">
         <is>
-          <t>25环球租赁MTN002</t>
+          <t>26唐山工业MTN001(并购)</t>
         </is>
       </c>
       <c r="L86" s="3" t="inlineStr">
         <is>
-          <t>2.00Y</t>
+          <t>2.79Y</t>
         </is>
       </c>
       <c r="M86" s="3" t="inlineStr">
         <is>
-          <t>1.7483</t>
+          <t>2.3729</t>
         </is>
       </c>
       <c r="N86" s="3" t="inlineStr">
         <is>
-          <t>1.7700/1.7000</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O86" s="3" t="inlineStr">
         <is>
-          <t>中国环球租赁有限公司</t>
+          <t>唐山工业控股集团有限公司</t>
         </is>
       </c>
       <c r="P86" s="3" t="inlineStr">
         <is>
-          <t>C- 22.46</t>
+          <t>C- 24.16</t>
         </is>
       </c>
       <c r="Q86" s="3" t="inlineStr">
@@ -20127,7 +20133,7 @@
       </c>
       <c r="R86" s="3" t="inlineStr">
         <is>
-          <t>08-25 10:00</t>
+          <t>08-25 14:00</t>
         </is>
       </c>
       <c r="S86" s="3" t="inlineStr">
@@ -20141,38 +20147,40 @@
         </is>
       </c>
       <c r="U86" s="4" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V86" s="3"/>
+        <v>1.68</v>
+      </c>
+      <c r="V86" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W86" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>7-</t>
         </is>
       </c>
       <c r="X86" s="3" t="inlineStr">
         <is>
-          <t>1.68%~1.78%</t>
+          <t>2.40%~2.50%</t>
         </is>
       </c>
       <c r="Y86" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z86" s="3"/>
       <c r="AA86" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>河北省-唐山市</t>
         </is>
       </c>
       <c r="AB86" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额为2.5亿元,用于偿还发行人存量债务融资工具[25环球租赁SCP014]</t>
+          <t>发行人本期中期票据基础发行规模0亿元,发行金额上限5.00亿元,募集资金全部用于偿还债务融资工具[25唐山工业MTN003,25唐山工业MTN004,24唐山工业MTN001B,24唐山工业MTN001A,25唐山工业MTN001A]</t>
         </is>
       </c>
       <c r="AC86" s="3" t="inlineStr">
         <is>
-          <t>天津银行股份有限公司,中信银行股份有限公司</t>
+          <t>东方证券股份有限公司,天津银行股份有限公司</t>
         </is>
       </c>
       <c r="AD86" s="3"/>
@@ -20183,7 +20191,7 @@
       </c>
       <c r="AF86" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG86" s="3" t="inlineStr">
@@ -20193,7 +20201,7 @@
       </c>
       <c r="AH86" s="3" t="inlineStr">
         <is>
-          <t>中国环球租赁有限公司2026年度第二期中期票据</t>
+          <t>唐山工业控股集团有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI86" s="3" t="inlineStr">
@@ -20203,12 +20211,12 @@
       </c>
       <c r="AJ86" s="3" t="inlineStr">
         <is>
-          <t>2028-08-26</t>
+          <t>2029-08-26</t>
         </is>
       </c>
       <c r="AK86" s="3" t="inlineStr">
         <is>
-          <t>休2</t>
+          <t>休1</t>
         </is>
       </c>
       <c r="AL86" s="3" t="inlineStr">
@@ -20228,32 +20236,28 @@
       </c>
       <c r="AO86" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP86" s="3" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP86" s="3"/>
       <c r="AQ86" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>化工制造</t>
         </is>
       </c>
       <c r="AR86" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>化学制品</t>
         </is>
       </c>
       <c r="AS86" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>化学制品</t>
         </is>
       </c>
       <c r="AT86" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>化学制品</t>
         </is>
       </c>
       <c r="AU86" s="3" t="inlineStr">
@@ -20281,14 +20285,12 @@
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="AZ86" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ86" s="3"/>
     </row>
     <row r="87" customHeight="true" ht="18.0">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>26唐山工业MTN002</t>
+          <t>26国丰集团MTN004B</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -20298,12 +20300,12 @@
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>102683351.IB</t>
+          <t>102683343.IB</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E87" s="4" t="n">
@@ -20314,48 +20316,48 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 3.00</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H87" s="4" t="n">
-        <v>2.35</v>
+        <v>1.69</v>
       </c>
       <c r="I87" s="4" t="n">
-        <v>109.67</v>
+        <v>30.28</v>
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>26唐山工业MTN001(并购)</t>
+          <t>26国丰04</t>
         </is>
       </c>
       <c r="L87" s="3" t="inlineStr">
         <is>
-          <t>2.79Y</t>
+          <t>4.91Y</t>
         </is>
       </c>
       <c r="M87" s="3" t="inlineStr">
         <is>
-          <t>2.3729</t>
+          <t>1.7923</t>
         </is>
       </c>
       <c r="N87" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8000/1.7700</t>
         </is>
       </c>
       <c r="O87" s="3" t="inlineStr">
         <is>
-          <t>唐山工业控股集团有限公司</t>
+          <t>烟台国丰投资控股集团有限公司</t>
         </is>
       </c>
       <c r="P87" s="3" t="inlineStr">
         <is>
-          <t>C- 24.16</t>
+          <t>C- 23.76</t>
         </is>
       </c>
       <c r="Q87" s="3" t="inlineStr">
@@ -20365,7 +20367,7 @@
       </c>
       <c r="R87" s="3" t="inlineStr">
         <is>
-          <t>08-25 14:00</t>
+          <t>08-25 09:00</t>
         </is>
       </c>
       <c r="S87" s="3" t="inlineStr">
@@ -20379,40 +20381,44 @@
         </is>
       </c>
       <c r="U87" s="4" t="n">
-        <v>1.68</v>
+        <v>6.74</v>
       </c>
       <c r="V87" s="4" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="W87" s="3" t="inlineStr">
         <is>
-          <t>7-</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X87" s="3" t="inlineStr">
         <is>
-          <t>2.40%~2.50%</t>
+          <t>1.77%~1.87%</t>
         </is>
       </c>
       <c r="Y87" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z87" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z87" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA87" s="3" t="inlineStr">
         <is>
-          <t>河北省-唐山市</t>
+          <t>山东省-烟台市</t>
         </is>
       </c>
       <c r="AB87" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据基础发行规模0亿元,发行金额上限5.00亿元,募集资金全部用于偿还债务融资工具[25唐山工业MTN003,25唐山工业MTN004,24唐山工业MTN001B,24唐山工业MTN001A,25唐山工业MTN001A]</t>
+          <t>本期中期票据基础发行规模0亿元,发行规模上限15亿元,所募集资金拟用于偿还发行人的有息负债。</t>
         </is>
       </c>
       <c r="AC87" s="3" t="inlineStr">
         <is>
-          <t>东方证券股份有限公司,天津银行股份有限公司</t>
+          <t>恒丰银行股份有限公司,中国民生银行股份有限公司</t>
         </is>
       </c>
       <c r="AD87" s="3"/>
@@ -20433,7 +20439,7 @@
       </c>
       <c r="AH87" s="3" t="inlineStr">
         <is>
-          <t>唐山工业控股集团有限公司2026年度第二期中期票据</t>
+          <t>烟台国丰投资控股集团有限公司2026年度第四期中期票据(品种二)</t>
         </is>
       </c>
       <c r="AI87" s="3" t="inlineStr">
@@ -20443,14 +20449,10 @@
       </c>
       <c r="AJ87" s="3" t="inlineStr">
         <is>
-          <t>2029-08-26</t>
-        </is>
-      </c>
-      <c r="AK87" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-08-26</t>
+        </is>
+      </c>
+      <c r="AK87" s="3"/>
       <c r="AL87" s="3" t="inlineStr">
         <is>
           <t>2026-08-27</t>
@@ -20471,7 +20473,11 @@
           <t>产业</t>
         </is>
       </c>
-      <c r="AP87" s="3"/>
+      <c r="AP87" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="AQ87" s="3" t="inlineStr">
         <is>
           <t>化工制造</t>
@@ -20522,7 +20528,7 @@
     <row r="88" customHeight="true" ht="18.0">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>26国丰集团MTN004B</t>
+          <t>26一汽租赁MTN003</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -20532,64 +20538,64 @@
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>102683343.IB</t>
+          <t>102683354.IB</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E88" s="4" t="n">
-        <v>5.0</v>
+        <v>15.0</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>5.0</v>
+        <v>15.0</v>
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.30 ~ 1.66</t>
         </is>
       </c>
       <c r="H88" s="4" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="I88" s="4" t="n">
-        <v>30.28</v>
+        <v>42.39</v>
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="K88" s="3" t="inlineStr">
         <is>
-          <t>26国丰04</t>
+          <t>26一汽租赁MTN002</t>
         </is>
       </c>
       <c r="L88" s="3" t="inlineStr">
         <is>
-          <t>4.91Y</t>
+          <t>1.75Y</t>
         </is>
       </c>
       <c r="M88" s="3" t="inlineStr">
         <is>
-          <t>1.7923</t>
+          <t>1.6648</t>
         </is>
       </c>
       <c r="N88" s="3" t="inlineStr">
         <is>
-          <t>1.8000/1.7700</t>
+          <t>1.6600/1.6300</t>
         </is>
       </c>
       <c r="O88" s="3" t="inlineStr">
         <is>
-          <t>烟台国丰投资控股集团有限公司</t>
+          <t>一汽租赁有限公司</t>
         </is>
       </c>
       <c r="P88" s="3" t="inlineStr">
         <is>
-          <t>C- 23.76</t>
+          <t>C+ 33.90</t>
         </is>
       </c>
       <c r="Q88" s="3" t="inlineStr">
@@ -20613,19 +20619,17 @@
         </is>
       </c>
       <c r="U88" s="4" t="n">
-        <v>6.74</v>
-      </c>
-      <c r="V88" s="4" t="n">
-        <v>3.0</v>
-      </c>
+        <v>0.4067</v>
+      </c>
+      <c r="V88" s="3"/>
       <c r="W88" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X88" s="3" t="inlineStr">
         <is>
-          <t>1.77%~1.87%</t>
+          <t>1.61%~1.71%</t>
         </is>
       </c>
       <c r="Y88" s="3" t="inlineStr">
@@ -20633,24 +20637,20 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z88" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z88" s="3"/>
       <c r="AA88" s="3" t="inlineStr">
         <is>
-          <t>山东省-烟台市</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="AB88" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据基础发行规模0亿元,发行规模上限15亿元,所募集资金拟用于偿还发行人的有息负债。</t>
+          <t>发行人本期发行中期票据15亿元,本期募集资金15亿元全部用于偿还有息债务</t>
         </is>
       </c>
       <c r="AC88" s="3" t="inlineStr">
         <is>
-          <t>恒丰银行股份有限公司,中国民生银行股份有限公司</t>
+          <t>平安银行股份有限公司,兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD88" s="3"/>
@@ -20661,7 +20661,7 @@
       </c>
       <c r="AF88" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG88" s="3" t="inlineStr">
@@ -20671,7 +20671,7 @@
       </c>
       <c r="AH88" s="3" t="inlineStr">
         <is>
-          <t>烟台国丰投资控股集团有限公司2026年度第四期中期票据(品种二)</t>
+          <t>一汽租赁有限公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI88" s="3" t="inlineStr">
@@ -20681,7 +20681,7 @@
       </c>
       <c r="AJ88" s="3" t="inlineStr">
         <is>
-          <t>2031-08-26</t>
+          <t>2028-08-25</t>
         </is>
       </c>
       <c r="AK88" s="3"/>
@@ -20702,7 +20702,7 @@
       </c>
       <c r="AO88" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP88" s="3" t="inlineStr">
@@ -20712,22 +20712,22 @@
       </c>
       <c r="AQ88" s="3" t="inlineStr">
         <is>
-          <t>化工制造</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR88" s="3" t="inlineStr">
         <is>
-          <t>化学制品</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AS88" s="3" t="inlineStr">
         <is>
-          <t>化学制品</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AT88" s="3" t="inlineStr">
         <is>
-          <t>化学制品</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU88" s="3" t="inlineStr">
@@ -20760,7 +20760,7 @@
     <row r="89" customHeight="true" ht="18.0">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>26一汽租赁MTN003</t>
+          <t>26华能水电GN012</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -20770,64 +20770,64 @@
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>102683354.IB</t>
+          <t>132680089.IB</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E89" s="4" t="n">
-        <v>15.0</v>
+        <v>10.0</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>15.0</v>
+        <v>10.0</v>
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.66</t>
+          <t>1.70 ~ 2.10</t>
         </is>
       </c>
       <c r="H89" s="4" t="n">
-        <v>1.66</v>
+        <v>1.88</v>
       </c>
       <c r="I89" s="4" t="n">
-        <v>42.39</v>
+        <v>49.28</v>
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>26一汽租赁MTN002</t>
+          <t>26华能水电GN010</t>
         </is>
       </c>
       <c r="L89" s="3" t="inlineStr">
         <is>
-          <t>1.75Y</t>
+          <t>4.88Y+N</t>
         </is>
       </c>
       <c r="M89" s="3" t="inlineStr">
         <is>
-          <t>1.6648</t>
+          <t>1.8930</t>
         </is>
       </c>
       <c r="N89" s="3" t="inlineStr">
         <is>
-          <t>1.6600/1.6300</t>
+          <t>1.9200/--</t>
         </is>
       </c>
       <c r="O89" s="3" t="inlineStr">
         <is>
-          <t>一汽租赁有限公司</t>
+          <t>华能澜沧江水电股份有限公司</t>
         </is>
       </c>
       <c r="P89" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.90</t>
+          <t>C- 20.27</t>
         </is>
       </c>
       <c r="Q89" s="3" t="inlineStr">
@@ -20851,17 +20851,19 @@
         </is>
       </c>
       <c r="U89" s="4" t="n">
-        <v>0.4067</v>
-      </c>
-      <c r="V89" s="3"/>
+        <v>3.18</v>
+      </c>
+      <c r="V89" s="4" t="n">
+        <v>2.79</v>
+      </c>
       <c r="W89" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X89" s="3" t="inlineStr">
         <is>
-          <t>1.61%~1.71%</t>
+          <t>1.85%~1.95%</t>
         </is>
       </c>
       <c r="Y89" s="3" t="inlineStr">
@@ -20872,17 +20874,17 @@
       <c r="Z89" s="3"/>
       <c r="AA89" s="3" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>云南省-昆明市</t>
         </is>
       </c>
       <c r="AB89" s="3" t="inlineStr">
         <is>
-          <t>发行人本期发行中期票据15亿元,本期募集资金15亿元全部用于偿还有息债务</t>
+          <t>本期绿色中期票据拟发行金额10亿元,募集资金将用于偿还26华能水电GN005(乡村振兴)的本金。本期募集资金穿透后用于景洪水电站、糯扎渡水电站、黄登水电站、漫湾水电站等4个绿色项目[26华能水电GN005(乡村振兴)]</t>
         </is>
       </c>
       <c r="AC89" s="3" t="inlineStr">
         <is>
-          <t>平安银行股份有限公司,兴业银行股份有限公司</t>
+          <t>中国银行股份有限公司,中国工商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD89" s="3"/>
@@ -20903,7 +20905,7 @@
       </c>
       <c r="AH89" s="3" t="inlineStr">
         <is>
-          <t>一汽租赁有限公司2026年度第三期中期票据</t>
+          <t>华能澜沧江水电股份有限公司2026年度第十二期绿色中期票据</t>
         </is>
       </c>
       <c r="AI89" s="3" t="inlineStr">
@@ -20913,7 +20915,7 @@
       </c>
       <c r="AJ89" s="3" t="inlineStr">
         <is>
-          <t>2028-08-25</t>
+          <t>2031-08-26</t>
         </is>
       </c>
       <c r="AK89" s="3"/>
@@ -20934,32 +20936,32 @@
       </c>
       <c r="AO89" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP89" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AQ89" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR89" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AS89" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>水电</t>
         </is>
       </c>
       <c r="AT89" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU89" s="3" t="inlineStr">
@@ -20974,12 +20976,12 @@
       </c>
       <c r="AW89" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX89" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY89" s="3" t="inlineStr">
@@ -20992,7 +20994,7 @@
     <row r="90" customHeight="true" ht="18.0">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>26华能水电GN012</t>
+          <t>26中交投SCP003</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -21002,12 +21004,12 @@
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>132680089.IB</t>
+          <t>012682144.IB</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>0.31Y</t>
         </is>
       </c>
       <c r="E90" s="4" t="n">
@@ -21018,48 +21020,48 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.10</t>
+          <t>1.30 ~ 1.55</t>
         </is>
       </c>
       <c r="H90" s="4" t="n">
-        <v>1.88</v>
+        <v>1.39</v>
       </c>
       <c r="I90" s="4" t="n">
-        <v>49.28</v>
+        <v>20.17</v>
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="K90" s="3" t="inlineStr">
         <is>
-          <t>26华能水电GN010</t>
+          <t>26中交投SCP002</t>
         </is>
       </c>
       <c r="L90" s="3" t="inlineStr">
         <is>
-          <t>4.88Y+N</t>
+          <t>108D</t>
         </is>
       </c>
       <c r="M90" s="3" t="inlineStr">
         <is>
-          <t>1.8930</t>
+          <t>1.5156</t>
         </is>
       </c>
       <c r="N90" s="3" t="inlineStr">
         <is>
-          <t>1.9200/--</t>
+          <t>1.5100/1.5000</t>
         </is>
       </c>
       <c r="O90" s="3" t="inlineStr">
         <is>
-          <t>华能澜沧江水电股份有限公司</t>
+          <t>中交投资有限公司</t>
         </is>
       </c>
       <c r="P90" s="3" t="inlineStr">
         <is>
-          <t>C- 20.27</t>
+          <t>C- 24.55</t>
         </is>
       </c>
       <c r="Q90" s="3" t="inlineStr">
@@ -21083,11 +21085,9 @@
         </is>
       </c>
       <c r="U90" s="4" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="V90" s="4" t="n">
-        <v>2.79</v>
-      </c>
+        <v>2.38</v>
+      </c>
+      <c r="V90" s="3"/>
       <c r="W90" s="3" t="inlineStr">
         <is>
           <t>3</t>
@@ -21095,7 +21095,7 @@
       </c>
       <c r="X90" s="3" t="inlineStr">
         <is>
-          <t>1.85%~1.95%</t>
+          <t>1.52%~1.56%</t>
         </is>
       </c>
       <c r="Y90" s="3" t="inlineStr">
@@ -21106,23 +21106,23 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3" t="inlineStr">
         <is>
-          <t>云南省-昆明市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB90" s="3" t="inlineStr">
         <is>
-          <t>本期绿色中期票据拟发行金额10亿元,募集资金将用于偿还26华能水电GN005(乡村振兴)的本金。本期募集资金穿透后用于景洪水电站、糯扎渡水电站、黄登水电站、漫湾水电站等4个绿色项目[26华能水电GN005(乡村振兴)]</t>
+          <t>本期超短期融资券发行规模为10亿元,拟全部用于偿还发行人有息债务。</t>
         </is>
       </c>
       <c r="AC90" s="3" t="inlineStr">
         <is>
-          <t>中国银行股份有限公司,中国工商银行股份有限公司</t>
+          <t>广发银行股份有限公司,杭州银行股份有限公司</t>
         </is>
       </c>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF90" s="3" t="inlineStr">
@@ -21137,7 +21137,7 @@
       </c>
       <c r="AH90" s="3" t="inlineStr">
         <is>
-          <t>华能澜沧江水电股份有限公司2026年度第十二期绿色中期票据</t>
+          <t>中交投资有限公司2026年度第三期超短期融资券</t>
         </is>
       </c>
       <c r="AI90" s="3" t="inlineStr">
@@ -21147,7 +21147,7 @@
       </c>
       <c r="AJ90" s="3" t="inlineStr">
         <is>
-          <t>2031-08-26</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="AK90" s="3"/>
@@ -21173,27 +21173,27 @@
       </c>
       <c r="AP90" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ90" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>建筑施工</t>
         </is>
       </c>
       <c r="AR90" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>专业工程</t>
         </is>
       </c>
       <c r="AS90" s="3" t="inlineStr">
         <is>
-          <t>水电</t>
+          <t>其他专业工程</t>
         </is>
       </c>
       <c r="AT90" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU90" s="3" t="inlineStr">
@@ -21208,12 +21208,12 @@
       </c>
       <c r="AW90" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX90" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY90" s="3" t="inlineStr">
@@ -21221,79 +21221,81 @@
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="AZ90" s="3"/>
+      <c r="AZ90" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="91" customHeight="true" ht="18.0">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>26中交投SCP003</t>
+          <t>26华为MTN004</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>08-25 18:00</t>
+          <t>08-26 18:00</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>012682144.IB</t>
+          <t>102683368.IB</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>0.31Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E91" s="4" t="n">
-        <v>10.0</v>
+        <v>40.0</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>10.0</v>
+        <v>40.0</v>
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.55</t>
+          <t>1.35 ~ 1.95</t>
         </is>
       </c>
       <c r="H91" s="4" t="n">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="I91" s="4" t="n">
-        <v>20.17</v>
+        <v>23.61</v>
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="K91" s="3" t="inlineStr">
         <is>
-          <t>26中交投SCP002</t>
+          <t>26华为MTN003</t>
         </is>
       </c>
       <c r="L91" s="3" t="inlineStr">
         <is>
-          <t>108D</t>
+          <t>2.98Y</t>
         </is>
       </c>
       <c r="M91" s="3" t="inlineStr">
         <is>
-          <t>1.5156</t>
+          <t>1.6621</t>
         </is>
       </c>
       <c r="N91" s="3" t="inlineStr">
         <is>
-          <t>1.5100/1.5000</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O91" s="3" t="inlineStr">
         <is>
-          <t>中交投资有限公司</t>
+          <t>华为投资控股有限公司</t>
         </is>
       </c>
       <c r="P91" s="3" t="inlineStr">
         <is>
-          <t>C- 24.55</t>
+          <t>C+ 32.62</t>
         </is>
       </c>
       <c r="Q91" s="3" t="inlineStr">
@@ -21313,13 +21315,15 @@
       </c>
       <c r="T91" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="U91" s="4" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="V91" s="3"/>
+        <v>2.67</v>
+      </c>
+      <c r="V91" s="4" t="n">
+        <v>1.52</v>
+      </c>
       <c r="W91" s="3" t="inlineStr">
         <is>
           <t>3</t>
@@ -21327,7 +21331,7 @@
       </c>
       <c r="X91" s="3" t="inlineStr">
         <is>
-          <t>1.52%~1.56%</t>
+          <t>1.60%~1.70%</t>
         </is>
       </c>
       <c r="Y91" s="3" t="inlineStr">
@@ -21338,28 +21342,28 @@
       <c r="Z91" s="3"/>
       <c r="AA91" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB91" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行规模为10亿元,拟全部用于偿还发行人有息债务。</t>
+          <t>公司本次拟发行40亿元中期票据,将用于补充公司本部及下属子公司营运资金</t>
         </is>
       </c>
       <c r="AC91" s="3" t="inlineStr">
         <is>
-          <t>广发银行股份有限公司,杭州银行股份有限公司</t>
+          <t>中国银行股份有限公司,中国工商银行股份有限公司,中国建设银行股份有限公司</t>
         </is>
       </c>
       <c r="AD91" s="3"/>
       <c r="AE91" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF91" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG91" s="3" t="inlineStr">
@@ -21369,7 +21373,7 @@
       </c>
       <c r="AH91" s="3" t="inlineStr">
         <is>
-          <t>中交投资有限公司2026年度第三期超短期融资券</t>
+          <t>华为投资控股有限公司2026年度第四期中期票据</t>
         </is>
       </c>
       <c r="AI91" s="3" t="inlineStr">
@@ -21379,88 +21383,86 @@
       </c>
       <c r="AJ91" s="3" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2029-08-27</t>
         </is>
       </c>
       <c r="AK91" s="3"/>
       <c r="AL91" s="3" t="inlineStr">
         <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AM91" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AN91" s="3" t="inlineStr">
+        <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="AM91" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="AN91" s="3" t="inlineStr">
+      <c r="AO91" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP91" s="3" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="AQ91" s="3" t="inlineStr">
+        <is>
+          <t>电子设备制造</t>
+        </is>
+      </c>
+      <c r="AR91" s="3" t="inlineStr">
+        <is>
+          <t>综合电子设备</t>
+        </is>
+      </c>
+      <c r="AS91" s="3" t="inlineStr">
+        <is>
+          <t>综合电子设备</t>
+        </is>
+      </c>
+      <c r="AT91" s="3" t="inlineStr">
+        <is>
+          <t>计算机设备</t>
+        </is>
+      </c>
+      <c r="AU91" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV91" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW91" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX91" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY91" s="3" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="AO91" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP91" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AQ91" s="3" t="inlineStr">
-        <is>
-          <t>建筑施工</t>
-        </is>
-      </c>
-      <c r="AR91" s="3" t="inlineStr">
-        <is>
-          <t>专业工程</t>
-        </is>
-      </c>
-      <c r="AS91" s="3" t="inlineStr">
-        <is>
-          <t>其他专业工程</t>
-        </is>
-      </c>
-      <c r="AT91" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU91" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AV91" s="3" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AW91" s="3" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AX91" s="3" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AY91" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="AZ91" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ91" s="3"/>
     </row>
     <row r="92" customHeight="true" ht="18.0">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>26华为MTN004</t>
+          <t>26信阳建投MTN003</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -21470,49 +21472,49 @@
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>102683368.IB</t>
+          <t>102683365.IB</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E92" s="4" t="n">
-        <v>40.0</v>
+        <v>6.0</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>40.0</v>
+        <v>6.0</v>
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>1.35 ~ 1.95</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H92" s="4" t="n">
-        <v>1.5</v>
+        <v>1.79</v>
       </c>
       <c r="I92" s="4" t="n">
-        <v>23.61</v>
+        <v>53.95</v>
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="K92" s="3" t="inlineStr">
         <is>
-          <t>26华为MTN003</t>
+          <t>24信阳建投MTN002</t>
         </is>
       </c>
       <c r="L92" s="3" t="inlineStr">
         <is>
-          <t>2.98Y</t>
+          <t>2.66Y</t>
         </is>
       </c>
       <c r="M92" s="3" t="inlineStr">
         <is>
-          <t>1.6621</t>
+          <t>1.9127</t>
         </is>
       </c>
       <c r="N92" s="3" t="inlineStr">
@@ -21522,12 +21524,12 @@
       </c>
       <c r="O92" s="3" t="inlineStr">
         <is>
-          <t>华为投资控股有限公司</t>
+          <t>信阳建投投资集团有限责任公司</t>
         </is>
       </c>
       <c r="P92" s="3" t="inlineStr">
         <is>
-          <t>C+ 32.62</t>
+          <t>B- 44.25</t>
         </is>
       </c>
       <c r="Q92" s="3" t="inlineStr">
@@ -21551,40 +21553,40 @@
         </is>
       </c>
       <c r="U92" s="4" t="n">
-        <v>2.67</v>
+        <v>4.375</v>
       </c>
       <c r="V92" s="4" t="n">
-        <v>1.52</v>
+        <v>1.538</v>
       </c>
       <c r="W92" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X92" s="3" t="inlineStr">
         <is>
-          <t>1.60%~1.70%</t>
+          <t>1.84%~1.94%</t>
         </is>
       </c>
       <c r="Y92" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z92" s="3"/>
       <c r="AA92" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>河南省-信阳市</t>
         </is>
       </c>
       <c r="AB92" s="3" t="inlineStr">
         <is>
-          <t>公司本次拟发行40亿元中期票据,将用于补充公司本部及下属子公司营运资金</t>
+          <t>本期中期票据发行金额上限6.00亿元,基础发行规模0.00亿元,拟全部用于偿还债务融资工具。[23信阳建投MTN007]</t>
         </is>
       </c>
       <c r="AC92" s="3" t="inlineStr">
         <is>
-          <t>中国银行股份有限公司,中国工商银行股份有限公司,中国建设银行股份有限公司</t>
+          <t>中信银行股份有限公司,中信建投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD92" s="3"/>
@@ -21595,7 +21597,7 @@
       </c>
       <c r="AF92" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG92" s="3" t="inlineStr">
@@ -21605,7 +21607,7 @@
       </c>
       <c r="AH92" s="3" t="inlineStr">
         <is>
-          <t>华为投资控股有限公司2026年度第四期中期票据</t>
+          <t>信阳建投投资集团有限责任公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI92" s="3" t="inlineStr">
@@ -21615,10 +21617,14 @@
       </c>
       <c r="AJ92" s="3" t="inlineStr">
         <is>
-          <t>2029-08-27</t>
-        </is>
-      </c>
-      <c r="AK92" s="3"/>
+          <t>2028-08-27</t>
+        </is>
+      </c>
+      <c r="AK92" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL92" s="3" t="inlineStr">
         <is>
           <t>2026-08-28</t>
@@ -21636,32 +21642,32 @@
       </c>
       <c r="AO92" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP92" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ92" s="3" t="inlineStr">
         <is>
-          <t>电子设备制造</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR92" s="3" t="inlineStr">
         <is>
-          <t>综合电子设备</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS92" s="3" t="inlineStr">
         <is>
-          <t>综合电子设备</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT92" s="3" t="inlineStr">
         <is>
-          <t>计算机设备</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU92" s="3" t="inlineStr">
@@ -21694,7 +21700,7 @@
     <row r="93" customHeight="true" ht="18.0">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>26信阳建投MTN003</t>
+          <t>26威高MTN003(科创债)</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -21704,39 +21710,39 @@
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>102683365.IB</t>
+          <t>102683369.IB</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E93" s="4" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>2.40 ~ 3.00</t>
         </is>
       </c>
       <c r="H93" s="4" t="n">
-        <v>1.79</v>
+        <v>2.9</v>
       </c>
       <c r="I93" s="4" t="n">
-        <v>53.95</v>
+        <v>150.16</v>
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="K93" s="3" t="inlineStr">
         <is>
-          <t>24信阳建投MTN002</t>
+          <t>26威高MTN002(科创债)</t>
         </is>
       </c>
       <c r="L93" s="3" t="inlineStr">
@@ -21746,22 +21752,22 @@
       </c>
       <c r="M93" s="3" t="inlineStr">
         <is>
-          <t>1.9127</t>
+          <t>2.7328</t>
         </is>
       </c>
       <c r="N93" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/2.7000</t>
         </is>
       </c>
       <c r="O93" s="3" t="inlineStr">
         <is>
-          <t>信阳建投投资集团有限责任公司</t>
+          <t>威高集团有限公司</t>
         </is>
       </c>
       <c r="P93" s="3" t="inlineStr">
         <is>
-          <t>B- 44.25</t>
+          <t>D- 2.60</t>
         </is>
       </c>
       <c r="Q93" s="3" t="inlineStr">
@@ -21784,20 +21790,16 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="U93" s="4" t="n">
-        <v>4.375</v>
-      </c>
-      <c r="V93" s="4" t="n">
-        <v>1.538</v>
-      </c>
+      <c r="U93" s="3"/>
+      <c r="V93" s="3"/>
       <c r="W93" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X93" s="3" t="inlineStr">
         <is>
-          <t>1.84%~1.94%</t>
+          <t>3.10%~3.20%</t>
         </is>
       </c>
       <c r="Y93" s="3" t="inlineStr">
@@ -21808,17 +21810,17 @@
       <c r="Z93" s="3"/>
       <c r="AA93" s="3" t="inlineStr">
         <is>
-          <t>河南省-信阳市</t>
+          <t>山东省-威海市</t>
         </is>
       </c>
       <c r="AB93" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额上限6.00亿元,基础发行规模0.00亿元,拟全部用于偿还债务融资工具。[23信阳建投MTN007]</t>
+          <t>本次中期票据发行规模不超过人民币5亿元,用途为偿还有息债务</t>
         </is>
       </c>
       <c r="AC93" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,中信建投证券股份有限公司</t>
+          <t>招商银行股份有限公司,青岛银行股份有限公司,中信银行股份有限公司,华夏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD93" s="3"/>
@@ -21829,7 +21831,7 @@
       </c>
       <c r="AF93" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG93" s="3" t="inlineStr">
@@ -21839,7 +21841,7 @@
       </c>
       <c r="AH93" s="3" t="inlineStr">
         <is>
-          <t>信阳建投投资集团有限责任公司2026年度第三期中期票据</t>
+          <t>威高集团有限公司2026年度第三期科技创新债券</t>
         </is>
       </c>
       <c r="AI93" s="3" t="inlineStr">
@@ -21849,14 +21851,10 @@
       </c>
       <c r="AJ93" s="3" t="inlineStr">
         <is>
-          <t>2028-08-27</t>
-        </is>
-      </c>
-      <c r="AK93" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-08-27</t>
+        </is>
+      </c>
+      <c r="AK93" s="3"/>
       <c r="AL93" s="3" t="inlineStr">
         <is>
           <t>2026-08-28</t>
@@ -21874,32 +21872,32 @@
       </c>
       <c r="AO93" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP93" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AQ93" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>医药制造</t>
         </is>
       </c>
       <c r="AR93" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>医疗器械制造</t>
         </is>
       </c>
       <c r="AS93" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>医疗器械制造</t>
         </is>
       </c>
       <c r="AT93" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>医疗器械</t>
         </is>
       </c>
       <c r="AU93" s="3" t="inlineStr">
@@ -21932,7 +21930,7 @@
     <row r="94" customHeight="true" ht="18.0">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>26威高MTN003(科创债)</t>
+          <t>26皖投集MTN004</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -21942,12 +21940,12 @@
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>102683369.IB</t>
+          <t>102683367.IB</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>30Y</t>
         </is>
       </c>
       <c r="E94" s="4" t="n">
@@ -21958,101 +21956,103 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2.40 ~ 3.00</t>
+          <t>2.30 ~ 2.70</t>
         </is>
       </c>
       <c r="H94" s="4" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="I94" s="4" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>2.36</t>
+        </is>
+      </c>
+      <c r="K94" s="3" t="inlineStr">
+        <is>
+          <t>25皖投集MTN004(科创债)</t>
+        </is>
+      </c>
+      <c r="L94" s="3" t="inlineStr">
+        <is>
+          <t>19.23Y</t>
+        </is>
+      </c>
+      <c r="M94" s="3" t="inlineStr">
+        <is>
+          <t>2.3597</t>
+        </is>
+      </c>
+      <c r="N94" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O94" s="3" t="inlineStr">
+        <is>
+          <t>安徽省投资集团控股有限公司</t>
+        </is>
+      </c>
+      <c r="P94" s="3" t="inlineStr">
+        <is>
+          <t>C 25.20</t>
+        </is>
+      </c>
+      <c r="Q94" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="R94" s="3" t="inlineStr">
+        <is>
+          <t>08-25 09:00</t>
+        </is>
+      </c>
+      <c r="S94" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="T94" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="U94" s="4" t="n">
         <v>2.9</v>
       </c>
-      <c r="I94" s="4" t="n">
-        <v>150.16</v>
-      </c>
-      <c r="J94" s="3" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="K94" s="3" t="inlineStr">
-        <is>
-          <t>26威高MTN002(科创债)</t>
-        </is>
-      </c>
-      <c r="L94" s="3" t="inlineStr">
-        <is>
-          <t>2.66Y</t>
-        </is>
-      </c>
-      <c r="M94" s="3" t="inlineStr">
-        <is>
-          <t>2.7328</t>
-        </is>
-      </c>
-      <c r="N94" s="3" t="inlineStr">
-        <is>
-          <t>--/2.7000</t>
-        </is>
-      </c>
-      <c r="O94" s="3" t="inlineStr">
-        <is>
-          <t>威高集团有限公司</t>
-        </is>
-      </c>
-      <c r="P94" s="3" t="inlineStr">
-        <is>
-          <t>D- 2.60</t>
-        </is>
-      </c>
-      <c r="Q94" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="R94" s="3" t="inlineStr">
-        <is>
-          <t>08-25 09:00</t>
-        </is>
-      </c>
-      <c r="S94" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="T94" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="U94" s="3"/>
       <c r="V94" s="3"/>
       <c r="W94" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X94" s="3" t="inlineStr">
         <is>
-          <t>3.10%~3.20%</t>
+          <t>3.92%~4.02%</t>
         </is>
       </c>
       <c r="Y94" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z94" s="3"/>
       <c r="AA94" s="3" t="inlineStr">
         <is>
-          <t>山东省-威海市</t>
+          <t>安徽省</t>
         </is>
       </c>
       <c r="AB94" s="3" t="inlineStr">
         <is>
-          <t>本次中期票据发行规模不超过人民币5亿元,用途为偿还有息债务</t>
+          <t>本期中期票据募集资金5亿元人民币，其中3亿元用于公司本部偿还金融机构借款，其余2亿元用于偿还发行人即将到期的债券[25皖投集SCP001]</t>
         </is>
       </c>
       <c r="AC94" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司,青岛银行股份有限公司,中信银行股份有限公司,华夏银行股份有限公司</t>
+          <t>招商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD94" s="3"/>
@@ -22063,7 +22063,7 @@
       </c>
       <c r="AF94" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG94" s="3" t="inlineStr">
@@ -22073,7 +22073,7 @@
       </c>
       <c r="AH94" s="3" t="inlineStr">
         <is>
-          <t>威高集团有限公司2026年度第三期科技创新债券</t>
+          <t>安徽省投资集团控股有限公司2026年度第四期中期票据</t>
         </is>
       </c>
       <c r="AI94" s="3" t="inlineStr">
@@ -22083,10 +22083,14 @@
       </c>
       <c r="AJ94" s="3" t="inlineStr">
         <is>
-          <t>2031-08-27</t>
-        </is>
-      </c>
-      <c r="AK94" s="3"/>
+          <t>2056-08-27</t>
+        </is>
+      </c>
+      <c r="AK94" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL94" s="3" t="inlineStr">
         <is>
           <t>2026-08-28</t>
@@ -22104,32 +22108,32 @@
       </c>
       <c r="AO94" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP94" s="3" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ94" s="3" t="inlineStr">
         <is>
-          <t>医药制造</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR94" s="3" t="inlineStr">
         <is>
-          <t>医疗器械制造</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS94" s="3" t="inlineStr">
         <is>
-          <t>医疗器械制造</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT94" s="3" t="inlineStr">
         <is>
-          <t>医疗器械</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU94" s="3" t="inlineStr">
@@ -22162,59 +22166,59 @@
     <row r="95" customHeight="true" ht="18.0">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>26皖投集MTN004</t>
+          <t>青铁KY03</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>08-26 18:00</t>
+          <t>08-25 19:00</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>102683367.IB</t>
+          <t>245920.SH</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>30Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E95" s="4" t="n">
         <v>5.0</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2.30 ~ 2.70</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H95" s="4" t="n">
-        <v>2.49</v>
+        <v>1.79</v>
       </c>
       <c r="I95" s="4" t="n">
-        <v>35.6</v>
+        <v>53.67</v>
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="K95" s="3" t="inlineStr">
         <is>
-          <t>25皖投集MTN004(科创债)</t>
+          <t>青铁KY01</t>
         </is>
       </c>
       <c r="L95" s="3" t="inlineStr">
         <is>
-          <t>19.23Y</t>
+          <t>2.54Y+N</t>
         </is>
       </c>
       <c r="M95" s="3" t="inlineStr">
         <is>
-          <t>2.3597</t>
+          <t>1.8085</t>
         </is>
       </c>
       <c r="N95" s="3" t="inlineStr">
@@ -22224,12 +22228,12 @@
       </c>
       <c r="O95" s="3" t="inlineStr">
         <is>
-          <t>安徽省投资集团控股有限公司</t>
+          <t>青岛地铁集团有限公司</t>
         </is>
       </c>
       <c r="P95" s="3" t="inlineStr">
         <is>
-          <t>C 25.20</t>
+          <t>B- 37.20</t>
         </is>
       </c>
       <c r="Q95" s="3" t="inlineStr">
@@ -22239,7 +22243,7 @@
       </c>
       <c r="R95" s="3" t="inlineStr">
         <is>
-          <t>08-25 09:00</t>
+          <t>08-25 15:00</t>
         </is>
       </c>
       <c r="S95" s="3" t="inlineStr">
@@ -22253,17 +22257,17 @@
         </is>
       </c>
       <c r="U95" s="4" t="n">
-        <v>2.9</v>
+        <v>4.77</v>
       </c>
       <c r="V95" s="3"/>
       <c r="W95" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X95" s="3" t="inlineStr">
         <is>
-          <t>3.92%~4.02%</t>
+          <t>1.77%~1.87%</t>
         </is>
       </c>
       <c r="Y95" s="3" t="inlineStr">
@@ -22274,23 +22278,23 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3" t="inlineStr">
         <is>
-          <t>安徽省</t>
+          <t>山东省-青岛市</t>
         </is>
       </c>
       <c r="AB95" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据募集资金5亿元人民币，其中3亿元用于公司本部偿还金融机构借款，其余2亿元用于偿还发行人即将到期的债券[25皖投集SCP001]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟用于偿还有息债务。[25青铁Y2]</t>
         </is>
       </c>
       <c r="AC95" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司</t>
+          <t>中国国际金融股份有限公司,中信证券股份有限公司,华泰联合证券有限责任公司,广发证券股份有限公司,国投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF95" s="3" t="inlineStr">
@@ -22300,12 +22304,12 @@
       </c>
       <c r="AG95" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH95" s="3" t="inlineStr">
         <is>
-          <t>安徽省投资集团控股有限公司2026年度第四期中期票据</t>
+          <t>青岛地铁集团有限公司2026年面向专业投资者公开发行科技创新可续期公司债券(第二期)(品种一)</t>
         </is>
       </c>
       <c r="AI95" s="3" t="inlineStr">
@@ -22315,22 +22319,18 @@
       </c>
       <c r="AJ95" s="3" t="inlineStr">
         <is>
-          <t>2056-08-27</t>
-        </is>
-      </c>
-      <c r="AK95" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-08-27</t>
+        </is>
+      </c>
+      <c r="AK95" s="3"/>
       <c r="AL95" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t/>
         </is>
       </c>
       <c r="AM95" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AN95" s="3" t="inlineStr">
@@ -22350,24 +22350,24 @@
       </c>
       <c r="AQ95" s="3" t="inlineStr">
         <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR95" s="3" t="inlineStr">
+        <is>
+          <t>轨道交通</t>
+        </is>
+      </c>
+      <c r="AS95" s="3" t="inlineStr">
+        <is>
+          <t>轨道交通</t>
+        </is>
+      </c>
+      <c r="AT95" s="3" t="inlineStr">
+        <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="AR95" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS95" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AT95" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
       <c r="AU95" s="3" t="inlineStr">
         <is>
           <t/>
@@ -22380,7 +22380,7 @@
       </c>
       <c r="AW95" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX95" s="3" t="inlineStr">
@@ -22390,7 +22390,7 @@
       </c>
       <c r="AY95" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AZ95" s="3"/>
@@ -22398,7 +22398,7 @@
     <row r="96" customHeight="true" ht="18.0">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>青铁KY03</t>
+          <t>青铁KY04</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -22408,49 +22408,49 @@
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>245920.SH</t>
+          <t>245921.SH</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E96" s="4" t="n">
         <v>5.0</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H96" s="4" t="n">
-        <v>1.79</v>
+        <v>1.93</v>
       </c>
       <c r="I96" s="4" t="n">
-        <v>53.67</v>
+        <v>54.28</v>
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="K96" s="3" t="inlineStr">
         <is>
-          <t>青铁KY01</t>
+          <t>青铁KY02</t>
         </is>
       </c>
       <c r="L96" s="3" t="inlineStr">
         <is>
-          <t>2.54Y+N</t>
+          <t>4.54Y+N</t>
         </is>
       </c>
       <c r="M96" s="3" t="inlineStr">
         <is>
-          <t>1.8085</t>
+          <t>1.9129</t>
         </is>
       </c>
       <c r="N96" s="3" t="inlineStr">
@@ -22489,7 +22489,7 @@
         </is>
       </c>
       <c r="U96" s="4" t="n">
-        <v>4.77</v>
+        <v>5.68</v>
       </c>
       <c r="V96" s="3"/>
       <c r="W96" s="3" t="inlineStr">
@@ -22499,7 +22499,7 @@
       </c>
       <c r="X96" s="3" t="inlineStr">
         <is>
-          <t>1.77%~1.87%</t>
+          <t>1.88%~1.98%</t>
         </is>
       </c>
       <c r="Y96" s="3" t="inlineStr">
@@ -22541,7 +22541,7 @@
       </c>
       <c r="AH96" s="3" t="inlineStr">
         <is>
-          <t>青岛地铁集团有限公司2026年面向专业投资者公开发行科技创新可续期公司债券(第二期)(品种一)</t>
+          <t>青岛地铁集团有限公司2026年面向专业投资者公开发行科技创新可续期公司债券(第二期)(品种二)</t>
         </is>
       </c>
       <c r="AI96" s="3" t="inlineStr">
@@ -22551,7 +22551,7 @@
       </c>
       <c r="AJ96" s="3" t="inlineStr">
         <is>
-          <t>2029-08-27</t>
+          <t>2031-08-27</t>
         </is>
       </c>
       <c r="AK96" s="3"/>
@@ -22630,7 +22630,7 @@
     <row r="97" customHeight="true" ht="18.0">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>青铁KY04</t>
+          <t>26化学K3</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -22640,64 +22640,64 @@
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>245921.SH</t>
+          <t>245897.SH</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E97" s="4" t="n">
-        <v>5.0</v>
+        <v>7.5</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.10 ~ 2.10</t>
         </is>
       </c>
       <c r="H97" s="4" t="n">
-        <v>1.93</v>
+        <v>1.58</v>
       </c>
       <c r="I97" s="4" t="n">
-        <v>54.28</v>
+        <v>32.67</v>
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="K97" s="3" t="inlineStr">
         <is>
-          <t>青铁KY02</t>
+          <t>26化学K1</t>
         </is>
       </c>
       <c r="L97" s="3" t="inlineStr">
         <is>
-          <t>4.54Y+N</t>
+          <t>2.81Y</t>
         </is>
       </c>
       <c r="M97" s="3" t="inlineStr">
         <is>
-          <t>1.9129</t>
+          <t>1.6442</t>
         </is>
       </c>
       <c r="N97" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6900/--</t>
         </is>
       </c>
       <c r="O97" s="3" t="inlineStr">
         <is>
-          <t>青岛地铁集团有限公司</t>
+          <t>中国化学工程集团有限公司</t>
         </is>
       </c>
       <c r="P97" s="3" t="inlineStr">
         <is>
-          <t>B- 37.20</t>
+          <t>C- 24.39</t>
         </is>
       </c>
       <c r="Q97" s="3" t="inlineStr">
@@ -22707,7 +22707,7 @@
       </c>
       <c r="R97" s="3" t="inlineStr">
         <is>
-          <t>08-25 15:00</t>
+          <t>08-25 16:00</t>
         </is>
       </c>
       <c r="S97" s="3" t="inlineStr">
@@ -22721,17 +22721,17 @@
         </is>
       </c>
       <c r="U97" s="4" t="n">
-        <v>5.68</v>
+        <v>4.37</v>
       </c>
       <c r="V97" s="3"/>
       <c r="W97" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X97" s="3" t="inlineStr">
         <is>
-          <t>1.88%~1.98%</t>
+          <t>1.60%~1.70%</t>
         </is>
       </c>
       <c r="Y97" s="3" t="inlineStr">
@@ -22739,20 +22739,24 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z97" s="3"/>
+      <c r="Z97" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA97" s="3" t="inlineStr">
         <is>
-          <t>山东省-青岛市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB97" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟用于偿还有息债务。[25青铁Y2]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟将用于生产性支出,包括项目建设、偿还有息债务、补充流动资金或其他符合法律法规的用途。</t>
         </is>
       </c>
       <c r="AC97" s="3" t="inlineStr">
         <is>
-          <t>中国国际金融股份有限公司,中信证券股份有限公司,华泰联合证券有限责任公司,广发证券股份有限公司,国投证券股份有限公司</t>
+          <t>中信证券股份有限公司,中信建投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD97" s="3"/>
@@ -22763,7 +22767,7 @@
       </c>
       <c r="AF97" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>中央国有企业</t>
         </is>
       </c>
       <c r="AG97" s="3" t="inlineStr">
@@ -22773,7 +22777,7 @@
       </c>
       <c r="AH97" s="3" t="inlineStr">
         <is>
-          <t>青岛地铁集团有限公司2026年面向专业投资者公开发行科技创新可续期公司债券(第二期)(品种二)</t>
+          <t>中国化学工程集团有限公司2026年面向专业投资者公开发行科技创新公司债券(第二期)(品种一)</t>
         </is>
       </c>
       <c r="AI97" s="3" t="inlineStr">
@@ -22783,7 +22787,7 @@
       </c>
       <c r="AJ97" s="3" t="inlineStr">
         <is>
-          <t>2031-08-27</t>
+          <t>2029-08-27</t>
         </is>
       </c>
       <c r="AK97" s="3"/>
@@ -22794,7 +22798,7 @@
       </c>
       <c r="AM97" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AN97" s="3" t="inlineStr">
@@ -22804,32 +22808,32 @@
       </c>
       <c r="AO97" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP97" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ97" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>建筑施工</t>
         </is>
       </c>
       <c r="AR97" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>专业工程</t>
         </is>
       </c>
       <c r="AS97" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>其他专业工程</t>
         </is>
       </c>
       <c r="AT97" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>石油化工</t>
         </is>
       </c>
       <c r="AU97" s="3" t="inlineStr">
@@ -22844,7 +22848,7 @@
       </c>
       <c r="AW97" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX97" s="3" t="inlineStr">
@@ -22862,74 +22866,74 @@
     <row r="98" customHeight="true" ht="18.0">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>26化学K3</t>
+          <t>26华阳新材MTN009</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>08-25 19:00</t>
+          <t>08-26 18:00</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>245897.SH</t>
+          <t>102690006.IB</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E98" s="4" t="n">
-        <v>7.5</v>
+        <v>10.0</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>7.0</v>
+        <v>10.0</v>
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>1.10 ~ 2.10</t>
+          <t>1.48 ~ 1.98</t>
         </is>
       </c>
       <c r="H98" s="4" t="n">
-        <v>1.58</v>
+        <v>1.93</v>
       </c>
       <c r="I98" s="4" t="n">
-        <v>32.67</v>
+        <v>66.61</v>
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="K98" s="3" t="inlineStr">
         <is>
-          <t>26化学K1</t>
+          <t>26华阳新材MTN007</t>
         </is>
       </c>
       <c r="L98" s="3" t="inlineStr">
         <is>
-          <t>2.81Y</t>
+          <t>2.82Y+N</t>
         </is>
       </c>
       <c r="M98" s="3" t="inlineStr">
         <is>
-          <t>1.6442</t>
+          <t>1.9637</t>
         </is>
       </c>
       <c r="N98" s="3" t="inlineStr">
         <is>
-          <t>1.6900/--</t>
+          <t>1.9600/--</t>
         </is>
       </c>
       <c r="O98" s="3" t="inlineStr">
         <is>
-          <t>中国化学工程集团有限公司</t>
+          <t>华阳新材料科技集团有限公司</t>
         </is>
       </c>
       <c r="P98" s="3" t="inlineStr">
         <is>
-          <t>C- 24.39</t>
+          <t>C- 23.19</t>
         </is>
       </c>
       <c r="Q98" s="3" t="inlineStr">
@@ -22939,7 +22943,7 @@
       </c>
       <c r="R98" s="3" t="inlineStr">
         <is>
-          <t>08-25 16:00</t>
+          <t>08-25 09:00</t>
         </is>
       </c>
       <c r="S98" s="3" t="inlineStr">
@@ -22952,18 +22956,16 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="U98" s="4" t="n">
-        <v>4.37</v>
-      </c>
+      <c r="U98" s="3"/>
       <c r="V98" s="3"/>
       <c r="W98" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X98" s="3" t="inlineStr">
         <is>
-          <t>1.60%~1.70%</t>
+          <t>1.94%~2.04%</t>
         </is>
       </c>
       <c r="Y98" s="3" t="inlineStr">
@@ -22971,45 +22973,41 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z98" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z98" s="3"/>
       <c r="AA98" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>山西省-阳泉市</t>
         </is>
       </c>
       <c r="AB98" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟将用于生产性支出,包括项目建设、偿还有息债务、补充流动资金或其他符合法律法规的用途。</t>
+          <t>发行人本期中期票据基础发行规模0亿元,发行金额上限10亿元,用于偿还发行人有息债务。</t>
         </is>
       </c>
       <c r="AC98" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,中信建投证券股份有限公司</t>
+          <t>中信证券股份有限公司,国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD98" s="3"/>
       <c r="AE98" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF98" s="3" t="inlineStr">
         <is>
-          <t>中央国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG98" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH98" s="3" t="inlineStr">
         <is>
-          <t>中国化学工程集团有限公司2026年面向专业投资者公开发行科技创新公司债券(第二期)(品种一)</t>
+          <t>华阳新材料科技集团有限公司2026年度第九期中期票据</t>
         </is>
       </c>
       <c r="AI98" s="3" t="inlineStr">
@@ -23025,54 +23023,54 @@
       <c r="AK98" s="3"/>
       <c r="AL98" s="3" t="inlineStr">
         <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AM98" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AN98" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AO98" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP98" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ98" s="3" t="inlineStr">
+        <is>
+          <t>化石能源</t>
+        </is>
+      </c>
+      <c r="AR98" s="3" t="inlineStr">
+        <is>
+          <t>煤炭</t>
+        </is>
+      </c>
+      <c r="AS98" s="3" t="inlineStr">
+        <is>
+          <t>其他煤炭</t>
+        </is>
+      </c>
+      <c r="AT98" s="3" t="inlineStr">
+        <is>
+          <t>煤炭开采</t>
+        </is>
+      </c>
+      <c r="AU98" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM98" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="AN98" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AO98" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP98" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AQ98" s="3" t="inlineStr">
-        <is>
-          <t>建筑施工</t>
-        </is>
-      </c>
-      <c r="AR98" s="3" t="inlineStr">
-        <is>
-          <t>专业工程</t>
-        </is>
-      </c>
-      <c r="AS98" s="3" t="inlineStr">
-        <is>
-          <t>其他专业工程</t>
-        </is>
-      </c>
-      <c r="AT98" s="3" t="inlineStr">
-        <is>
-          <t>石油化工</t>
-        </is>
-      </c>
-      <c r="AU98" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV98" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -23080,7 +23078,7 @@
       </c>
       <c r="AW98" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX98" s="3" t="inlineStr">
@@ -23090,82 +23088,84 @@
       </c>
       <c r="AY98" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="AZ98" s="3"/>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AZ98" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="99" customHeight="true" ht="18.0">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>26华阳新材MTN009</t>
+          <t>26虞交03</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>08-26 18:00</t>
+          <t>08-25 19:00</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>102690006.IB</t>
+          <t>283772.SH</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E99" s="4" t="n">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>1.48 ~ 1.98</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="H99" s="4" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="I99" s="4" t="n">
-        <v>66.61</v>
+        <v>57.28</v>
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="K99" s="3" t="inlineStr">
         <is>
-          <t>26华阳新材MTN007</t>
+          <t>26虞交01</t>
         </is>
       </c>
       <c r="L99" s="3" t="inlineStr">
         <is>
-          <t>2.82Y+N</t>
+          <t>2.66Y+2.00Y</t>
         </is>
       </c>
       <c r="M99" s="3" t="inlineStr">
         <is>
-          <t>1.9637</t>
+          <t>1.7488</t>
         </is>
       </c>
       <c r="N99" s="3" t="inlineStr">
         <is>
-          <t>1.9600/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O99" s="3" t="inlineStr">
         <is>
-          <t>华阳新材料科技集团有限公司</t>
+          <t>绍兴上虞交通集团有限公司</t>
         </is>
       </c>
       <c r="P99" s="3" t="inlineStr">
         <is>
-          <t>C- 23.19</t>
+          <t>C+ 31.25</t>
         </is>
       </c>
       <c r="Q99" s="3" t="inlineStr">
@@ -23175,7 +23175,7 @@
       </c>
       <c r="R99" s="3" t="inlineStr">
         <is>
-          <t>08-25 09:00</t>
+          <t>08-25 16:00</t>
         </is>
       </c>
       <c r="S99" s="3" t="inlineStr">
@@ -23185,46 +23185,48 @@
       </c>
       <c r="T99" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="U99" s="3"/>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="U99" s="4" t="n">
+        <v>2.77</v>
+      </c>
       <c r="V99" s="3"/>
       <c r="W99" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X99" s="3" t="inlineStr">
         <is>
-          <t>1.94%~2.04%</t>
+          <t>1.82%~1.92%</t>
         </is>
       </c>
       <c r="Y99" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z99" s="3"/>
       <c r="AA99" s="3" t="inlineStr">
         <is>
-          <t>山西省-阳泉市</t>
+          <t>浙江省-绍兴市</t>
         </is>
       </c>
       <c r="AB99" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据基础发行规模0亿元,发行金额上限10亿元,用于偿还发行人有息债务。</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟将3亿元用于偿还到期公司债券本金[23虞交02]</t>
         </is>
       </c>
       <c r="AC99" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,国泰海通证券股份有限公司</t>
+          <t>中信证券股份有限公司,天风证券股份有限公司</t>
         </is>
       </c>
       <c r="AD99" s="3"/>
       <c r="AE99" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF99" s="3" t="inlineStr">
@@ -23234,28 +23236,28 @@
       </c>
       <c r="AG99" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH99" s="3" t="inlineStr">
         <is>
-          <t>华阳新材料科技集团有限公司2026年度第九期中期票据</t>
+          <t>绍兴上虞交通集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI99" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ99" s="3" t="inlineStr">
         <is>
-          <t>2029-08-27</t>
+          <t>2031-08-26</t>
         </is>
       </c>
       <c r="AK99" s="3"/>
       <c r="AL99" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AM99" s="3" t="inlineStr">
@@ -23265,37 +23267,37 @@
       </c>
       <c r="AN99" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="AO99" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP99" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ99" s="3" t="inlineStr">
         <is>
-          <t>化石能源</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR99" s="3" t="inlineStr">
         <is>
-          <t>煤炭</t>
+          <t>其他交运基础设施</t>
         </is>
       </c>
       <c r="AS99" s="3" t="inlineStr">
         <is>
-          <t>其他煤炭</t>
+          <t>其他交运基础设施</t>
         </is>
       </c>
       <c r="AT99" s="3" t="inlineStr">
         <is>
-          <t>煤炭开采</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU99" s="3" t="inlineStr">
@@ -23310,7 +23312,7 @@
       </c>
       <c r="AW99" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX99" s="3" t="inlineStr">
@@ -23320,12 +23322,10 @@
       </c>
       <c r="AY99" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="AZ99" s="4" t="n">
-        <v>0.01</v>
-      </c>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AZ99" s="3"/>
     </row>
   </sheetData>
   <mergeCells>

--- a/data/credit_bond_all_2026-08-25.xlsx
+++ b/data/credit_bond_all_2026-08-25.xlsx
@@ -13538,7 +13538,7 @@
     <row r="58" customHeight="true" ht="18.0">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>26核电K4</t>
+          <t>26西经发</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -13548,64 +13548,64 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>245919.SH</t>
+          <t>245975.SH</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E58" s="4" t="n">
-        <v>25.0</v>
+        <v>7.5</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>25.0</v>
+        <v>7.5</v>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>1.10 ~ 2.10</t>
+          <t>2.30 ~ 3.50</t>
         </is>
       </c>
       <c r="H58" s="4" t="n">
-        <v>1.51</v>
+        <v>2.55</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>25.67</v>
+        <v>116.28</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>26核电K3</t>
+          <t>26经发F2</t>
         </is>
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>2.89Y</t>
+          <t>4.91Y</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>1.5902</t>
+          <t>2.8636</t>
         </is>
       </c>
       <c r="N58" s="3" t="inlineStr">
         <is>
-          <t>1.6300/--</t>
+          <t>--/2.6500</t>
         </is>
       </c>
       <c r="O58" s="3" t="inlineStr">
         <is>
-          <t>中国核能电力股份有限公司</t>
+          <t>西安经发集团有限责任公司</t>
         </is>
       </c>
       <c r="P58" s="3" t="inlineStr">
         <is>
-          <t>C 26.25</t>
+          <t>C- 20.04</t>
         </is>
       </c>
       <c r="Q58" s="3" t="inlineStr">
@@ -13629,42 +13629,34 @@
         </is>
       </c>
       <c r="U58" s="4" t="n">
-        <v>3.36</v>
+        <v>2.26</v>
       </c>
       <c r="V58" s="3"/>
       <c r="W58" s="3" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X58" s="3" t="inlineStr">
-        <is>
-          <t>1.56%~1.66%</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X58" s="3"/>
       <c r="Y58" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z58" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z58" s="3"/>
       <c r="AA58" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>陕西省-西安市</t>
         </is>
       </c>
       <c r="AB58" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后将全部用于生产性支出,包括科技创新领域相关支出、偿还公司债务、补充流动资金等符合法律法规要求的用途。</t>
+          <t>本次债券发行规模为7.50亿元,募集资金扣除发行费用后,拟用于偿还到期公司债券本金[21西经发]</t>
         </is>
       </c>
       <c r="AC58" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,华泰联合证券有限责任公司,中国国际金融股份有限公司,国泰海通证券股份有限公司,中信证券股份有限公司</t>
+          <t>天风证券股份有限公司,五矿证券有限公司</t>
         </is>
       </c>
       <c r="AD58" s="3"/>
@@ -13675,7 +13667,7 @@
       </c>
       <c r="AF58" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG58" s="3" t="inlineStr">
@@ -13685,7 +13677,7 @@
       </c>
       <c r="AH58" s="3" t="inlineStr">
         <is>
-          <t>中国核能电力股份有限公司2026年面向专业投资者公开发行科技创新公司债券(第四期)</t>
+          <t>西安经发集团有限责任公司2026年面向专业投资者公开发行公司债券</t>
         </is>
       </c>
       <c r="AI58" s="3" t="inlineStr">
@@ -13695,7 +13687,7 @@
       </c>
       <c r="AJ58" s="3" t="inlineStr">
         <is>
-          <t>2029-08-27</t>
+          <t>2031-08-27</t>
         </is>
       </c>
       <c r="AK58" s="3"/>
@@ -13706,7 +13698,7 @@
       </c>
       <c r="AM58" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AN58" s="3" t="inlineStr">
@@ -13716,32 +13708,32 @@
       </c>
       <c r="AO58" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP58" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AQ58" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR58" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS58" s="3" t="inlineStr">
         <is>
-          <t>核电</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT58" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU58" s="3" t="inlineStr">
@@ -13774,7 +13766,7 @@
     <row r="59" customHeight="true" ht="18.0">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>26西经发</t>
+          <t>26浔交02</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -13784,64 +13776,64 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>245975.SH</t>
+          <t>283756.SH</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>5+2</t>
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>7.5</v>
+        <v>5.2</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>7.5</v>
+        <v>5.2</v>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2.30 ~ 3.50</t>
+          <t>1.80 ~ 2.80</t>
         </is>
       </c>
       <c r="H59" s="4" t="n">
-        <v>2.55</v>
+        <v>2.14</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>116.28</v>
+        <v>62.52</v>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>26经发F2</t>
+          <t>26浔交01</t>
         </is>
       </c>
       <c r="L59" s="3" t="inlineStr">
         <is>
-          <t>4.91Y</t>
+          <t>4.84Y+2.00Y</t>
         </is>
       </c>
       <c r="M59" s="3" t="inlineStr">
         <is>
-          <t>2.8636</t>
+          <t>2.1623</t>
         </is>
       </c>
       <c r="N59" s="3" t="inlineStr">
         <is>
-          <t>--/2.6500</t>
+          <t>2.1700/--</t>
         </is>
       </c>
       <c r="O59" s="3" t="inlineStr">
         <is>
-          <t>西安经发集团有限责任公司</t>
+          <t>湖州市南浔区交通投资集团有限公司</t>
         </is>
       </c>
       <c r="P59" s="3" t="inlineStr">
         <is>
-          <t>C- 20.04</t>
+          <t>C- 13.88</t>
         </is>
       </c>
       <c r="Q59" s="3" t="inlineStr">
@@ -13865,7 +13857,7 @@
         </is>
       </c>
       <c r="U59" s="4" t="n">
-        <v>2.26</v>
+        <v>4.15</v>
       </c>
       <c r="V59" s="3"/>
       <c r="W59" s="3" t="inlineStr">
@@ -13873,7 +13865,11 @@
           <t>7</t>
         </is>
       </c>
-      <c r="X59" s="3"/>
+      <c r="X59" s="3" t="inlineStr">
+        <is>
+          <t>2.15%~2.25%</t>
+        </is>
+      </c>
       <c r="Y59" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -13882,17 +13878,17 @@
       <c r="Z59" s="3"/>
       <c r="AA59" s="3" t="inlineStr">
         <is>
-          <t>陕西省-西安市</t>
+          <t>浙江省-湖州市</t>
         </is>
       </c>
       <c r="AB59" s="3" t="inlineStr">
         <is>
-          <t>本次债券发行规模为7.50亿元,募集资金扣除发行费用后,拟用于偿还到期公司债券本金[21西经发]</t>
+          <t>本期债券募集资金扣除发行费用后,拟用于偿还回售的公司债券本金[23浔交02]</t>
         </is>
       </c>
       <c r="AC59" s="3" t="inlineStr">
         <is>
-          <t>天风证券股份有限公司,五矿证券有限公司</t>
+          <t>东方证券股份有限公司,华鑫证券有限责任公司,浙商证券股份有限公司</t>
         </is>
       </c>
       <c r="AD59" s="3"/>
@@ -13913,70 +13909,74 @@
       </c>
       <c r="AH59" s="3" t="inlineStr">
         <is>
-          <t>西安经发集团有限责任公司2026年面向专业投资者公开发行公司债券</t>
+          <t>湖州市南浔区交通投资集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI59" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ59" s="3" t="inlineStr">
         <is>
+          <t>2033-08-27</t>
+        </is>
+      </c>
+      <c r="AK59" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
+      <c r="AL59" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM59" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AN59" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AO59" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP59" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AQ59" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR59" s="3" t="inlineStr">
+        <is>
+          <t>其他交运基础设施</t>
+        </is>
+      </c>
+      <c r="AS59" s="3" t="inlineStr">
+        <is>
+          <t>其他交运基础设施</t>
+        </is>
+      </c>
+      <c r="AT59" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU59" s="3" t="inlineStr">
+        <is>
           <t>2031-08-27</t>
         </is>
       </c>
-      <c r="AK59" s="3"/>
-      <c r="AL59" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="AM59" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="AN59" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AO59" s="3" t="inlineStr">
-        <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP59" s="3" t="inlineStr">
-        <is>
-          <t>7.5</t>
-        </is>
-      </c>
-      <c r="AQ59" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR59" s="3" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AS59" s="3" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AT59" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU59" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV59" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -13984,7 +13984,7 @@
       </c>
       <c r="AW59" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX59" s="3" t="inlineStr">
@@ -14002,7 +14002,7 @@
     <row r="60" customHeight="true" ht="18.0">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>26浔交02</t>
+          <t>26富港01</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -14012,64 +14012,64 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>283756.SH</t>
+          <t>283735.SH</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>5+2</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E60" s="4" t="n">
-        <v>5.2</v>
+        <v>5.0</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>5.2</v>
+        <v>5.0</v>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.80</t>
+          <t>1.70 ~ 2.50</t>
         </is>
       </c>
       <c r="H60" s="4" t="n">
-        <v>2.14</v>
+        <v>1.83</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>62.52</v>
+        <v>57.67</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>26浔交01</t>
+          <t>25富港01</t>
         </is>
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>4.84Y+2.00Y</t>
+          <t>2.20Y</t>
         </is>
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>2.1623</t>
+          <t>1.8022</t>
         </is>
       </c>
       <c r="N60" s="3" t="inlineStr">
         <is>
-          <t>2.1700/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O60" s="3" t="inlineStr">
         <is>
-          <t>湖州市南浔区交通投资集团有限公司</t>
+          <t>富港建设集团有限公司</t>
         </is>
       </c>
       <c r="P60" s="3" t="inlineStr">
         <is>
-          <t>C- 13.88</t>
+          <t>D+ 8.26</t>
         </is>
       </c>
       <c r="Q60" s="3" t="inlineStr">
@@ -14093,7 +14093,7 @@
         </is>
       </c>
       <c r="U60" s="4" t="n">
-        <v>4.15</v>
+        <v>2.88</v>
       </c>
       <c r="V60" s="3"/>
       <c r="W60" s="3" t="inlineStr">
@@ -14101,33 +14101,33 @@
           <t>7</t>
         </is>
       </c>
-      <c r="X60" s="3" t="inlineStr">
-        <is>
-          <t>2.15%~2.25%</t>
-        </is>
-      </c>
+      <c r="X60" s="3"/>
       <c r="Y60" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z60" s="3"/>
       <c r="AA60" s="3" t="inlineStr">
         <is>
-          <t>浙江省-湖州市</t>
+          <t>江苏省-南通市</t>
         </is>
       </c>
       <c r="AB60" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟用于偿还回售的公司债券本金[23浔交02]</t>
+          <t>本期债券募集资金扣除发行费用后,拟将全部用于偿还即将到期的公司债券本金[23富港01]</t>
         </is>
       </c>
       <c r="AC60" s="3" t="inlineStr">
         <is>
-          <t>东方证券股份有限公司,华鑫证券有限责任公司,浙商证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD60" s="3"/>
+          <t>国泰海通证券股份有限公司,中信建投证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD60" s="3" t="inlineStr">
+        <is>
+          <t>江苏皋开投资发展集团有限公司</t>
+        </is>
+      </c>
       <c r="AE60" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -14145,7 +14145,7 @@
       </c>
       <c r="AH60" s="3" t="inlineStr">
         <is>
-          <t>湖州市南浔区交通投资集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>富港建设集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI60" s="3" t="inlineStr">
@@ -14155,14 +14155,10 @@
       </c>
       <c r="AJ60" s="3" t="inlineStr">
         <is>
-          <t>2033-08-27</t>
-        </is>
-      </c>
-      <c r="AK60" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2029-08-27</t>
+        </is>
+      </c>
+      <c r="AK60" s="3"/>
       <c r="AL60" s="3" t="inlineStr">
         <is>
           <t/>
@@ -14180,12 +14176,12 @@
       </c>
       <c r="AO60" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP60" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AQ60" s="3" t="inlineStr">
@@ -14195,12 +14191,12 @@
       </c>
       <c r="AR60" s="3" t="inlineStr">
         <is>
-          <t>其他交运基础设施</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS60" s="3" t="inlineStr">
         <is>
-          <t>其他交运基础设施</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT60" s="3" t="inlineStr">
@@ -14210,17 +14206,17 @@
       </c>
       <c r="AU60" s="3" t="inlineStr">
         <is>
-          <t>2031-08-27</t>
+          <t/>
         </is>
       </c>
       <c r="AV60" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW60" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX60" s="3" t="inlineStr">
@@ -14238,7 +14234,7 @@
     <row r="61" customHeight="true" ht="18.0">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>26富港01</t>
+          <t>26城铁01</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -14248,49 +14244,49 @@
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>283735.SH</t>
+          <t>283762.SH</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.50</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="H61" s="4" t="n">
-        <v>1.83</v>
+        <v>2.08</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>57.67</v>
+        <v>69.28</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>25富港01</t>
+          <t>25城铁02</t>
         </is>
       </c>
       <c r="L61" s="3" t="inlineStr">
         <is>
-          <t>2.20Y</t>
+          <t>3.87Y</t>
         </is>
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
-          <t>1.8022</t>
+          <t>1.8769</t>
         </is>
       </c>
       <c r="N61" s="3" t="inlineStr">
@@ -14300,12 +14296,12 @@
       </c>
       <c r="O61" s="3" t="inlineStr">
         <is>
-          <t>富港建设集团有限公司</t>
+          <t>无锡沪宁城铁惠山站区投资开发建设有限公司</t>
         </is>
       </c>
       <c r="P61" s="3" t="inlineStr">
         <is>
-          <t>D+ 8.26</t>
+          <t>C- 17.88</t>
         </is>
       </c>
       <c r="Q61" s="3" t="inlineStr">
@@ -14329,15 +14325,19 @@
         </is>
       </c>
       <c r="U61" s="4" t="n">
-        <v>2.88</v>
+        <v>1.65</v>
       </c>
       <c r="V61" s="3"/>
       <c r="W61" s="3" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="X61" s="3"/>
+          <t>6-</t>
+        </is>
+      </c>
+      <c r="X61" s="3" t="inlineStr">
+        <is>
+          <t>1.86%~1.96%</t>
+        </is>
+      </c>
       <c r="Y61" s="3" t="inlineStr">
         <is>
           <t>AA</t>
@@ -14346,24 +14346,20 @@
       <c r="Z61" s="3"/>
       <c r="AA61" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南通市</t>
+          <t>江苏省-无锡市</t>
         </is>
       </c>
       <c r="AB61" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟将全部用于偿还即将到期的公司债券本金[23富港01]</t>
+          <t>本期债券募集资金不超过8亿元,在不考虑发行费用的情况下,拟用于偿还存量公司债券本金[23城铁债]</t>
         </is>
       </c>
       <c r="AC61" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,中信建投证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD61" s="3" t="inlineStr">
-        <is>
-          <t>江苏皋开投资发展集团有限公司</t>
-        </is>
-      </c>
+          <t>天风证券股份有限公司,国联民生证券承销保荐有限公司</t>
+        </is>
+      </c>
+      <c r="AD61" s="3"/>
       <c r="AE61" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -14381,7 +14377,7 @@
       </c>
       <c r="AH61" s="3" t="inlineStr">
         <is>
-          <t>富港建设集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>无锡沪宁城铁惠山站区投资开发建设有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI61" s="3" t="inlineStr">
@@ -14391,63 +14387,63 @@
       </c>
       <c r="AJ61" s="3" t="inlineStr">
         <is>
-          <t>2029-08-27</t>
+          <t>2031-08-27</t>
         </is>
       </c>
       <c r="AK61" s="3"/>
       <c r="AL61" s="3" t="inlineStr">
         <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AM61" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AN61" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AO61" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP61" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AQ61" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR61" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AS61" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AT61" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU61" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM61" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="AN61" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AO61" s="3" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP61" s="3" t="inlineStr">
-        <is>
-          <t>7.5</t>
-        </is>
-      </c>
-      <c r="AQ61" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR61" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AS61" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AT61" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU61" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV61" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW61" s="3" t="inlineStr">
@@ -14470,7 +14466,7 @@
     <row r="62" customHeight="true" ht="18.0">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>26城铁01</t>
+          <t>26金发02</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -14480,64 +14476,64 @@
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>283762.SH</t>
+          <t>283808.SH</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>5+5</t>
         </is>
       </c>
       <c r="E62" s="4" t="n">
-        <v>8.0</v>
+        <v>8.1</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>8.0</v>
+        <v>8.1</v>
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H62" s="4" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>69.28</v>
+        <v>46.85</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>25城铁02</t>
+          <t>26金发01</t>
         </is>
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>3.87Y</t>
+          <t>4.92Y+5.00Y</t>
         </is>
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
-          <t>1.8769</t>
+          <t>2.1205</t>
         </is>
       </c>
       <c r="N62" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.2300/2.1250</t>
         </is>
       </c>
       <c r="O62" s="3" t="inlineStr">
         <is>
-          <t>无锡沪宁城铁惠山站区投资开发建设有限公司</t>
+          <t>湖南金阳新城建设发展集团有限公司</t>
         </is>
       </c>
       <c r="P62" s="3" t="inlineStr">
         <is>
-          <t>C- 17.88</t>
+          <t>C- 20.90</t>
         </is>
       </c>
       <c r="Q62" s="3" t="inlineStr">
@@ -14557,11 +14553,11 @@
       </c>
       <c r="T62" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="U62" s="4" t="n">
-        <v>1.65</v>
+        <v>3.9</v>
       </c>
       <c r="V62" s="3"/>
       <c r="W62" s="3" t="inlineStr">
@@ -14569,30 +14565,26 @@
           <t>6-</t>
         </is>
       </c>
-      <c r="X62" s="3" t="inlineStr">
-        <is>
-          <t>1.86%~1.96%</t>
-        </is>
-      </c>
+      <c r="X62" s="3"/>
       <c r="Y62" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z62" s="3"/>
       <c r="AA62" s="3" t="inlineStr">
         <is>
-          <t>江苏省-无锡市</t>
+          <t>湖南省-长沙市</t>
         </is>
       </c>
       <c r="AB62" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金不超过8亿元,在不考虑发行费用的情况下,拟用于偿还存量公司债券本金[23城铁债]</t>
+          <t>本期公司债券发行规模为不超过81,000.00万元(含81,000.00万元),本期债券募集资金扣除发行费用后,拟全部用于偿还到期的“23金发02”本金。[23金发02]</t>
         </is>
       </c>
       <c r="AC62" s="3" t="inlineStr">
         <is>
-          <t>天风证券股份有限公司,国联民生证券承销保荐有限公司</t>
+          <t>财信证券股份有限公司,中国银河证券股份有限公司</t>
         </is>
       </c>
       <c r="AD62" s="3"/>
@@ -14613,7 +14605,7 @@
       </c>
       <c r="AH62" s="3" t="inlineStr">
         <is>
-          <t>无锡沪宁城铁惠山站区投资开发建设有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>湖南金阳新城建设发展集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI62" s="3" t="inlineStr">
@@ -14623,23 +14615,23 @@
       </c>
       <c r="AJ62" s="3" t="inlineStr">
         <is>
-          <t>2031-08-27</t>
+          <t>2036-08-26</t>
         </is>
       </c>
       <c r="AK62" s="3"/>
       <c r="AL62" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AM62" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AN62" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="AO62" s="3" t="inlineStr">
@@ -14649,7 +14641,7 @@
       </c>
       <c r="AP62" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6.5*无效</t>
         </is>
       </c>
       <c r="AQ62" s="3" t="inlineStr">
@@ -14674,7 +14666,7 @@
       </c>
       <c r="AU62" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2031-08-26</t>
         </is>
       </c>
       <c r="AV62" s="3" t="inlineStr">
@@ -14684,7 +14676,7 @@
       </c>
       <c r="AW62" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX62" s="3" t="inlineStr">
@@ -14702,7 +14694,7 @@
     <row r="63" customHeight="true" ht="18.0">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>26金发02</t>
+          <t>26汕投02</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -14712,64 +14704,64 @@
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>283808.SH</t>
+          <t>283779.SH</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>5+5</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E63" s="4" t="n">
-        <v>8.1</v>
+        <v>6.0</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>8.1</v>
+        <v>6.0</v>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.50 ~ 2.60</t>
         </is>
       </c>
       <c r="H63" s="4" t="n">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>46.85</v>
+        <v>54.28</v>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>26金发01</t>
+          <t>26汕投01</t>
         </is>
       </c>
       <c r="L63" s="3" t="inlineStr">
         <is>
-          <t>4.92Y+5.00Y</t>
+          <t>4.67Y</t>
         </is>
       </c>
       <c r="M63" s="3" t="inlineStr">
         <is>
-          <t>2.1205</t>
+          <t>1.8653</t>
         </is>
       </c>
       <c r="N63" s="3" t="inlineStr">
         <is>
-          <t>2.2300/2.1250</t>
+          <t>1.9600/--</t>
         </is>
       </c>
       <c r="O63" s="3" t="inlineStr">
         <is>
-          <t>湖南金阳新城建设发展集团有限公司</t>
+          <t>汕头市投资控股集团有限公司</t>
         </is>
       </c>
       <c r="P63" s="3" t="inlineStr">
         <is>
-          <t>C- 20.90</t>
+          <t>B- 38.66</t>
         </is>
       </c>
       <c r="Q63" s="3" t="inlineStr">
@@ -14789,38 +14781,46 @@
       </c>
       <c r="T63" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="U63" s="4" t="n">
-        <v>3.9</v>
+        <v>4.07</v>
       </c>
       <c r="V63" s="3"/>
       <c r="W63" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
-        </is>
-      </c>
-      <c r="X63" s="3"/>
+          <t>5+</t>
+        </is>
+      </c>
+      <c r="X63" s="3" t="inlineStr">
+        <is>
+          <t>1.85%~1.95%</t>
+        </is>
+      </c>
       <c r="Y63" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
         </is>
       </c>
-      <c r="Z63" s="3"/>
+      <c r="Z63" s="3" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
       <c r="AA63" s="3" t="inlineStr">
         <is>
-          <t>湖南省-长沙市</t>
+          <t>广东省-汕头市</t>
         </is>
       </c>
       <c r="AB63" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券发行规模为不超过81,000.00万元(含81,000.00万元),本期债券募集资金扣除发行费用后,拟全部用于偿还到期的“23金发02”本金。[23金发02]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还发行人拟回售公司债券本金[23汕投02]</t>
         </is>
       </c>
       <c r="AC63" s="3" t="inlineStr">
         <is>
-          <t>财信证券股份有限公司,中国银河证券股份有限公司</t>
+          <t>广发证券股份有限公司</t>
         </is>
       </c>
       <c r="AD63" s="3"/>
@@ -14841,7 +14841,7 @@
       </c>
       <c r="AH63" s="3" t="inlineStr">
         <is>
-          <t>湖南金阳新城建设发展集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>汕头市投资控股集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI63" s="3" t="inlineStr">
@@ -14851,58 +14851,58 @@
       </c>
       <c r="AJ63" s="3" t="inlineStr">
         <is>
-          <t>2036-08-26</t>
+          <t>2031-08-27</t>
         </is>
       </c>
       <c r="AK63" s="3"/>
       <c r="AL63" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AM63" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AN63" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AO63" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP63" s="3" t="inlineStr">
         <is>
-          <t>6.5*无效</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ63" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR63" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS63" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT63" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU63" s="3" t="inlineStr">
         <is>
-          <t>2031-08-26</t>
+          <t/>
         </is>
       </c>
       <c r="AV63" s="3" t="inlineStr">
@@ -14912,7 +14912,7 @@
       </c>
       <c r="AW63" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX63" s="3" t="inlineStr">
@@ -14930,7 +14930,7 @@
     <row r="64" customHeight="true" ht="18.0">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>26汕投02</t>
+          <t>26锡科01</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -14940,64 +14940,64 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>283779.SH</t>
+          <t>283757.SH</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E64" s="4" t="n">
-        <v>6.0</v>
+        <v>14.5</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>6.0</v>
+        <v>14.5</v>
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.60</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H64" s="4" t="n">
-        <v>1.93</v>
+        <v>1.79</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>54.28</v>
+        <v>53.67</v>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>26汕投01</t>
+          <t>25临投01</t>
         </is>
       </c>
       <c r="L64" s="3" t="inlineStr">
         <is>
-          <t>4.67Y</t>
+          <t>3.49Y</t>
         </is>
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
-          <t>1.8653</t>
+          <t>1.8118</t>
         </is>
       </c>
       <c r="N64" s="3" t="inlineStr">
         <is>
-          <t>1.9600/--</t>
+          <t>--/1.7600</t>
         </is>
       </c>
       <c r="O64" s="3" t="inlineStr">
         <is>
-          <t>汕头市投资控股集团有限公司</t>
+          <t>无锡锡东科技投资控股有限公司</t>
         </is>
       </c>
       <c r="P64" s="3" t="inlineStr">
         <is>
-          <t>B- 38.66</t>
+          <t>E 0.00</t>
         </is>
       </c>
       <c r="Q64" s="3" t="inlineStr">
@@ -15021,17 +15021,17 @@
         </is>
       </c>
       <c r="U64" s="4" t="n">
-        <v>4.07</v>
+        <v>4.48</v>
       </c>
       <c r="V64" s="3"/>
       <c r="W64" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X64" s="3" t="inlineStr">
         <is>
-          <t>1.85%~1.95%</t>
+          <t>1.77%~1.87%</t>
         </is>
       </c>
       <c r="Y64" s="3" t="inlineStr">
@@ -15039,24 +15039,20 @@
           <t>AA+</t>
         </is>
       </c>
-      <c r="Z64" s="3" t="inlineStr">
-        <is>
-          <t>AA+</t>
-        </is>
-      </c>
+      <c r="Z64" s="3"/>
       <c r="AA64" s="3" t="inlineStr">
         <is>
-          <t>广东省-汕头市</t>
+          <t>江苏省-无锡市</t>
         </is>
       </c>
       <c r="AB64" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还发行人拟回售公司债券本金[23汕投02]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟将14.50亿元全部用于偿还到期公司债券本金[23锡东02]</t>
         </is>
       </c>
       <c r="AC64" s="3" t="inlineStr">
         <is>
-          <t>广发证券股份有限公司</t>
+          <t>东吴证券股份有限公司,兴业证券股份有限公司,国信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD64" s="3"/>
@@ -15077,7 +15073,7 @@
       </c>
       <c r="AH64" s="3" t="inlineStr">
         <is>
-          <t>汕头市投资控股集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>无锡锡东科技投资控股有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI64" s="3" t="inlineStr">
@@ -15087,7 +15083,7 @@
       </c>
       <c r="AJ64" s="3" t="inlineStr">
         <is>
-          <t>2031-08-27</t>
+          <t>2029-08-27</t>
         </is>
       </c>
       <c r="AK64" s="3"/>
@@ -15108,32 +15104,32 @@
       </c>
       <c r="AO64" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP64" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>7*无效</t>
         </is>
       </c>
       <c r="AQ64" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR64" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS64" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT64" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU64" s="3" t="inlineStr">
@@ -15166,7 +15162,7 @@
     <row r="65" customHeight="true" ht="18.0">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>26锡科01</t>
+          <t>26济建01(取消发行)</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -15176,64 +15172,58 @@
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>283757.SH</t>
+          <t>DY283677.SH</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E65" s="4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="F65" s="4" t="n">
-        <v>14.5</v>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="F65" s="3"/>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
-        </is>
-      </c>
-      <c r="H65" s="4" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="I65" s="4" t="n">
-        <v>53.67</v>
-      </c>
+          <t>1.40 ~ 2.40</t>
+        </is>
+      </c>
+      <c r="H65" s="3"/>
+      <c r="I65" s="3"/>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>--</t>
         </is>
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>25临投01</t>
+          <t>24济南城建PPN001</t>
         </is>
       </c>
       <c r="L65" s="3" t="inlineStr">
         <is>
-          <t>3.49Y</t>
+          <t>2.92Y</t>
         </is>
       </c>
       <c r="M65" s="3" t="inlineStr">
         <is>
-          <t>1.8118</t>
+          <t>1.7508</t>
         </is>
       </c>
       <c r="N65" s="3" t="inlineStr">
         <is>
-          <t>--/1.7600</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O65" s="3" t="inlineStr">
         <is>
-          <t>无锡锡东科技投资控股有限公司</t>
+          <t>济南城市建设集团有限公司</t>
         </is>
       </c>
       <c r="P65" s="3" t="inlineStr">
         <is>
-          <t>E 0.00</t>
+          <t>C 27.60</t>
         </is>
       </c>
       <c r="Q65" s="3" t="inlineStr">
@@ -15256,39 +15246,37 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="U65" s="4" t="n">
-        <v>4.48</v>
-      </c>
+      <c r="U65" s="3"/>
       <c r="V65" s="3"/>
       <c r="W65" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X65" s="3" t="inlineStr">
         <is>
-          <t>1.77%~1.87%</t>
+          <t>1.86%~1.96%</t>
         </is>
       </c>
       <c r="Y65" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z65" s="3"/>
       <c r="AA65" s="3" t="inlineStr">
         <is>
-          <t>江苏省-无锡市</t>
+          <t>山东省-济南市</t>
         </is>
       </c>
       <c r="AB65" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟将14.50亿元全部用于偿还到期公司债券本金[23锡东02]</t>
+          <t>本期债券发行规模为不超过人民币5亿元(含5亿元),全部用于偿还公司债券本金[23济建04]</t>
         </is>
       </c>
       <c r="AC65" s="3" t="inlineStr">
         <is>
-          <t>东吴证券股份有限公司,兴业证券股份有限公司,国信证券股份有限公司</t>
+          <t>国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD65" s="3"/>
@@ -15309,7 +15297,7 @@
       </c>
       <c r="AH65" s="3" t="inlineStr">
         <is>
-          <t>无锡锡东科技投资控股有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>济南城市建设集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种一)(取消发行)</t>
         </is>
       </c>
       <c r="AI65" s="3" t="inlineStr">
@@ -15319,13 +15307,13 @@
       </c>
       <c r="AJ65" s="3" t="inlineStr">
         <is>
-          <t>2029-08-27</t>
+          <t>2031-08-27</t>
         </is>
       </c>
       <c r="AK65" s="3"/>
       <c r="AL65" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t/>
         </is>
       </c>
       <c r="AM65" s="3" t="inlineStr">
@@ -15340,27 +15328,27 @@
       </c>
       <c r="AO65" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP65" s="3" t="inlineStr">
         <is>
-          <t>7*无效</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ65" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR65" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS65" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT65" s="3" t="inlineStr">
@@ -15398,92 +15386,102 @@
     <row r="66" customHeight="true" ht="18.0">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>26济建01(取消发行)</t>
+          <t>26福州地铁SCP003</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>08-25 19:00</t>
+          <t>08-25 18:00</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>DY283677.SH</t>
+          <t>012682152.IB</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E66" s="4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F66" s="3"/>
+        <v>9.0</v>
+      </c>
+      <c r="F66" s="4" t="n">
+        <v>9.0</v>
+      </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
-        </is>
-      </c>
-      <c r="H66" s="3"/>
-      <c r="I66" s="3"/>
+          <t>1.20 ~ 1.70</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I66" s="4" t="n">
+        <v>36.44</v>
+      </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="K66" s="3" t="inlineStr">
+        <is>
+          <t>26福州地铁SCP002</t>
+        </is>
+      </c>
+      <c r="L66" s="3" t="inlineStr">
+        <is>
+          <t>200D</t>
+        </is>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>1.5118</t>
+        </is>
+      </c>
+      <c r="N66" s="3" t="inlineStr">
+        <is>
+          <t>--/1.5100</t>
+        </is>
+      </c>
+      <c r="O66" s="3" t="inlineStr">
+        <is>
+          <t>福州地铁集团有限公司</t>
+        </is>
+      </c>
+      <c r="P66" s="3" t="inlineStr">
+        <is>
+          <t>C 27.84</t>
+        </is>
+      </c>
+      <c r="Q66" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="R66" s="3" t="inlineStr">
+        <is>
+          <t>08-25 09:00</t>
+        </is>
+      </c>
+      <c r="S66" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K66" s="3" t="inlineStr">
-        <is>
-          <t>24济南城建PPN001</t>
-        </is>
-      </c>
-      <c r="L66" s="3" t="inlineStr">
-        <is>
-          <t>2.92Y</t>
-        </is>
-      </c>
-      <c r="M66" s="3" t="inlineStr">
-        <is>
-          <t>1.7508</t>
-        </is>
-      </c>
-      <c r="N66" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O66" s="3" t="inlineStr">
-        <is>
-          <t>济南城市建设集团有限公司</t>
-        </is>
-      </c>
-      <c r="P66" s="3" t="inlineStr">
-        <is>
-          <t>C 27.60</t>
-        </is>
-      </c>
-      <c r="Q66" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="R66" s="3" t="inlineStr">
-        <is>
-          <t>08-25 15:00</t>
-        </is>
-      </c>
-      <c r="S66" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T66" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="U66" s="3"/>
-      <c r="V66" s="3"/>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="U66" s="4" t="n">
+        <v>4.1889</v>
+      </c>
+      <c r="V66" s="4" t="n">
+        <v>4.6</v>
+      </c>
       <c r="W66" s="3" t="inlineStr">
         <is>
           <t>4+</t>
@@ -15491,7 +15489,7 @@
       </c>
       <c r="X66" s="3" t="inlineStr">
         <is>
-          <t>1.86%~1.96%</t>
+          <t>1.45%~1.49%</t>
         </is>
       </c>
       <c r="Y66" s="3" t="inlineStr">
@@ -15502,23 +15500,23 @@
       <c r="Z66" s="3"/>
       <c r="AA66" s="3" t="inlineStr">
         <is>
-          <t>山东省-济南市</t>
+          <t>福建省-福州市</t>
         </is>
       </c>
       <c r="AB66" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模为不超过人民币5亿元(含5亿元),全部用于偿还公司债券本金[23济建04]</t>
+          <t>本期超短期融资券募集资金9.00亿元,期限270天,拟用于归还到期债券。[25福州地铁SCP005]</t>
         </is>
       </c>
       <c r="AC66" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司</t>
+          <t>中信银行股份有限公司,中国建设银行股份有限公司</t>
         </is>
       </c>
       <c r="AD66" s="3"/>
       <c r="AE66" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF66" s="3" t="inlineStr">
@@ -15528,28 +15526,32 @@
       </c>
       <c r="AG66" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH66" s="3" t="inlineStr">
         <is>
-          <t>济南城市建设集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种一)(取消发行)</t>
+          <t>福州地铁集团有限公司2026年度第三期超短期融资券</t>
         </is>
       </c>
       <c r="AI66" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ66" s="3" t="inlineStr">
         <is>
-          <t>2031-08-27</t>
-        </is>
-      </c>
-      <c r="AK66" s="3"/>
+          <t>2027-05-23</t>
+        </is>
+      </c>
+      <c r="AK66" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL66" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AM66" s="3" t="inlineStr">
@@ -15559,37 +15561,37 @@
       </c>
       <c r="AN66" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="AO66" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP66" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ66" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR66" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AS66" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AT66" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>公交</t>
         </is>
       </c>
       <c r="AU66" s="3" t="inlineStr">
@@ -15622,7 +15624,7 @@
     <row r="67" customHeight="true" ht="18.0">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>26福州地铁SCP003</t>
+          <t>26常山集团PPN001</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -15632,64 +15634,62 @@
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>012682152.IB</t>
+          <t>032680255.IB</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E67" s="4" t="n">
-        <v>9.0</v>
+        <v>5.0</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>9.0</v>
+        <v>5.0</v>
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 1.70</t>
+          <t>1.80 ~ 2.80</t>
         </is>
       </c>
       <c r="H67" s="4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I67" s="4" t="n">
-        <v>36.44</v>
-      </c>
+        <v>2.2</v>
+      </c>
+      <c r="I67" s="3"/>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>26福州地铁SCP002</t>
+          <t>25常山K2</t>
         </is>
       </c>
       <c r="L67" s="3" t="inlineStr">
         <is>
-          <t>200D</t>
+          <t>2.15Y+2.00Y</t>
         </is>
       </c>
       <c r="M67" s="3" t="inlineStr">
         <is>
-          <t>1.5118</t>
+          <t>2.3546</t>
         </is>
       </c>
       <c r="N67" s="3" t="inlineStr">
         <is>
-          <t>--/1.5100</t>
+          <t>2.3000/--</t>
         </is>
       </c>
       <c r="O67" s="3" t="inlineStr">
         <is>
-          <t>福州地铁集团有限公司</t>
+          <t>石家庄常山纺织集团有限责任公司</t>
         </is>
       </c>
       <c r="P67" s="3" t="inlineStr">
         <is>
-          <t>C 27.84</t>
+          <t>A 71.67</t>
         </is>
       </c>
       <c r="Q67" s="3" t="inlineStr">
@@ -15699,7 +15699,7 @@
       </c>
       <c r="R67" s="3" t="inlineStr">
         <is>
-          <t>08-25 09:00</t>
+          <t>08-25 15:00</t>
         </is>
       </c>
       <c r="S67" s="3" t="inlineStr">
@@ -15713,46 +15713,44 @@
         </is>
       </c>
       <c r="U67" s="4" t="n">
-        <v>4.1889</v>
-      </c>
-      <c r="V67" s="4" t="n">
-        <v>4.6</v>
-      </c>
+        <v>2.46</v>
+      </c>
+      <c r="V67" s="3"/>
       <c r="W67" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X67" s="3" t="inlineStr">
         <is>
-          <t>1.45%~1.49%</t>
+          <t>2.50%~2.60%</t>
         </is>
       </c>
       <c r="Y67" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3" t="inlineStr">
         <is>
-          <t>福建省-福州市</t>
+          <t>河北省-石家庄市</t>
         </is>
       </c>
       <c r="AB67" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券募集资金9.00亿元,期限270天,拟用于归还到期债券。[25福州地铁SCP005]</t>
+          <t>发行人本期定向债务融资工具发行规模为5.00亿元,扣除承销费用后拟全部用于偿还发行人及其子公司有息债务</t>
         </is>
       </c>
       <c r="AC67" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,中国建设银行股份有限公司</t>
+          <t>国泰海通证券股份有限公司,中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF67" s="3" t="inlineStr">
@@ -15767,22 +15765,22 @@
       </c>
       <c r="AH67" s="3" t="inlineStr">
         <is>
-          <t>福州地铁集团有限公司2026年度第三期超短期融资券</t>
+          <t>石家庄常山纺织集团有限责任公司2026年度第一期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI67" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ67" s="3" t="inlineStr">
         <is>
-          <t>2027-05-23</t>
+          <t>2028-08-26</t>
         </is>
       </c>
       <c r="AK67" s="3" t="inlineStr">
         <is>
-          <t>休1</t>
+          <t>休2</t>
         </is>
       </c>
       <c r="AL67" s="3" t="inlineStr">
@@ -15802,32 +15800,32 @@
       </c>
       <c r="AO67" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP67" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ67" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR67" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>产业集团</t>
         </is>
       </c>
       <c r="AS67" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>产业集团</t>
         </is>
       </c>
       <c r="AT67" s="3" t="inlineStr">
         <is>
-          <t>公交</t>
+          <t>计算机应用</t>
         </is>
       </c>
       <c r="AU67" s="3" t="inlineStr">
@@ -15860,7 +15858,7 @@
     <row r="68" customHeight="true" ht="18.0">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>26常山集团PPN001</t>
+          <t>26宿迁高新MTN001</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -15870,64 +15868,64 @@
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>032680255.IB</t>
+          <t>102683333.IB</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E68" s="4" t="n">
-        <v>5.0</v>
+        <v>3.81</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>5.0</v>
+        <v>3.81</v>
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.80</t>
+          <t>1.60 ~ 2.50</t>
         </is>
       </c>
       <c r="H68" s="4" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="I68" s="4" t="n">
-        <v>96.39</v>
+        <v>46.28</v>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>25常山K2</t>
+          <t>24宿迁高新PPN001</t>
         </is>
       </c>
       <c r="L68" s="3" t="inlineStr">
         <is>
-          <t>2.15Y+2.00Y</t>
+          <t>307D</t>
         </is>
       </c>
       <c r="M68" s="3" t="inlineStr">
         <is>
-          <t>2.3546</t>
+          <t>1.7413</t>
         </is>
       </c>
       <c r="N68" s="3" t="inlineStr">
         <is>
-          <t>2.3000/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O68" s="3" t="inlineStr">
         <is>
-          <t>石家庄常山纺织集团有限责任公司</t>
+          <t>宿迁高新开发投资有限公司</t>
         </is>
       </c>
       <c r="P68" s="3" t="inlineStr">
         <is>
-          <t>A 71.67</t>
+          <t>C 29.94</t>
         </is>
       </c>
       <c r="Q68" s="3" t="inlineStr">
@@ -15937,7 +15935,7 @@
       </c>
       <c r="R68" s="3" t="inlineStr">
         <is>
-          <t>08-25 15:00</t>
+          <t>08-25 09:00</t>
         </is>
       </c>
       <c r="S68" s="3" t="inlineStr">
@@ -15950,43 +15948,47 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="U68" s="3"/>
-      <c r="V68" s="3"/>
+      <c r="U68" s="4" t="n">
+        <v>2.2415</v>
+      </c>
+      <c r="V68" s="4" t="n">
+        <v>3.33</v>
+      </c>
       <c r="W68" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X68" s="3" t="inlineStr">
         <is>
-          <t>2.50%~2.60%</t>
+          <t>1.90%~2.00%</t>
         </is>
       </c>
       <c r="Y68" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z68" s="3"/>
       <c r="AA68" s="3" t="inlineStr">
         <is>
-          <t>河北省-石家庄市</t>
+          <t>江苏省-宿迁市</t>
         </is>
       </c>
       <c r="AB68" s="3" t="inlineStr">
         <is>
-          <t>发行人本期定向债务融资工具发行规模为5.00亿元,扣除承销费用后拟全部用于偿还发行人及其子公司有息债务</t>
+          <t>本次中期票据注册金额3.81亿元,本期发行金额3.81亿元,全部用于偿还发行人存量债务融资工具[21宿迁高新MTN001]</t>
         </is>
       </c>
       <c r="AC68" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,中信银行股份有限公司</t>
+          <t>南京银行股份有限公司</t>
         </is>
       </c>
       <c r="AD68" s="3"/>
       <c r="AE68" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF68" s="3" t="inlineStr">
@@ -16001,24 +16003,20 @@
       </c>
       <c r="AH68" s="3" t="inlineStr">
         <is>
-          <t>石家庄常山纺织集团有限责任公司2026年度第一期定向债务融资工具</t>
+          <t>宿迁高新开发投资有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI68" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ68" s="3" t="inlineStr">
         <is>
-          <t>2028-08-26</t>
-        </is>
-      </c>
-      <c r="AK68" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2031-08-26</t>
+        </is>
+      </c>
+      <c r="AK68" s="3"/>
       <c r="AL68" s="3" t="inlineStr">
         <is>
           <t>2026-08-27</t>
@@ -16036,37 +16034,37 @@
       </c>
       <c r="AO68" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP68" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6.5*无效</t>
         </is>
       </c>
       <c r="AQ68" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR68" s="3" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS68" s="3" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT68" s="3" t="inlineStr">
         <is>
-          <t>计算机应用</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU68" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-08-26</t>
         </is>
       </c>
       <c r="AV68" s="3" t="inlineStr">
@@ -16076,7 +16074,7 @@
       </c>
       <c r="AW68" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX68" s="3" t="inlineStr">
@@ -16094,7 +16092,7 @@
     <row r="69" customHeight="true" ht="18.0">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>26宿迁高新MTN001</t>
+          <t>26之江城投PPN001A</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -16104,7 +16102,7 @@
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>102683333.IB</t>
+          <t>032680490.IB</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
@@ -16113,55 +16111,55 @@
         </is>
       </c>
       <c r="E69" s="4" t="n">
-        <v>3.81</v>
+        <v>5.0</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>3.81</v>
+        <v>5.0</v>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.50</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H69" s="4" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="I69" s="4" t="n">
-        <v>46.28</v>
+        <v>36.28</v>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>24宿迁高新PPN001</t>
+          <t>24之江03</t>
         </is>
       </c>
       <c r="L69" s="3" t="inlineStr">
         <is>
-          <t>307D</t>
+          <t>2.82Y</t>
         </is>
       </c>
       <c r="M69" s="3" t="inlineStr">
         <is>
-          <t>1.7413</t>
+          <t>1.6945</t>
         </is>
       </c>
       <c r="N69" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.7500</t>
         </is>
       </c>
       <c r="O69" s="3" t="inlineStr">
         <is>
-          <t>宿迁高新开发投资有限公司</t>
+          <t>杭州之江城市建设投资集团有限公司</t>
         </is>
       </c>
       <c r="P69" s="3" t="inlineStr">
         <is>
-          <t>C 29.94</t>
+          <t>B- 36.90</t>
         </is>
       </c>
       <c r="Q69" s="3" t="inlineStr">
@@ -16171,7 +16169,7 @@
       </c>
       <c r="R69" s="3" t="inlineStr">
         <is>
-          <t>08-25 09:00</t>
+          <t>08-25 15:00</t>
         </is>
       </c>
       <c r="S69" s="3" t="inlineStr">
@@ -16185,46 +16183,46 @@
         </is>
       </c>
       <c r="U69" s="4" t="n">
-        <v>2.2415</v>
+        <v>4.56</v>
       </c>
       <c r="V69" s="4" t="n">
-        <v>3.33</v>
+        <v>11.5</v>
       </c>
       <c r="W69" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X69" s="3" t="inlineStr">
         <is>
-          <t>1.90%~2.00%</t>
+          <t>1.72%~1.82%</t>
         </is>
       </c>
       <c r="Y69" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z69" s="3"/>
       <c r="AA69" s="3" t="inlineStr">
         <is>
-          <t>江苏省-宿迁市</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB69" s="3" t="inlineStr">
         <is>
-          <t>本次中期票据注册金额3.81亿元,本期发行金额3.81亿元,全部用于偿还发行人存量债务融资工具[21宿迁高新MTN001]</t>
+          <t>发行人本期债务融资工具注册金额为10.00亿元,均用于偿还“21之江城投PPN001”的债务融资工具本金[21之江城投PPN001]</t>
         </is>
       </c>
       <c r="AC69" s="3" t="inlineStr">
         <is>
-          <t>南京银行股份有限公司</t>
+          <t>中信建投证券股份有限公司,国泰海通证券股份有限公司,东方证券股份有限公司</t>
         </is>
       </c>
       <c r="AD69" s="3"/>
       <c r="AE69" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF69" s="3" t="inlineStr">
@@ -16239,12 +16237,12 @@
       </c>
       <c r="AH69" s="3" t="inlineStr">
         <is>
-          <t>宿迁高新开发投资有限公司2026年度第一期中期票据</t>
+          <t>杭州之江城市建设投资集团有限公司2026年度第一期定向债务融资工具(品种一)</t>
         </is>
       </c>
       <c r="AI69" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ69" s="3" t="inlineStr">
@@ -16270,12 +16268,12 @@
       </c>
       <c r="AO69" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP69" s="3" t="inlineStr">
         <is>
-          <t>6.5*无效</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ69" s="3" t="inlineStr">
@@ -16285,12 +16283,12 @@
       </c>
       <c r="AR69" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>其他基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS69" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>其他基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT69" s="3" t="inlineStr">
@@ -16328,7 +16326,7 @@
     <row r="70" customHeight="true" ht="18.0">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>26之江城投PPN001A</t>
+          <t>26吉林高速MTN007</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -16338,7 +16336,7 @@
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>032680490.IB</t>
+          <t>102683337.IB</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
@@ -16347,55 +16345,55 @@
         </is>
       </c>
       <c r="E70" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.50 ~ 1.90</t>
         </is>
       </c>
       <c r="H70" s="4" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="I70" s="4" t="n">
-        <v>36.28</v>
+        <v>33.28</v>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>24之江03</t>
+          <t>26吉林高速MTN006</t>
         </is>
       </c>
       <c r="L70" s="3" t="inlineStr">
         <is>
-          <t>2.82Y</t>
+          <t>2.98Y+2.00Y</t>
         </is>
       </c>
       <c r="M70" s="3" t="inlineStr">
         <is>
-          <t>1.6945</t>
+          <t>1.7744</t>
         </is>
       </c>
       <c r="N70" s="3" t="inlineStr">
         <is>
-          <t>--/1.7500</t>
+          <t>1.7500/1.7400</t>
         </is>
       </c>
       <c r="O70" s="3" t="inlineStr">
         <is>
-          <t>杭州之江城市建设投资集团有限公司</t>
+          <t>吉林省高速公路集团有限公司</t>
         </is>
       </c>
       <c r="P70" s="3" t="inlineStr">
         <is>
-          <t>B- 36.90</t>
+          <t>B 53.49</t>
         </is>
       </c>
       <c r="Q70" s="3" t="inlineStr">
@@ -16405,7 +16403,7 @@
       </c>
       <c r="R70" s="3" t="inlineStr">
         <is>
-          <t>08-25 15:00</t>
+          <t>08-25 09:00</t>
         </is>
       </c>
       <c r="S70" s="3" t="inlineStr">
@@ -16419,19 +16417,19 @@
         </is>
       </c>
       <c r="U70" s="4" t="n">
-        <v>4.56</v>
+        <v>4.78</v>
       </c>
       <c r="V70" s="4" t="n">
-        <v>11.5</v>
+        <v>1.6</v>
       </c>
       <c r="W70" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X70" s="3" t="inlineStr">
         <is>
-          <t>1.72%~1.82%</t>
+          <t>1.70%~1.80%</t>
         </is>
       </c>
       <c r="Y70" s="3" t="inlineStr">
@@ -16439,26 +16437,30 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z70" s="3"/>
+      <c r="Z70" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA70" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
+          <t>吉林省</t>
         </is>
       </c>
       <c r="AB70" s="3" t="inlineStr">
         <is>
-          <t>发行人本期债务融资工具注册金额为10.00亿元,均用于偿还“21之江城投PPN001”的债务融资工具本金[21之江城投PPN001]</t>
+          <t>本期中期票据基础发行规模为0亿元，发行金额上限为10亿元，拟全部用于偿还发行人有息债务本息。</t>
         </is>
       </c>
       <c r="AC70" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,国泰海通证券股份有限公司,东方证券股份有限公司</t>
+          <t>华夏银行股份有限公司,上海浦东发展银行股份有限公司</t>
         </is>
       </c>
       <c r="AD70" s="3"/>
       <c r="AE70" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF70" s="3" t="inlineStr">
@@ -16473,12 +16475,12 @@
       </c>
       <c r="AH70" s="3" t="inlineStr">
         <is>
-          <t>杭州之江城市建设投资集团有限公司2026年度第一期定向债务融资工具(品种一)</t>
+          <t>吉林省高速公路集团有限公司2026年度第七期中期票据</t>
         </is>
       </c>
       <c r="AI70" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ70" s="3" t="inlineStr">
@@ -16504,12 +16506,12 @@
       </c>
       <c r="AO70" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP70" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ70" s="3" t="inlineStr">
@@ -16519,17 +16521,17 @@
       </c>
       <c r="AR70" s="3" t="inlineStr">
         <is>
-          <t>其他基础设施投融资建设</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AS70" s="3" t="inlineStr">
         <is>
-          <t>其他基础设施投融资建设</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AT70" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU70" s="3" t="inlineStr">
@@ -16562,7 +16564,7 @@
     <row r="71" customHeight="true" ht="18.0">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>26吉林高速MTN007</t>
+          <t>26桂林银行绿债01A</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -16572,64 +16574,64 @@
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>102683337.IB</t>
+          <t>222680017.IB</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E71" s="4" t="n">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.90</t>
+          <t>1.40 ~ 1.90</t>
         </is>
       </c>
       <c r="H71" s="4" t="n">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="I71" s="4" t="n">
-        <v>33.28</v>
+        <v>37.67</v>
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>26吉林高速MTN006</t>
+          <t>25桂林银行绿色债02</t>
         </is>
       </c>
       <c r="L71" s="3" t="inlineStr">
         <is>
-          <t>2.98Y+2.00Y</t>
+          <t>2.23Y</t>
         </is>
       </c>
       <c r="M71" s="3" t="inlineStr">
         <is>
-          <t>1.7744</t>
+          <t>1.6141</t>
         </is>
       </c>
       <c r="N71" s="3" t="inlineStr">
         <is>
-          <t>1.7500/1.7400</t>
+          <t>--/1.6300</t>
         </is>
       </c>
       <c r="O71" s="3" t="inlineStr">
         <is>
-          <t>吉林省高速公路集团有限公司</t>
+          <t>桂林银行股份有限公司</t>
         </is>
       </c>
       <c r="P71" s="3" t="inlineStr">
         <is>
-          <t>B 53.49</t>
+          <t>B- 48.33</t>
         </is>
       </c>
       <c r="Q71" s="3" t="inlineStr">
@@ -16649,15 +16651,11 @@
       </c>
       <c r="T71" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="U71" s="4" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="V71" s="4" t="n">
-        <v>1.6</v>
-      </c>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="U71" s="3"/>
+      <c r="V71" s="3"/>
       <c r="W71" s="3" t="inlineStr">
         <is>
           <t>5-</t>
@@ -16665,7 +16663,7 @@
       </c>
       <c r="X71" s="3" t="inlineStr">
         <is>
-          <t>1.70%~1.80%</t>
+          <t>1.69%~1.79%</t>
         </is>
       </c>
       <c r="Y71" s="3" t="inlineStr">
@@ -16680,23 +16678,23 @@
       </c>
       <c r="AA71" s="3" t="inlineStr">
         <is>
-          <t>吉林省</t>
+          <t>广西壮族自治区-桂林市</t>
         </is>
       </c>
       <c r="AB71" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据基础发行规模为0亿元，发行金额上限为10亿元，拟全部用于偿还发行人有息债务本息。</t>
+          <t>本期债券发行所募集资金将依据适用法律和监管部门的批准,用于投放《绿色金融支持项目目录(2025年版)》支持的绿色产业项目相关贷款,优先支持同时符合《生物多样性金融目录[试用稿]》的项目。</t>
         </is>
       </c>
       <c r="AC71" s="3" t="inlineStr">
         <is>
-          <t>华夏银行股份有限公司,上海浦东发展银行股份有限公司</t>
+          <t>中信证券股份有限公司,中国国际金融股份有限公司,国泰海通证券股份有限公司,中信建投证券股份有限公司,申万宏源证券有限公司,国开证券股份有限公司</t>
         </is>
       </c>
       <c r="AD71" s="3"/>
       <c r="AE71" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>商业银行普通债券</t>
         </is>
       </c>
       <c r="AF71" s="3" t="inlineStr">
@@ -16711,7 +16709,7 @@
       </c>
       <c r="AH71" s="3" t="inlineStr">
         <is>
-          <t>吉林省高速公路集团有限公司2026年度第七期中期票据</t>
+          <t>桂林银行股份有限公司2026年绿色金融债券(第一期)(品种一)</t>
         </is>
       </c>
       <c r="AI71" s="3" t="inlineStr">
@@ -16721,28 +16719,28 @@
       </c>
       <c r="AJ71" s="3" t="inlineStr">
         <is>
-          <t>2031-08-26</t>
+          <t>2029-08-27</t>
         </is>
       </c>
       <c r="AK71" s="3"/>
       <c r="AL71" s="3" t="inlineStr">
         <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AM71" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AN71" s="3" t="inlineStr">
+        <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="AM71" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="AN71" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
       <c r="AO71" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP71" s="3" t="inlineStr">
@@ -16752,27 +16750,27 @@
       </c>
       <c r="AQ71" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AR71" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AS71" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>城商行</t>
         </is>
       </c>
       <c r="AT71" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AU71" s="3" t="inlineStr">
         <is>
-          <t>2029-08-26</t>
+          <t/>
         </is>
       </c>
       <c r="AV71" s="3" t="inlineStr">
@@ -16782,7 +16780,7 @@
       </c>
       <c r="AW71" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX71" s="3" t="inlineStr">
@@ -16800,74 +16798,74 @@
     <row r="72" customHeight="true" ht="18.0">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>26桂林银行绿债01A</t>
+          <t>26蓉高04</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>08-25 18:00</t>
+          <t>08-25 19:00</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>222680017.IB</t>
+          <t>245886.SH</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5+5</t>
         </is>
       </c>
       <c r="E72" s="4" t="n">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.90</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H72" s="4" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="I72" s="4" t="n">
-        <v>37.67</v>
+        <v>6.85</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>25桂林银行绿色债02</t>
+          <t>26蓉高03</t>
         </is>
       </c>
       <c r="L72" s="3" t="inlineStr">
         <is>
-          <t>2.23Y</t>
+          <t>4.91Y+5.00Y</t>
         </is>
       </c>
       <c r="M72" s="3" t="inlineStr">
         <is>
-          <t>1.6141</t>
+          <t>1.7882</t>
         </is>
       </c>
       <c r="N72" s="3" t="inlineStr">
         <is>
-          <t>--/1.6300</t>
+          <t>1.8300/--</t>
         </is>
       </c>
       <c r="O72" s="3" t="inlineStr">
         <is>
-          <t>桂林银行股份有限公司</t>
+          <t>成都高新投资集团有限公司</t>
         </is>
       </c>
       <c r="P72" s="3" t="inlineStr">
         <is>
-          <t>B- 48.33</t>
+          <t>B- 36.00</t>
         </is>
       </c>
       <c r="Q72" s="3" t="inlineStr">
@@ -16877,7 +16875,7 @@
       </c>
       <c r="R72" s="3" t="inlineStr">
         <is>
-          <t>08-25 09:00</t>
+          <t>08-25 15:00</t>
         </is>
       </c>
       <c r="S72" s="3" t="inlineStr">
@@ -16887,19 +16885,21 @@
       </c>
       <c r="T72" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="U72" s="3"/>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="U72" s="4" t="n">
+        <v>7.13</v>
+      </c>
       <c r="V72" s="3"/>
       <c r="W72" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X72" s="3" t="inlineStr">
         <is>
-          <t>1.69%~1.79%</t>
+          <t>1.75%~1.85%</t>
         </is>
       </c>
       <c r="Y72" s="3" t="inlineStr">
@@ -16907,30 +16907,26 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z72" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z72" s="3"/>
       <c r="AA72" s="3" t="inlineStr">
         <is>
-          <t>广西壮族自治区-桂林市</t>
+          <t>四川省-成都市</t>
         </is>
       </c>
       <c r="AB72" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行所募集资金将依据适用法律和监管部门的批准,用于投放《绿色金融支持项目目录(2025年版)》支持的绿色产业项目相关贷款,优先支持同时符合《生物多样性金融目录[试用稿]》的项目。</t>
+          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还回售的公司债券21蓉高03的本金。[21蓉高03]</t>
         </is>
       </c>
       <c r="AC72" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,中国国际金融股份有限公司,国泰海通证券股份有限公司,中信建投证券股份有限公司,申万宏源证券有限公司,国开证券股份有限公司</t>
+          <t>国泰海通证券股份有限公司,国投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD72" s="3"/>
       <c r="AE72" s="3" t="inlineStr">
         <is>
-          <t>商业银行普通债券</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF72" s="3" t="inlineStr">
@@ -16940,12 +16936,12 @@
       </c>
       <c r="AG72" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH72" s="3" t="inlineStr">
         <is>
-          <t>桂林银行股份有限公司2026年绿色金融债券(第一期)(品种一)</t>
+          <t>成都高新投资集团有限公司2026年面向专业投资者公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI72" s="3" t="inlineStr">
@@ -16955,58 +16951,58 @@
       </c>
       <c r="AJ72" s="3" t="inlineStr">
         <is>
-          <t>2029-08-27</t>
+          <t>2036-08-26</t>
         </is>
       </c>
       <c r="AK72" s="3"/>
       <c r="AL72" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AM72" s="3" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AN72" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="AO72" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP72" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.5*无效</t>
         </is>
       </c>
       <c r="AQ72" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR72" s="3" t="inlineStr">
         <is>
-          <t>商业银行</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS72" s="3" t="inlineStr">
         <is>
-          <t>城商行</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT72" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU72" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2031-08-26</t>
         </is>
       </c>
       <c r="AV72" s="3" t="inlineStr">
@@ -17016,7 +17012,7 @@
       </c>
       <c r="AW72" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX72" s="3" t="inlineStr">
@@ -17034,74 +17030,74 @@
     <row r="73" customHeight="true" ht="18.0">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>26蓉高04</t>
+          <t>26心连心MTN001(科创债)</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>08-25 19:00</t>
+          <t>08-25 18:00</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>245886.SH</t>
+          <t>102683346.IB</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>5+5</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E73" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="H73" s="4" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="I73" s="4" t="n">
-        <v>6.85</v>
+        <v>94.67</v>
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>26蓉高03</t>
+          <t>24连云工投MTN001</t>
         </is>
       </c>
       <c r="L73" s="3" t="inlineStr">
         <is>
-          <t>4.91Y+5.00Y</t>
+          <t>3.09Y</t>
         </is>
       </c>
       <c r="M73" s="3" t="inlineStr">
         <is>
-          <t>1.7882</t>
+          <t>2.0090</t>
         </is>
       </c>
       <c r="N73" s="3" t="inlineStr">
         <is>
-          <t>1.8300/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O73" s="3" t="inlineStr">
         <is>
-          <t>成都高新投资集团有限公司</t>
+          <t>河南心连心化学工业集团股份有限公司</t>
         </is>
       </c>
       <c r="P73" s="3" t="inlineStr">
         <is>
-          <t>B- 36.00</t>
+          <t>B 55.00</t>
         </is>
       </c>
       <c r="Q73" s="3" t="inlineStr">
@@ -17125,59 +17121,55 @@
         </is>
       </c>
       <c r="U73" s="4" t="n">
-        <v>7.13</v>
+        <v>1.42</v>
       </c>
       <c r="V73" s="3"/>
       <c r="W73" s="3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X73" s="3" t="inlineStr">
-        <is>
-          <t>1.75%~1.85%</t>
-        </is>
-      </c>
+          <t>6-</t>
+        </is>
+      </c>
+      <c r="X73" s="3"/>
       <c r="Y73" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z73" s="3"/>
       <c r="AA73" s="3" t="inlineStr">
         <is>
-          <t>四川省-成都市</t>
+          <t>河南省-新乡市</t>
         </is>
       </c>
       <c r="AB73" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还回售的公司债券21蓉高03的本金。[21蓉高03]</t>
+          <t>发行人本期中期票据发行金额5亿元,本次发行扣除发行费用后,募集资金拟全部用于偿还发行人本部及合并范围内下属子公司的存量有息债务</t>
         </is>
       </c>
       <c r="AC73" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,国投证券股份有限公司</t>
+          <t>国泰海通证券股份有限公司,渤海银行股份有限公司,交通银行股份有限公司,中国民生银行股份有限公司,中国工商银行股份有限公司,招商银行股份有限公司,华夏银行股份有限公司,中国建设银行股份有限公司</t>
         </is>
       </c>
       <c r="AD73" s="3"/>
       <c r="AE73" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF73" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG73" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH73" s="3" t="inlineStr">
         <is>
-          <t>成都高新投资集团有限公司2026年面向专业投资者公开发行公司债券(第三期)</t>
+          <t>河南心连心化学工业集团股份有限公司2026年度第一期科技创新债券(乡村振兴)</t>
         </is>
       </c>
       <c r="AI73" s="3" t="inlineStr">
@@ -17187,13 +17179,17 @@
       </c>
       <c r="AJ73" s="3" t="inlineStr">
         <is>
-          <t>2036-08-26</t>
-        </is>
-      </c>
-      <c r="AK73" s="3"/>
+          <t>2029-08-26</t>
+        </is>
+      </c>
+      <c r="AK73" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL73" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AM73" s="3" t="inlineStr">
@@ -17211,34 +17207,30 @@
           <t>产业</t>
         </is>
       </c>
-      <c r="AP73" s="3" t="inlineStr">
-        <is>
-          <t>6.5*无效</t>
-        </is>
-      </c>
+      <c r="AP73" s="3"/>
       <c r="AQ73" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>化工制造</t>
         </is>
       </c>
       <c r="AR73" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>化学制品</t>
         </is>
       </c>
       <c r="AS73" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>化学制品</t>
         </is>
       </c>
       <c r="AT73" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>化学制品</t>
         </is>
       </c>
       <c r="AU73" s="3" t="inlineStr">
         <is>
-          <t>2031-08-26</t>
+          <t/>
         </is>
       </c>
       <c r="AV73" s="3" t="inlineStr">
@@ -17248,7 +17240,7 @@
       </c>
       <c r="AW73" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX73" s="3" t="inlineStr">
@@ -17266,7 +17258,7 @@
     <row r="74" customHeight="true" ht="18.0">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>26心连心MTN001(科创债)</t>
+          <t>26新疆城建CP002</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -17276,49 +17268,49 @@
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>102683346.IB</t>
+          <t>042680299.IB</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>1Y</t>
         </is>
       </c>
       <c r="E74" s="4" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.70 ~ 2.70</t>
         </is>
       </c>
       <c r="H74" s="4" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="I74" s="4" t="n">
-        <v>94.67</v>
+        <v>54.7</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>24连云工投MTN001</t>
+          <t>26新疆城建CP001</t>
         </is>
       </c>
       <c r="L74" s="3" t="inlineStr">
         <is>
-          <t>3.09Y</t>
+          <t>319D</t>
         </is>
       </c>
       <c r="M74" s="3" t="inlineStr">
         <is>
-          <t>2.0090</t>
+          <t>1.7946</t>
         </is>
       </c>
       <c r="N74" s="3" t="inlineStr">
@@ -17328,12 +17320,12 @@
       </c>
       <c r="O74" s="3" t="inlineStr">
         <is>
-          <t>河南心连心化学工业集团股份有限公司</t>
+          <t>新疆城建(集团)股份有限公司</t>
         </is>
       </c>
       <c r="P74" s="3" t="inlineStr">
         <is>
-          <t>B 55.00</t>
+          <t>C- 17.00</t>
         </is>
       </c>
       <c r="Q74" s="3" t="inlineStr">
@@ -17343,7 +17335,7 @@
       </c>
       <c r="R74" s="3" t="inlineStr">
         <is>
-          <t>08-25 15:00</t>
+          <t>08-25 09:00</t>
         </is>
       </c>
       <c r="S74" s="3" t="inlineStr">
@@ -17357,45 +17349,47 @@
         </is>
       </c>
       <c r="U74" s="4" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V74" s="3"/>
-      <c r="W74" s="3" t="inlineStr">
-        <is>
-          <t>6-</t>
-        </is>
-      </c>
-      <c r="X74" s="3"/>
+        <v>1.85</v>
+      </c>
+      <c r="V74" s="4" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="W74" s="3"/>
+      <c r="X74" s="3" t="inlineStr">
+        <is>
+          <t>1.82%~1.86%</t>
+        </is>
+      </c>
       <c r="Y74" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z74" s="3"/>
       <c r="AA74" s="3" t="inlineStr">
         <is>
-          <t>河南省-新乡市</t>
+          <t>新疆维吾尔自治区-乌鲁木齐市</t>
         </is>
       </c>
       <c r="AB74" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据发行金额5亿元,本次发行扣除发行费用后,募集资金拟全部用于偿还发行人本部及合并范围内下属子公司的存量有息债务</t>
+          <t>本次短期融资券发行金额为2亿元,募集资金用于偿还发行人本部银行贷款。</t>
         </is>
       </c>
       <c r="AC74" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,渤海银行股份有限公司,交通银行股份有限公司,中国民生银行股份有限公司,中国工商银行股份有限公司,招商银行股份有限公司,华夏银行股份有限公司,中国建设银行股份有限公司</t>
+          <t>华夏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD74" s="3"/>
       <c r="AE74" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>短期融资券(CP)</t>
         </is>
       </c>
       <c r="AF74" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG74" s="3" t="inlineStr">
@@ -17405,7 +17399,7 @@
       </c>
       <c r="AH74" s="3" t="inlineStr">
         <is>
-          <t>河南心连心化学工业集团股份有限公司2026年度第一期科技创新债券(乡村振兴)</t>
+          <t>新疆城建(集团)股份有限公司2026年度第二期短期融资券</t>
         </is>
       </c>
       <c r="AI74" s="3" t="inlineStr">
@@ -17415,14 +17409,10 @@
       </c>
       <c r="AJ74" s="3" t="inlineStr">
         <is>
-          <t>2029-08-26</t>
-        </is>
-      </c>
-      <c r="AK74" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2027-08-26</t>
+        </is>
+      </c>
+      <c r="AK74" s="3"/>
       <c r="AL74" s="3" t="inlineStr">
         <is>
           <t>2026-08-27</t>
@@ -17443,25 +17433,29 @@
           <t>产业</t>
         </is>
       </c>
-      <c r="AP74" s="3"/>
+      <c r="AP74" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="AQ74" s="3" t="inlineStr">
         <is>
-          <t>化工制造</t>
+          <t>建筑施工</t>
         </is>
       </c>
       <c r="AR74" s="3" t="inlineStr">
         <is>
-          <t>化学制品</t>
+          <t>综合建筑施工</t>
         </is>
       </c>
       <c r="AS74" s="3" t="inlineStr">
         <is>
-          <t>化学制品</t>
+          <t>综合建筑施工</t>
         </is>
       </c>
       <c r="AT74" s="3" t="inlineStr">
         <is>
-          <t>化学制品</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU74" s="3" t="inlineStr">
@@ -17494,7 +17488,7 @@
     <row r="75" customHeight="true" ht="18.0">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>26新疆城建CP002</t>
+          <t>26保利久联CP003</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -17504,49 +17498,49 @@
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>042680299.IB</t>
+          <t>042680298.IB</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>1Y</t>
+          <t>0.49Y</t>
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>2.0</v>
+        <v>1.5</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>2.0</v>
+        <v>1.5</v>
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
+          <t>2.64 ~ 3.64</t>
         </is>
       </c>
       <c r="H75" s="4" t="n">
-        <v>1.75</v>
+        <v>3.6</v>
       </c>
       <c r="I75" s="4" t="n">
-        <v>54.7</v>
+        <v>239.89</v>
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>26新疆城建CP001</t>
+          <t>25保利久联MTN001</t>
         </is>
       </c>
       <c r="L75" s="3" t="inlineStr">
         <is>
-          <t>319D</t>
+          <t>190D</t>
         </is>
       </c>
       <c r="M75" s="3" t="inlineStr">
         <is>
-          <t>1.7946</t>
+          <t>3.6560</t>
         </is>
       </c>
       <c r="N75" s="3" t="inlineStr">
@@ -17556,12 +17550,12 @@
       </c>
       <c r="O75" s="3" t="inlineStr">
         <is>
-          <t>新疆城建(集团)股份有限公司</t>
+          <t>保利久联控股集团有限责任公司</t>
         </is>
       </c>
       <c r="P75" s="3" t="inlineStr">
         <is>
-          <t>C- 17.00</t>
+          <t>D+ 7.36</t>
         </is>
       </c>
       <c r="Q75" s="3" t="inlineStr">
@@ -17585,36 +17579,40 @@
         </is>
       </c>
       <c r="U75" s="4" t="n">
-        <v>1.85</v>
+        <v>1.4</v>
       </c>
       <c r="V75" s="4" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="W75" s="3"/>
+        <v>5.0</v>
+      </c>
+      <c r="W75" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="X75" s="3" t="inlineStr">
         <is>
-          <t>1.82%~1.86%</t>
+          <t>3.65%~3.69%</t>
         </is>
       </c>
       <c r="Y75" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z75" s="3"/>
       <c r="AA75" s="3" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区-乌鲁木齐市</t>
+          <t>贵州省-贵阳市</t>
         </is>
       </c>
       <c r="AB75" s="3" t="inlineStr">
         <is>
-          <t>本次短期融资券发行金额为2亿元,募集资金用于偿还发行人本部银行贷款。</t>
+          <t>本期短期融资券发行金额1.50亿元，全部用于偿还发行人有息债务[25保利久联CP003（科创债）]</t>
         </is>
       </c>
       <c r="AC75" s="3" t="inlineStr">
         <is>
-          <t>华夏银行股份有限公司</t>
+          <t>贵阳银行股份有限公司</t>
         </is>
       </c>
       <c r="AD75" s="3"/>
@@ -17625,7 +17623,7 @@
       </c>
       <c r="AF75" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG75" s="3" t="inlineStr">
@@ -17635,7 +17633,7 @@
       </c>
       <c r="AH75" s="3" t="inlineStr">
         <is>
-          <t>新疆城建(集团)股份有限公司2026年度第二期短期融资券</t>
+          <t>保利久联控股集团有限责任公司2026年度第三期短期融资券</t>
         </is>
       </c>
       <c r="AI75" s="3" t="inlineStr">
@@ -17645,7 +17643,7 @@
       </c>
       <c r="AJ75" s="3" t="inlineStr">
         <is>
-          <t>2027-08-26</t>
+          <t>2027-02-22</t>
         </is>
       </c>
       <c r="AK75" s="3"/>
@@ -17671,27 +17669,27 @@
       </c>
       <c r="AP75" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ75" s="3" t="inlineStr">
         <is>
-          <t>建筑施工</t>
+          <t>化工制造</t>
         </is>
       </c>
       <c r="AR75" s="3" t="inlineStr">
         <is>
-          <t>综合建筑施工</t>
+          <t>化学制品</t>
         </is>
       </c>
       <c r="AS75" s="3" t="inlineStr">
         <is>
-          <t>综合建筑施工</t>
+          <t>化学制品</t>
         </is>
       </c>
       <c r="AT75" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>化学制品</t>
         </is>
       </c>
       <c r="AU75" s="3" t="inlineStr">
@@ -17724,7 +17722,7 @@
     <row r="76" customHeight="true" ht="18.0">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>26保利久联CP003</t>
+          <t>26蓉城交通SCP001</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -17734,64 +17732,64 @@
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>042680298.IB</t>
+          <t>012682146.IB</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>0.49Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E76" s="4" t="n">
-        <v>1.5</v>
+        <v>2.0</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>1.5</v>
+        <v>2.0</v>
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2.64 ~ 3.64</t>
+          <t>1.30 ~ 1.90</t>
         </is>
       </c>
       <c r="H76" s="4" t="n">
-        <v>3.6</v>
+        <v>1.52</v>
       </c>
       <c r="I76" s="4" t="n">
-        <v>239.89</v>
+        <v>38.44</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>25保利久联MTN001</t>
+          <t>24成都公交GN002</t>
         </is>
       </c>
       <c r="L76" s="3" t="inlineStr">
         <is>
-          <t>190D</t>
+          <t>349D</t>
         </is>
       </c>
       <c r="M76" s="3" t="inlineStr">
         <is>
-          <t>3.6560</t>
+          <t>1.5802</t>
         </is>
       </c>
       <c r="N76" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6000/1.5600</t>
         </is>
       </c>
       <c r="O76" s="3" t="inlineStr">
         <is>
-          <t>保利久联控股集团有限责任公司</t>
+          <t>成都市公共交通集团有限公司</t>
         </is>
       </c>
       <c r="P76" s="3" t="inlineStr">
         <is>
-          <t>D+ 7.36</t>
+          <t>C+ 32.00</t>
         </is>
       </c>
       <c r="Q76" s="3" t="inlineStr">
@@ -17815,19 +17813,19 @@
         </is>
       </c>
       <c r="U76" s="4" t="n">
-        <v>1.4</v>
+        <v>3.05</v>
       </c>
       <c r="V76" s="4" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="W76" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X76" s="3" t="inlineStr">
         <is>
-          <t>3.65%~3.69%</t>
+          <t>1.57%~1.61%</t>
         </is>
       </c>
       <c r="Y76" s="3" t="inlineStr">
@@ -17838,28 +17836,28 @@
       <c r="Z76" s="3"/>
       <c r="AA76" s="3" t="inlineStr">
         <is>
-          <t>贵州省-贵阳市</t>
+          <t>四川省-成都市</t>
         </is>
       </c>
       <c r="AB76" s="3" t="inlineStr">
         <is>
-          <t>本期短期融资券发行金额1.50亿元，全部用于偿还发行人有息债务[25保利久联CP003（科创债）]</t>
+          <t>发行人本期发行金额2亿元,拟用于偿还发行人到期的有息债务</t>
         </is>
       </c>
       <c r="AC76" s="3" t="inlineStr">
         <is>
-          <t>贵阳银行股份有限公司</t>
+          <t>招商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD76" s="3"/>
       <c r="AE76" s="3" t="inlineStr">
         <is>
-          <t>短期融资券(CP)</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF76" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG76" s="3" t="inlineStr">
@@ -17869,7 +17867,7 @@
       </c>
       <c r="AH76" s="3" t="inlineStr">
         <is>
-          <t>保利久联控股集团有限责任公司2026年度第三期短期融资券</t>
+          <t>成都市公共交通集团有限公司2026年度第一期超短期融资券</t>
         </is>
       </c>
       <c r="AI76" s="3" t="inlineStr">
@@ -17879,10 +17877,14 @@
       </c>
       <c r="AJ76" s="3" t="inlineStr">
         <is>
-          <t>2027-02-22</t>
-        </is>
-      </c>
-      <c r="AK76" s="3"/>
+          <t>2027-05-23</t>
+        </is>
+      </c>
+      <c r="AK76" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL76" s="3" t="inlineStr">
         <is>
           <t>2026-08-27</t>
@@ -17900,32 +17902,32 @@
       </c>
       <c r="AO76" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP76" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ76" s="3" t="inlineStr">
         <is>
-          <t>化工制造</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR76" s="3" t="inlineStr">
         <is>
-          <t>化学制品</t>
+          <t>其他公用</t>
         </is>
       </c>
       <c r="AS76" s="3" t="inlineStr">
         <is>
-          <t>化学制品</t>
+          <t>其他公用</t>
         </is>
       </c>
       <c r="AT76" s="3" t="inlineStr">
         <is>
-          <t>化学制品</t>
+          <t>公交</t>
         </is>
       </c>
       <c r="AU76" s="3" t="inlineStr">
@@ -17958,7 +17960,7 @@
     <row r="77" customHeight="true" ht="18.0">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>26蓉城交通SCP001</t>
+          <t>26海润城发MTN001</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -17968,64 +17970,64 @@
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>012682146.IB</t>
+          <t>102683336.IB</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E77" s="4" t="n">
-        <v>2.0</v>
+        <v>2.2</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>2.0</v>
+        <v>2.2</v>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.90</t>
+          <t>1.60 ~ 2.20</t>
         </is>
       </c>
       <c r="H77" s="4" t="n">
-        <v>1.52</v>
+        <v>1.7</v>
       </c>
       <c r="I77" s="4" t="n">
-        <v>38.44</v>
+        <v>44.67</v>
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>24成都公交GN002</t>
+          <t>24海润G4</t>
         </is>
       </c>
       <c r="L77" s="3" t="inlineStr">
         <is>
-          <t>349D</t>
+          <t>1.22Y</t>
         </is>
       </c>
       <c r="M77" s="3" t="inlineStr">
         <is>
-          <t>1.5802</t>
+          <t>1.6247</t>
         </is>
       </c>
       <c r="N77" s="3" t="inlineStr">
         <is>
-          <t>1.6000/1.5600</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O77" s="3" t="inlineStr">
         <is>
-          <t>成都市公共交通集团有限公司</t>
+          <t>江苏海润城市发展集团有限公司</t>
         </is>
       </c>
       <c r="P77" s="3" t="inlineStr">
         <is>
-          <t>C+ 32.00</t>
+          <t>C- 17.94</t>
         </is>
       </c>
       <c r="Q77" s="3" t="inlineStr">
@@ -18049,19 +18051,17 @@
         </is>
       </c>
       <c r="U77" s="4" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="V77" s="4" t="n">
-        <v>1.0</v>
-      </c>
+        <v>5.2727</v>
+      </c>
+      <c r="V77" s="3"/>
       <c r="W77" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X77" s="3" t="inlineStr">
         <is>
-          <t>1.57%~1.61%</t>
+          <t>1.65%~1.75%</t>
         </is>
       </c>
       <c r="Y77" s="3" t="inlineStr">
@@ -18072,23 +18072,23 @@
       <c r="Z77" s="3"/>
       <c r="AA77" s="3" t="inlineStr">
         <is>
-          <t>四川省-成都市</t>
+          <t>江苏省-南通市</t>
         </is>
       </c>
       <c r="AB77" s="3" t="inlineStr">
         <is>
-          <t>发行人本期发行金额2亿元,拟用于偿还发行人到期的有息债务</t>
+          <t>发行人本期中期票据发行金额为2.2亿元,募集资金用于偿还发行人存量债务融资工具本金[25海润城发SCP005]</t>
         </is>
       </c>
       <c r="AC77" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司</t>
+          <t>南京银行股份有限公司</t>
         </is>
       </c>
       <c r="AD77" s="3"/>
       <c r="AE77" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF77" s="3" t="inlineStr">
@@ -18103,7 +18103,7 @@
       </c>
       <c r="AH77" s="3" t="inlineStr">
         <is>
-          <t>成都市公共交通集团有限公司2026年度第一期超短期融资券</t>
+          <t>江苏海润城市发展集团有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI77" s="3" t="inlineStr">
@@ -18113,7 +18113,7 @@
       </c>
       <c r="AJ77" s="3" t="inlineStr">
         <is>
-          <t>2027-05-23</t>
+          <t>2029-08-26</t>
         </is>
       </c>
       <c r="AK77" s="3" t="inlineStr">
@@ -18143,27 +18143,27 @@
       </c>
       <c r="AP77" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ77" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR77" s="3" t="inlineStr">
         <is>
-          <t>其他公用</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS77" s="3" t="inlineStr">
         <is>
-          <t>其他公用</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT77" s="3" t="inlineStr">
         <is>
-          <t>公交</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU77" s="3" t="inlineStr">
@@ -18191,12 +18191,14 @@
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="AZ77" s="3"/>
+      <c r="AZ77" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="78" customHeight="true" ht="18.0">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>26海润城发MTN001</t>
+          <t>26桂国控SCP005</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -18206,49 +18208,49 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>102683336.IB</t>
+          <t>012682149.IB</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E78" s="4" t="n">
-        <v>2.2</v>
+        <v>7.0</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>2.2</v>
+        <v>7.0</v>
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.20</t>
+          <t>1.39 ~ 1.69</t>
         </is>
       </c>
       <c r="H78" s="4" t="n">
-        <v>1.7</v>
+        <v>1.46</v>
       </c>
       <c r="I78" s="4" t="n">
-        <v>44.67</v>
+        <v>32.44</v>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="K78" s="3" t="inlineStr">
         <is>
-          <t>24海润G4</t>
+          <t>24农垦MTN002A</t>
         </is>
       </c>
       <c r="L78" s="3" t="inlineStr">
         <is>
-          <t>1.22Y</t>
+          <t>324D</t>
         </is>
       </c>
       <c r="M78" s="3" t="inlineStr">
         <is>
-          <t>1.6247</t>
+          <t>1.6104</t>
         </is>
       </c>
       <c r="N78" s="3" t="inlineStr">
@@ -18258,12 +18260,12 @@
       </c>
       <c r="O78" s="3" t="inlineStr">
         <is>
-          <t>江苏海润城市发展集团有限公司</t>
+          <t>广西国控资本运营集团有限责任公司</t>
         </is>
       </c>
       <c r="P78" s="3" t="inlineStr">
         <is>
-          <t>C- 17.94</t>
+          <t>C- 16.55</t>
         </is>
       </c>
       <c r="Q78" s="3" t="inlineStr">
@@ -18287,44 +18289,46 @@
         </is>
       </c>
       <c r="U78" s="4" t="n">
-        <v>5.2727</v>
-      </c>
-      <c r="V78" s="3"/>
+        <v>4.5143</v>
+      </c>
+      <c r="V78" s="4" t="n">
+        <v>1.08</v>
+      </c>
       <c r="W78" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X78" s="3" t="inlineStr">
         <is>
-          <t>1.65%~1.75%</t>
+          <t>1.56%~1.60%</t>
         </is>
       </c>
       <c r="Y78" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z78" s="3"/>
       <c r="AA78" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南通市</t>
+          <t>广西壮族自治区</t>
         </is>
       </c>
       <c r="AB78" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据发行金额为2.2亿元,募集资金用于偿还发行人存量债务融资工具本金[25海润城发SCP005]</t>
+          <t>本期债务融资工具募集资金全部用于归还发行人本部及下属公司的有息债务</t>
         </is>
       </c>
       <c r="AC78" s="3" t="inlineStr">
         <is>
-          <t>南京银行股份有限公司</t>
+          <t>上海浦东发展银行股份有限公司,交通银行股份有限公司</t>
         </is>
       </c>
       <c r="AD78" s="3"/>
       <c r="AE78" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF78" s="3" t="inlineStr">
@@ -18339,7 +18343,7 @@
       </c>
       <c r="AH78" s="3" t="inlineStr">
         <is>
-          <t>江苏海润城市发展集团有限公司2026年度第一期中期票据</t>
+          <t>广西国控资本运营集团有限责任公司2026年度第五期超短期融资券</t>
         </is>
       </c>
       <c r="AI78" s="3" t="inlineStr">
@@ -18349,7 +18353,7 @@
       </c>
       <c r="AJ78" s="3" t="inlineStr">
         <is>
-          <t>2029-08-26</t>
+          <t>2027-05-23</t>
         </is>
       </c>
       <c r="AK78" s="3" t="inlineStr">
@@ -18374,7 +18378,7 @@
       </c>
       <c r="AO78" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP78" s="3" t="inlineStr">
@@ -18384,24 +18388,24 @@
       </c>
       <c r="AQ78" s="3" t="inlineStr">
         <is>
+          <t>农林牧渔</t>
+        </is>
+      </c>
+      <c r="AR78" s="3" t="inlineStr">
+        <is>
+          <t>综合农林牧渔</t>
+        </is>
+      </c>
+      <c r="AS78" s="3" t="inlineStr">
+        <is>
+          <t>综合农林牧渔</t>
+        </is>
+      </c>
+      <c r="AT78" s="3" t="inlineStr">
+        <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="AR78" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS78" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AT78" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
       <c r="AU78" s="3" t="inlineStr">
         <is>
           <t/>
@@ -18427,14 +18431,12 @@
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="AZ78" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ78" s="3"/>
     </row>
     <row r="79" customHeight="true" ht="18.0">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>26桂国控SCP005</t>
+          <t>26铁塔股份MTN004</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -18444,64 +18446,64 @@
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>012682149.IB</t>
+          <t>102683331.IB</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E79" s="4" t="n">
-        <v>7.0</v>
+        <v>40.0</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>7.0</v>
+        <v>40.0</v>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>1.39 ~ 1.69</t>
+          <t>1.40 ~ 1.90</t>
         </is>
       </c>
       <c r="H79" s="4" t="n">
-        <v>1.46</v>
+        <v>1.56</v>
       </c>
       <c r="I79" s="4" t="n">
-        <v>32.44</v>
+        <v>30.67</v>
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>24农垦MTN002A</t>
+          <t>26铁塔股份MTN001</t>
         </is>
       </c>
       <c r="L79" s="3" t="inlineStr">
         <is>
-          <t>324D</t>
+          <t>2.66Y</t>
         </is>
       </c>
       <c r="M79" s="3" t="inlineStr">
         <is>
-          <t>1.6104</t>
+          <t>1.6451</t>
         </is>
       </c>
       <c r="N79" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6600/1.6400</t>
         </is>
       </c>
       <c r="O79" s="3" t="inlineStr">
         <is>
-          <t>广西国控资本运营集团有限责任公司</t>
+          <t>中国铁塔股份有限公司</t>
         </is>
       </c>
       <c r="P79" s="3" t="inlineStr">
         <is>
-          <t>C- 16.55</t>
+          <t>C 26.25</t>
         </is>
       </c>
       <c r="Q79" s="3" t="inlineStr">
@@ -18525,19 +18527,19 @@
         </is>
       </c>
       <c r="U79" s="4" t="n">
-        <v>4.5143</v>
+        <v>1.575</v>
       </c>
       <c r="V79" s="4" t="n">
-        <v>1.08</v>
+        <v>1.0</v>
       </c>
       <c r="W79" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X79" s="3" t="inlineStr">
         <is>
-          <t>1.56%~1.60%</t>
+          <t>1.60%~1.70%</t>
         </is>
       </c>
       <c r="Y79" s="3" t="inlineStr">
@@ -18548,28 +18550,28 @@
       <c r="Z79" s="3"/>
       <c r="AA79" s="3" t="inlineStr">
         <is>
-          <t>广西壮族自治区</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB79" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具募集资金全部用于归还发行人本部及下属公司的有息债务</t>
+          <t>本期中期票据发行金额40亿元,募集资金14.85亿元拟将用于偿还有息债务,25.15亿元拟将用于补充流动资金。</t>
         </is>
       </c>
       <c r="AC79" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司,交通银行股份有限公司</t>
+          <t>招商银行股份有限公司,中国工商银行股份有限公司,中国建设银行股份有限公司</t>
         </is>
       </c>
       <c r="AD79" s="3"/>
       <c r="AE79" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF79" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG79" s="3" t="inlineStr">
@@ -18579,7 +18581,7 @@
       </c>
       <c r="AH79" s="3" t="inlineStr">
         <is>
-          <t>广西国控资本运营集团有限责任公司2026年度第五期超短期融资券</t>
+          <t>中国铁塔股份有限公司2026年度第四期中期票据</t>
         </is>
       </c>
       <c r="AI79" s="3" t="inlineStr">
@@ -18589,7 +18591,7 @@
       </c>
       <c r="AJ79" s="3" t="inlineStr">
         <is>
-          <t>2027-05-23</t>
+          <t>2029-08-26</t>
         </is>
       </c>
       <c r="AK79" s="3" t="inlineStr">
@@ -18619,27 +18621,27 @@
       </c>
       <c r="AP79" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AQ79" s="3" t="inlineStr">
         <is>
-          <t>农林牧渔</t>
+          <t>电子设备制造</t>
         </is>
       </c>
       <c r="AR79" s="3" t="inlineStr">
         <is>
-          <t>综合农林牧渔</t>
+          <t>通信设备</t>
         </is>
       </c>
       <c r="AS79" s="3" t="inlineStr">
         <is>
-          <t>综合农林牧渔</t>
+          <t>通信设备</t>
         </is>
       </c>
       <c r="AT79" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>通信设备</t>
         </is>
       </c>
       <c r="AU79" s="3" t="inlineStr">
@@ -18672,7 +18674,7 @@
     <row r="80" customHeight="true" ht="18.0">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>26铁塔股份MTN004</t>
+          <t>26浙江经投MTN002</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -18682,7 +18684,7 @@
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>102683331.IB</t>
+          <t>102683330.IB</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
@@ -18691,14 +18693,14 @@
         </is>
       </c>
       <c r="E80" s="4" t="n">
-        <v>40.0</v>
+        <v>1.4</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>40.0</v>
+        <v>1.4</v>
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.90</t>
+          <t>1.40 ~ 2.00</t>
         </is>
       </c>
       <c r="H80" s="4" t="n">
@@ -18709,37 +18711,37 @@
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>26铁塔股份MTN001</t>
+          <t>24鲁资K1</t>
         </is>
       </c>
       <c r="L80" s="3" t="inlineStr">
         <is>
-          <t>2.66Y</t>
+          <t>3.00Y</t>
         </is>
       </c>
       <c r="M80" s="3" t="inlineStr">
         <is>
-          <t>1.6451</t>
+          <t>1.6616</t>
         </is>
       </c>
       <c r="N80" s="3" t="inlineStr">
         <is>
-          <t>1.6600/1.6400</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O80" s="3" t="inlineStr">
         <is>
-          <t>中国铁塔股份有限公司</t>
+          <t>浙江省经济建设投资有限公司</t>
         </is>
       </c>
       <c r="P80" s="3" t="inlineStr">
         <is>
-          <t>C 26.25</t>
+          <t>D+ 6.50</t>
         </is>
       </c>
       <c r="Q80" s="3" t="inlineStr">
@@ -18763,19 +18765,19 @@
         </is>
       </c>
       <c r="U80" s="4" t="n">
-        <v>1.575</v>
+        <v>2.55</v>
       </c>
       <c r="V80" s="4" t="n">
         <v>1.0</v>
       </c>
       <c r="W80" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X80" s="3" t="inlineStr">
         <is>
-          <t>1.60%~1.70%</t>
+          <t>1.51%~1.61%</t>
         </is>
       </c>
       <c r="Y80" s="3" t="inlineStr">
@@ -18784,19 +18786,15 @@
         </is>
       </c>
       <c r="Z80" s="3"/>
-      <c r="AA80" s="3" t="inlineStr">
-        <is>
-          <t>北京市</t>
-        </is>
-      </c>
+      <c r="AA80" s="3"/>
       <c r="AB80" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额40亿元,募集资金14.85亿元拟将用于偿还有息债务,25.15亿元拟将用于补充流动资金。</t>
+          <t>发行人本期发行金额1.4亿元,募集资金拟用于偿还发行人的有息债务1.4亿元</t>
         </is>
       </c>
       <c r="AC80" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司,中国工商银行股份有限公司,中国建设银行股份有限公司</t>
+          <t>上海浦东发展银行股份有限公司,南京银行股份有限公司</t>
         </is>
       </c>
       <c r="AD80" s="3"/>
@@ -18807,7 +18805,7 @@
       </c>
       <c r="AF80" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG80" s="3" t="inlineStr">
@@ -18817,7 +18815,7 @@
       </c>
       <c r="AH80" s="3" t="inlineStr">
         <is>
-          <t>中国铁塔股份有限公司2026年度第四期中期票据</t>
+          <t>浙江省经济建设投资有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI80" s="3" t="inlineStr">
@@ -18842,7 +18840,7 @@
       </c>
       <c r="AM80" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="AN80" s="3" t="inlineStr">
@@ -18852,32 +18850,28 @@
       </c>
       <c r="AO80" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP80" s="3" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP80" s="3"/>
       <c r="AQ80" s="3" t="inlineStr">
         <is>
-          <t>电子设备制造</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR80" s="3" t="inlineStr">
         <is>
-          <t>通信设备</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS80" s="3" t="inlineStr">
         <is>
-          <t>通信设备</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT80" s="3" t="inlineStr">
         <is>
-          <t>通信设备</t>
+          <t>元件</t>
         </is>
       </c>
       <c r="AU80" s="3" t="inlineStr">
@@ -18910,7 +18904,7 @@
     <row r="81" customHeight="true" ht="18.0">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>26浙江经投MTN002</t>
+          <t>26鄂州城投MTN001</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -18920,64 +18914,64 @@
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>102683330.IB</t>
+          <t>102683358.IB</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E81" s="4" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.00</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="H81" s="4" t="n">
-        <v>1.56</v>
+        <v>2.13</v>
       </c>
       <c r="I81" s="4" t="n">
-        <v>30.67</v>
+        <v>74.28</v>
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>24鲁资K1</t>
+          <t>25鄂州城投MTN002</t>
         </is>
       </c>
       <c r="L81" s="3" t="inlineStr">
         <is>
-          <t>3.00Y</t>
+          <t>4.08Y</t>
         </is>
       </c>
       <c r="M81" s="3" t="inlineStr">
         <is>
-          <t>1.6616</t>
+          <t>2.0866</t>
         </is>
       </c>
       <c r="N81" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.1200/--</t>
         </is>
       </c>
       <c r="O81" s="3" t="inlineStr">
         <is>
-          <t>浙江省经济建设投资有限公司</t>
+          <t>鄂州市城市建设投资有限公司</t>
         </is>
       </c>
       <c r="P81" s="3" t="inlineStr">
         <is>
-          <t>D+ 6.50</t>
+          <t>C- 14.37</t>
         </is>
       </c>
       <c r="Q81" s="3" t="inlineStr">
@@ -18987,7 +18981,7 @@
       </c>
       <c r="R81" s="3" t="inlineStr">
         <is>
-          <t>08-25 09:00</t>
+          <t>08-25 15:00</t>
         </is>
       </c>
       <c r="S81" s="3" t="inlineStr">
@@ -19001,36 +18995,40 @@
         </is>
       </c>
       <c r="U81" s="4" t="n">
-        <v>2.55</v>
+        <v>3.875</v>
       </c>
       <c r="V81" s="4" t="n">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
       <c r="W81" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X81" s="3" t="inlineStr">
         <is>
-          <t>1.51%~1.61%</t>
+          <t>2.11%~2.21%</t>
         </is>
       </c>
       <c r="Y81" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z81" s="3"/>
-      <c r="AA81" s="3"/>
+      <c r="AA81" s="3" t="inlineStr">
+        <is>
+          <t>湖北省-鄂州市</t>
+        </is>
+      </c>
       <c r="AB81" s="3" t="inlineStr">
         <is>
-          <t>发行人本期发行金额1.4亿元,募集资金拟用于偿还发行人的有息债务1.4亿元</t>
+          <t>本期中期票据发行规模为2.40亿元,拟偿还的非金融企业债务融资工具本金[24鄂州城投MTN001]</t>
         </is>
       </c>
       <c r="AC81" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司,南京银行股份有限公司</t>
+          <t>国泰海通证券股份有限公司,申万宏源证券有限公司</t>
         </is>
       </c>
       <c r="AD81" s="3"/>
@@ -19051,7 +19049,7 @@
       </c>
       <c r="AH81" s="3" t="inlineStr">
         <is>
-          <t>浙江省经济建设投资有限公司2026年度第二期中期票据</t>
+          <t>鄂州市城市建设投资有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI81" s="3" t="inlineStr">
@@ -19061,14 +19059,10 @@
       </c>
       <c r="AJ81" s="3" t="inlineStr">
         <is>
-          <t>2029-08-26</t>
-        </is>
-      </c>
-      <c r="AK81" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-08-26</t>
+        </is>
+      </c>
+      <c r="AK81" s="3"/>
       <c r="AL81" s="3" t="inlineStr">
         <is>
           <t>2026-08-27</t>
@@ -19076,7 +19070,7 @@
       </c>
       <c r="AM81" s="3" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AN81" s="3" t="inlineStr">
@@ -19086,10 +19080,14 @@
       </c>
       <c r="AO81" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP81" s="3"/>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP81" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="AQ81" s="3" t="inlineStr">
         <is>
           <t>综合</t>
@@ -19097,17 +19095,17 @@
       </c>
       <c r="AR81" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS81" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT81" s="3" t="inlineStr">
         <is>
-          <t>元件</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU81" s="3" t="inlineStr">
@@ -19140,7 +19138,7 @@
     <row r="82" customHeight="true" ht="18.0">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>26鄂州城投MTN001</t>
+          <t>26环球租赁MTN002</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -19150,64 +19148,64 @@
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>102683358.IB</t>
+          <t>102683348.IB</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E82" s="4" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.50 ~ 1.73</t>
         </is>
       </c>
       <c r="H82" s="4" t="n">
-        <v>2.13</v>
+        <v>1.73</v>
       </c>
       <c r="I82" s="4" t="n">
-        <v>74.28</v>
+        <v>49.39</v>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t>25鄂州城投MTN002</t>
+          <t>25环球租赁MTN002</t>
         </is>
       </c>
       <c r="L82" s="3" t="inlineStr">
         <is>
-          <t>4.08Y</t>
+          <t>2.00Y</t>
         </is>
       </c>
       <c r="M82" s="3" t="inlineStr">
         <is>
-          <t>2.0866</t>
+          <t>1.7483</t>
         </is>
       </c>
       <c r="N82" s="3" t="inlineStr">
         <is>
-          <t>2.1200/--</t>
+          <t>1.7700/1.7000</t>
         </is>
       </c>
       <c r="O82" s="3" t="inlineStr">
         <is>
-          <t>鄂州市城市建设投资有限公司</t>
+          <t>中国环球租赁有限公司</t>
         </is>
       </c>
       <c r="P82" s="3" t="inlineStr">
         <is>
-          <t>C- 14.37</t>
+          <t>C- 19.27</t>
         </is>
       </c>
       <c r="Q82" s="3" t="inlineStr">
@@ -19217,7 +19215,7 @@
       </c>
       <c r="R82" s="3" t="inlineStr">
         <is>
-          <t>08-25 15:00</t>
+          <t>08-25 10:00</t>
         </is>
       </c>
       <c r="S82" s="3" t="inlineStr">
@@ -19231,40 +19229,38 @@
         </is>
       </c>
       <c r="U82" s="4" t="n">
-        <v>3.875</v>
-      </c>
-      <c r="V82" s="4" t="n">
-        <v>8.0</v>
-      </c>
+        <v>1.28</v>
+      </c>
+      <c r="V82" s="3"/>
       <c r="W82" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X82" s="3" t="inlineStr">
         <is>
-          <t>2.11%~2.21%</t>
+          <t>1.68%~1.78%</t>
         </is>
       </c>
       <c r="Y82" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3" t="inlineStr">
         <is>
-          <t>湖北省-鄂州市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB82" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行规模为2.40亿元,拟偿还的非金融企业债务融资工具本金[24鄂州城投MTN001]</t>
+          <t>本期中期票据发行金额为2.5亿元,用于偿还发行人存量债务融资工具[25环球租赁SCP014]</t>
         </is>
       </c>
       <c r="AC82" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,申万宏源证券有限公司</t>
+          <t>天津银行股份有限公司,中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD82" s="3"/>
@@ -19275,7 +19271,7 @@
       </c>
       <c r="AF82" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG82" s="3" t="inlineStr">
@@ -19285,7 +19281,7 @@
       </c>
       <c r="AH82" s="3" t="inlineStr">
         <is>
-          <t>鄂州市城市建设投资有限公司2026年度第一期中期票据</t>
+          <t>中国环球租赁有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI82" s="3" t="inlineStr">
@@ -19295,10 +19291,14 @@
       </c>
       <c r="AJ82" s="3" t="inlineStr">
         <is>
-          <t>2031-08-26</t>
-        </is>
-      </c>
-      <c r="AK82" s="3"/>
+          <t>2028-08-26</t>
+        </is>
+      </c>
+      <c r="AK82" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL82" s="3" t="inlineStr">
         <is>
           <t>2026-08-27</t>
@@ -19316,32 +19316,32 @@
       </c>
       <c r="AO82" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP82" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ82" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR82" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AS82" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AT82" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU82" s="3" t="inlineStr">
@@ -19369,12 +19369,14 @@
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="AZ82" s="3"/>
+      <c r="AZ82" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="83" customHeight="true" ht="18.0">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>26环球租赁MTN002</t>
+          <t>26唐山工业MTN002</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -19384,64 +19386,64 @@
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>102683348.IB</t>
+          <t>102683351.IB</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E83" s="4" t="n">
-        <v>2.5</v>
+        <v>5.0</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>2.5</v>
+        <v>5.0</v>
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.73</t>
+          <t>2.00 ~ 3.00</t>
         </is>
       </c>
       <c r="H83" s="4" t="n">
-        <v>1.73</v>
+        <v>2.35</v>
       </c>
       <c r="I83" s="4" t="n">
-        <v>49.39</v>
+        <v>109.67</v>
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>25环球租赁MTN002</t>
+          <t>26唐山工业MTN001(并购)</t>
         </is>
       </c>
       <c r="L83" s="3" t="inlineStr">
         <is>
-          <t>2.00Y</t>
+          <t>2.79Y</t>
         </is>
       </c>
       <c r="M83" s="3" t="inlineStr">
         <is>
-          <t>1.7483</t>
+          <t>2.3729</t>
         </is>
       </c>
       <c r="N83" s="3" t="inlineStr">
         <is>
-          <t>1.7700/1.7000</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O83" s="3" t="inlineStr">
         <is>
-          <t>中国环球租赁有限公司</t>
+          <t>唐山工业控股集团有限公司</t>
         </is>
       </c>
       <c r="P83" s="3" t="inlineStr">
         <is>
-          <t>C- 19.27</t>
+          <t>C 28.38</t>
         </is>
       </c>
       <c r="Q83" s="3" t="inlineStr">
@@ -19451,7 +19453,7 @@
       </c>
       <c r="R83" s="3" t="inlineStr">
         <is>
-          <t>08-25 10:00</t>
+          <t>08-25 14:00</t>
         </is>
       </c>
       <c r="S83" s="3" t="inlineStr">
@@ -19465,38 +19467,40 @@
         </is>
       </c>
       <c r="U83" s="4" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V83" s="3"/>
+        <v>1.68</v>
+      </c>
+      <c r="V83" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W83" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>7-</t>
         </is>
       </c>
       <c r="X83" s="3" t="inlineStr">
         <is>
-          <t>1.68%~1.78%</t>
+          <t>2.40%~2.50%</t>
         </is>
       </c>
       <c r="Y83" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z83" s="3"/>
       <c r="AA83" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>河北省-唐山市</t>
         </is>
       </c>
       <c r="AB83" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额为2.5亿元,用于偿还发行人存量债务融资工具[25环球租赁SCP014]</t>
+          <t>发行人本期中期票据基础发行规模0亿元,发行金额上限5.00亿元,募集资金全部用于偿还债务融资工具[25唐山工业MTN003,25唐山工业MTN004,24唐山工业MTN001B,24唐山工业MTN001A,25唐山工业MTN001A]</t>
         </is>
       </c>
       <c r="AC83" s="3" t="inlineStr">
         <is>
-          <t>天津银行股份有限公司,中信银行股份有限公司</t>
+          <t>东方证券股份有限公司,天津银行股份有限公司</t>
         </is>
       </c>
       <c r="AD83" s="3"/>
@@ -19507,7 +19511,7 @@
       </c>
       <c r="AF83" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG83" s="3" t="inlineStr">
@@ -19517,7 +19521,7 @@
       </c>
       <c r="AH83" s="3" t="inlineStr">
         <is>
-          <t>中国环球租赁有限公司2026年度第二期中期票据</t>
+          <t>唐山工业控股集团有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI83" s="3" t="inlineStr">
@@ -19527,12 +19531,12 @@
       </c>
       <c r="AJ83" s="3" t="inlineStr">
         <is>
-          <t>2028-08-26</t>
+          <t>2029-08-26</t>
         </is>
       </c>
       <c r="AK83" s="3" t="inlineStr">
         <is>
-          <t>休2</t>
+          <t>休1</t>
         </is>
       </c>
       <c r="AL83" s="3" t="inlineStr">
@@ -19552,32 +19556,32 @@
       </c>
       <c r="AO83" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP83" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ83" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>化工制造</t>
         </is>
       </c>
       <c r="AR83" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>化学制品</t>
         </is>
       </c>
       <c r="AS83" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>化学制品</t>
         </is>
       </c>
       <c r="AT83" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>化学制品</t>
         </is>
       </c>
       <c r="AU83" s="3" t="inlineStr">
@@ -19605,14 +19609,12 @@
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="AZ83" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ83" s="3"/>
     </row>
     <row r="84" customHeight="true" ht="18.0">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>26唐山工业MTN002</t>
+          <t>26国丰集团MTN004B</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -19622,12 +19624,12 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>102683351.IB</t>
+          <t>102683343.IB</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E84" s="4" t="n">
@@ -19638,48 +19640,48 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 3.00</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H84" s="4" t="n">
-        <v>2.35</v>
+        <v>1.69</v>
       </c>
       <c r="I84" s="4" t="n">
-        <v>109.67</v>
+        <v>30.28</v>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="K84" s="3" t="inlineStr">
         <is>
-          <t>26唐山工业MTN001(并购)</t>
+          <t>26国丰04</t>
         </is>
       </c>
       <c r="L84" s="3" t="inlineStr">
         <is>
-          <t>2.79Y</t>
+          <t>4.91Y</t>
         </is>
       </c>
       <c r="M84" s="3" t="inlineStr">
         <is>
-          <t>2.3729</t>
+          <t>1.7923</t>
         </is>
       </c>
       <c r="N84" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8000/1.7700</t>
         </is>
       </c>
       <c r="O84" s="3" t="inlineStr">
         <is>
-          <t>唐山工业控股集团有限公司</t>
+          <t>烟台国丰投资控股集团有限公司</t>
         </is>
       </c>
       <c r="P84" s="3" t="inlineStr">
         <is>
-          <t>C 28.38</t>
+          <t>C- 23.98</t>
         </is>
       </c>
       <c r="Q84" s="3" t="inlineStr">
@@ -19689,7 +19691,7 @@
       </c>
       <c r="R84" s="3" t="inlineStr">
         <is>
-          <t>08-25 14:00</t>
+          <t>08-25 09:00</t>
         </is>
       </c>
       <c r="S84" s="3" t="inlineStr">
@@ -19703,40 +19705,44 @@
         </is>
       </c>
       <c r="U84" s="4" t="n">
-        <v>1.68</v>
+        <v>6.74</v>
       </c>
       <c r="V84" s="4" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="W84" s="3" t="inlineStr">
         <is>
-          <t>7-</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X84" s="3" t="inlineStr">
         <is>
-          <t>2.40%~2.50%</t>
+          <t>1.77%~1.87%</t>
         </is>
       </c>
       <c r="Y84" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z84" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z84" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA84" s="3" t="inlineStr">
         <is>
-          <t>河北省-唐山市</t>
+          <t>山东省-烟台市</t>
         </is>
       </c>
       <c r="AB84" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据基础发行规模0亿元,发行金额上限5.00亿元,募集资金全部用于偿还债务融资工具[25唐山工业MTN003,25唐山工业MTN004,24唐山工业MTN001B,24唐山工业MTN001A,25唐山工业MTN001A]</t>
+          <t>本期中期票据基础发行规模0亿元,发行规模上限15亿元,所募集资金拟用于偿还发行人的有息负债。</t>
         </is>
       </c>
       <c r="AC84" s="3" t="inlineStr">
         <is>
-          <t>东方证券股份有限公司,天津银行股份有限公司</t>
+          <t>恒丰银行股份有限公司,中国民生银行股份有限公司</t>
         </is>
       </c>
       <c r="AD84" s="3"/>
@@ -19757,7 +19763,7 @@
       </c>
       <c r="AH84" s="3" t="inlineStr">
         <is>
-          <t>唐山工业控股集团有限公司2026年度第二期中期票据</t>
+          <t>烟台国丰投资控股集团有限公司2026年度第四期中期票据(品种二)</t>
         </is>
       </c>
       <c r="AI84" s="3" t="inlineStr">
@@ -19767,14 +19773,10 @@
       </c>
       <c r="AJ84" s="3" t="inlineStr">
         <is>
-          <t>2029-08-26</t>
-        </is>
-      </c>
-      <c r="AK84" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-08-26</t>
+        </is>
+      </c>
+      <c r="AK84" s="3"/>
       <c r="AL84" s="3" t="inlineStr">
         <is>
           <t>2026-08-27</t>
@@ -19797,7 +19799,7 @@
       </c>
       <c r="AP84" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ84" s="3" t="inlineStr">
@@ -19850,7 +19852,7 @@
     <row r="85" customHeight="true" ht="18.0">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>26国丰集团MTN004B</t>
+          <t>26一汽租赁MTN003</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -19860,64 +19862,64 @@
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>102683343.IB</t>
+          <t>102683354.IB</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E85" s="4" t="n">
-        <v>5.0</v>
+        <v>15.0</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>5.0</v>
+        <v>15.0</v>
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.30 ~ 1.66</t>
         </is>
       </c>
       <c r="H85" s="4" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="I85" s="4" t="n">
-        <v>30.28</v>
+        <v>42.39</v>
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>26国丰04</t>
+          <t>26一汽租赁MTN002</t>
         </is>
       </c>
       <c r="L85" s="3" t="inlineStr">
         <is>
-          <t>4.91Y</t>
+          <t>1.75Y</t>
         </is>
       </c>
       <c r="M85" s="3" t="inlineStr">
         <is>
-          <t>1.7923</t>
+          <t>1.6648</t>
         </is>
       </c>
       <c r="N85" s="3" t="inlineStr">
         <is>
-          <t>1.8000/1.7700</t>
+          <t>1.6600/1.6300</t>
         </is>
       </c>
       <c r="O85" s="3" t="inlineStr">
         <is>
-          <t>烟台国丰投资控股集团有限公司</t>
+          <t>一汽租赁有限公司</t>
         </is>
       </c>
       <c r="P85" s="3" t="inlineStr">
         <is>
-          <t>C- 23.98</t>
+          <t>C+ 34.14</t>
         </is>
       </c>
       <c r="Q85" s="3" t="inlineStr">
@@ -19941,19 +19943,17 @@
         </is>
       </c>
       <c r="U85" s="4" t="n">
-        <v>6.74</v>
-      </c>
-      <c r="V85" s="4" t="n">
-        <v>3.0</v>
-      </c>
+        <v>0.4067</v>
+      </c>
+      <c r="V85" s="3"/>
       <c r="W85" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X85" s="3" t="inlineStr">
         <is>
-          <t>1.77%~1.87%</t>
+          <t>1.61%~1.71%</t>
         </is>
       </c>
       <c r="Y85" s="3" t="inlineStr">
@@ -19961,24 +19961,20 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z85" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z85" s="3"/>
       <c r="AA85" s="3" t="inlineStr">
         <is>
-          <t>山东省-烟台市</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="AB85" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据基础发行规模0亿元,发行规模上限15亿元,所募集资金拟用于偿还发行人的有息负债。</t>
+          <t>发行人本期发行中期票据15亿元,本期募集资金15亿元全部用于偿还有息债务</t>
         </is>
       </c>
       <c r="AC85" s="3" t="inlineStr">
         <is>
-          <t>恒丰银行股份有限公司,中国民生银行股份有限公司</t>
+          <t>平安银行股份有限公司,兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD85" s="3"/>
@@ -19989,7 +19985,7 @@
       </c>
       <c r="AF85" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG85" s="3" t="inlineStr">
@@ -19999,7 +19995,7 @@
       </c>
       <c r="AH85" s="3" t="inlineStr">
         <is>
-          <t>烟台国丰投资控股集团有限公司2026年度第四期中期票据(品种二)</t>
+          <t>一汽租赁有限公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI85" s="3" t="inlineStr">
@@ -20009,7 +20005,7 @@
       </c>
       <c r="AJ85" s="3" t="inlineStr">
         <is>
-          <t>2031-08-26</t>
+          <t>2028-08-25</t>
         </is>
       </c>
       <c r="AK85" s="3"/>
@@ -20030,32 +20026,32 @@
       </c>
       <c r="AO85" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP85" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ85" s="3" t="inlineStr">
         <is>
-          <t>化工制造</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR85" s="3" t="inlineStr">
         <is>
-          <t>化学制品</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AS85" s="3" t="inlineStr">
         <is>
-          <t>化学制品</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AT85" s="3" t="inlineStr">
         <is>
-          <t>化学制品</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU85" s="3" t="inlineStr">
@@ -20088,7 +20084,7 @@
     <row r="86" customHeight="true" ht="18.0">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>26一汽租赁MTN003</t>
+          <t>26华能水电GN012</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -20098,64 +20094,64 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>102683354.IB</t>
+          <t>132680089.IB</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E86" s="4" t="n">
-        <v>15.0</v>
+        <v>10.0</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>15.0</v>
+        <v>10.0</v>
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.66</t>
+          <t>1.70 ~ 2.10</t>
         </is>
       </c>
       <c r="H86" s="4" t="n">
-        <v>1.66</v>
+        <v>1.88</v>
       </c>
       <c r="I86" s="4" t="n">
-        <v>42.39</v>
+        <v>49.28</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="K86" s="3" t="inlineStr">
         <is>
-          <t>26一汽租赁MTN002</t>
+          <t>26华能水电GN010</t>
         </is>
       </c>
       <c r="L86" s="3" t="inlineStr">
         <is>
-          <t>1.75Y</t>
+          <t>4.88Y+N</t>
         </is>
       </c>
       <c r="M86" s="3" t="inlineStr">
         <is>
-          <t>1.6648</t>
+          <t>1.8930</t>
         </is>
       </c>
       <c r="N86" s="3" t="inlineStr">
         <is>
-          <t>1.6600/1.6300</t>
+          <t>1.9200/--</t>
         </is>
       </c>
       <c r="O86" s="3" t="inlineStr">
         <is>
-          <t>一汽租赁有限公司</t>
+          <t>华能澜沧江水电股份有限公司</t>
         </is>
       </c>
       <c r="P86" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.14</t>
+          <t>C- 20.81</t>
         </is>
       </c>
       <c r="Q86" s="3" t="inlineStr">
@@ -20179,17 +20175,19 @@
         </is>
       </c>
       <c r="U86" s="4" t="n">
-        <v>0.4067</v>
-      </c>
-      <c r="V86" s="3"/>
+        <v>3.18</v>
+      </c>
+      <c r="V86" s="4" t="n">
+        <v>2.79</v>
+      </c>
       <c r="W86" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X86" s="3" t="inlineStr">
         <is>
-          <t>1.61%~1.71%</t>
+          <t>1.85%~1.95%</t>
         </is>
       </c>
       <c r="Y86" s="3" t="inlineStr">
@@ -20200,17 +20198,17 @@
       <c r="Z86" s="3"/>
       <c r="AA86" s="3" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>云南省-昆明市</t>
         </is>
       </c>
       <c r="AB86" s="3" t="inlineStr">
         <is>
-          <t>发行人本期发行中期票据15亿元,本期募集资金15亿元全部用于偿还有息债务</t>
+          <t>本期绿色中期票据拟发行金额10亿元,募集资金将用于偿还26华能水电GN005(乡村振兴)的本金。本期募集资金穿透后用于景洪水电站、糯扎渡水电站、黄登水电站、漫湾水电站等4个绿色项目[26华能水电GN005(乡村振兴)]</t>
         </is>
       </c>
       <c r="AC86" s="3" t="inlineStr">
         <is>
-          <t>平安银行股份有限公司,兴业银行股份有限公司</t>
+          <t>中国银行股份有限公司,中国工商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD86" s="3"/>
@@ -20231,7 +20229,7 @@
       </c>
       <c r="AH86" s="3" t="inlineStr">
         <is>
-          <t>一汽租赁有限公司2026年度第三期中期票据</t>
+          <t>华能澜沧江水电股份有限公司2026年度第十二期绿色中期票据</t>
         </is>
       </c>
       <c r="AI86" s="3" t="inlineStr">
@@ -20241,7 +20239,7 @@
       </c>
       <c r="AJ86" s="3" t="inlineStr">
         <is>
-          <t>2028-08-25</t>
+          <t>2031-08-26</t>
         </is>
       </c>
       <c r="AK86" s="3"/>
@@ -20262,32 +20260,32 @@
       </c>
       <c r="AO86" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP86" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AQ86" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR86" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AS86" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>水电</t>
         </is>
       </c>
       <c r="AT86" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU86" s="3" t="inlineStr">
@@ -20302,12 +20300,12 @@
       </c>
       <c r="AW86" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX86" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY86" s="3" t="inlineStr">
@@ -20320,7 +20318,7 @@
     <row r="87" customHeight="true" ht="18.0">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>26华能水电GN012</t>
+          <t>26中交投SCP003</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -20330,12 +20328,12 @@
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>132680089.IB</t>
+          <t>012682144.IB</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>0.31Y</t>
         </is>
       </c>
       <c r="E87" s="4" t="n">
@@ -20346,48 +20344,48 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.10</t>
+          <t>1.30 ~ 1.55</t>
         </is>
       </c>
       <c r="H87" s="4" t="n">
-        <v>1.88</v>
+        <v>1.39</v>
       </c>
       <c r="I87" s="4" t="n">
-        <v>49.28</v>
+        <v>20.17</v>
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>26华能水电GN010</t>
+          <t>26中交投SCP002</t>
         </is>
       </c>
       <c r="L87" s="3" t="inlineStr">
         <is>
-          <t>4.88Y+N</t>
+          <t>108D</t>
         </is>
       </c>
       <c r="M87" s="3" t="inlineStr">
         <is>
-          <t>1.8930</t>
+          <t>1.5156</t>
         </is>
       </c>
       <c r="N87" s="3" t="inlineStr">
         <is>
-          <t>1.9200/--</t>
+          <t>1.5100/1.5000</t>
         </is>
       </c>
       <c r="O87" s="3" t="inlineStr">
         <is>
-          <t>华能澜沧江水电股份有限公司</t>
+          <t>中交投资有限公司</t>
         </is>
       </c>
       <c r="P87" s="3" t="inlineStr">
         <is>
-          <t>C- 20.81</t>
+          <t>C- 21.57</t>
         </is>
       </c>
       <c r="Q87" s="3" t="inlineStr">
@@ -20411,11 +20409,9 @@
         </is>
       </c>
       <c r="U87" s="4" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="V87" s="4" t="n">
-        <v>2.79</v>
-      </c>
+        <v>2.38</v>
+      </c>
+      <c r="V87" s="3"/>
       <c r="W87" s="3" t="inlineStr">
         <is>
           <t>3</t>
@@ -20423,7 +20419,7 @@
       </c>
       <c r="X87" s="3" t="inlineStr">
         <is>
-          <t>1.85%~1.95%</t>
+          <t>1.52%~1.56%</t>
         </is>
       </c>
       <c r="Y87" s="3" t="inlineStr">
@@ -20434,23 +20430,23 @@
       <c r="Z87" s="3"/>
       <c r="AA87" s="3" t="inlineStr">
         <is>
-          <t>云南省-昆明市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB87" s="3" t="inlineStr">
         <is>
-          <t>本期绿色中期票据拟发行金额10亿元,募集资金将用于偿还26华能水电GN005(乡村振兴)的本金。本期募集资金穿透后用于景洪水电站、糯扎渡水电站、黄登水电站、漫湾水电站等4个绿色项目[26华能水电GN005(乡村振兴)]</t>
+          <t>本期超短期融资券发行规模为10亿元,拟全部用于偿还发行人有息债务。</t>
         </is>
       </c>
       <c r="AC87" s="3" t="inlineStr">
         <is>
-          <t>中国银行股份有限公司,中国工商银行股份有限公司</t>
+          <t>广发银行股份有限公司,杭州银行股份有限公司</t>
         </is>
       </c>
       <c r="AD87" s="3"/>
       <c r="AE87" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF87" s="3" t="inlineStr">
@@ -20465,7 +20461,7 @@
       </c>
       <c r="AH87" s="3" t="inlineStr">
         <is>
-          <t>华能澜沧江水电股份有限公司2026年度第十二期绿色中期票据</t>
+          <t>中交投资有限公司2026年度第三期超短期融资券</t>
         </is>
       </c>
       <c r="AI87" s="3" t="inlineStr">
@@ -20475,7 +20471,7 @@
       </c>
       <c r="AJ87" s="3" t="inlineStr">
         <is>
-          <t>2031-08-26</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="AK87" s="3"/>
@@ -20501,27 +20497,27 @@
       </c>
       <c r="AP87" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AQ87" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>建筑施工</t>
         </is>
       </c>
       <c r="AR87" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>专业工程</t>
         </is>
       </c>
       <c r="AS87" s="3" t="inlineStr">
         <is>
-          <t>水电</t>
+          <t>其他专业工程</t>
         </is>
       </c>
       <c r="AT87" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU87" s="3" t="inlineStr">
@@ -20536,12 +20532,12 @@
       </c>
       <c r="AW87" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX87" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY87" s="3" t="inlineStr">
@@ -20549,79 +20545,81 @@
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="AZ87" s="3"/>
+      <c r="AZ87" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="88" customHeight="true" ht="18.0">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>26中交投SCP003</t>
+          <t>26华为MTN004</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>08-25 18:00</t>
+          <t>08-26 18:00</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>012682144.IB</t>
+          <t>102683368.IB</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>0.31Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E88" s="4" t="n">
-        <v>10.0</v>
+        <v>40.0</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>10.0</v>
+        <v>40.0</v>
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.55</t>
+          <t>1.35 ~ 1.95</t>
         </is>
       </c>
       <c r="H88" s="4" t="n">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="I88" s="4" t="n">
-        <v>20.17</v>
+        <v>23.61</v>
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="K88" s="3" t="inlineStr">
         <is>
-          <t>26中交投SCP002</t>
+          <t>26华为MTN003</t>
         </is>
       </c>
       <c r="L88" s="3" t="inlineStr">
         <is>
-          <t>108D</t>
+          <t>2.98Y</t>
         </is>
       </c>
       <c r="M88" s="3" t="inlineStr">
         <is>
-          <t>1.5156</t>
+          <t>1.6621</t>
         </is>
       </c>
       <c r="N88" s="3" t="inlineStr">
         <is>
-          <t>1.5100/1.5000</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O88" s="3" t="inlineStr">
         <is>
-          <t>中交投资有限公司</t>
+          <t>华为投资控股有限公司</t>
         </is>
       </c>
       <c r="P88" s="3" t="inlineStr">
         <is>
-          <t>C- 21.57</t>
+          <t>C+ 34.52</t>
         </is>
       </c>
       <c r="Q88" s="3" t="inlineStr">
@@ -20641,13 +20639,15 @@
       </c>
       <c r="T88" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="U88" s="4" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="V88" s="3"/>
+        <v>2.6675</v>
+      </c>
+      <c r="V88" s="4" t="n">
+        <v>1.52</v>
+      </c>
       <c r="W88" s="3" t="inlineStr">
         <is>
           <t>3</t>
@@ -20655,7 +20655,7 @@
       </c>
       <c r="X88" s="3" t="inlineStr">
         <is>
-          <t>1.52%~1.56%</t>
+          <t>1.60%~1.70%</t>
         </is>
       </c>
       <c r="Y88" s="3" t="inlineStr">
@@ -20666,28 +20666,28 @@
       <c r="Z88" s="3"/>
       <c r="AA88" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB88" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行规模为10亿元,拟全部用于偿还发行人有息债务。</t>
+          <t>公司本次拟发行40亿元中期票据,将用于补充公司本部及下属子公司营运资金</t>
         </is>
       </c>
       <c r="AC88" s="3" t="inlineStr">
         <is>
-          <t>广发银行股份有限公司,杭州银行股份有限公司</t>
+          <t>中国银行股份有限公司,中国工商银行股份有限公司,中国建设银行股份有限公司</t>
         </is>
       </c>
       <c r="AD88" s="3"/>
       <c r="AE88" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF88" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG88" s="3" t="inlineStr">
@@ -20697,7 +20697,7 @@
       </c>
       <c r="AH88" s="3" t="inlineStr">
         <is>
-          <t>中交投资有限公司2026年度第三期超短期融资券</t>
+          <t>华为投资控股有限公司2026年度第四期中期票据</t>
         </is>
       </c>
       <c r="AI88" s="3" t="inlineStr">
@@ -20707,88 +20707,86 @@
       </c>
       <c r="AJ88" s="3" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2029-08-27</t>
         </is>
       </c>
       <c r="AK88" s="3"/>
       <c r="AL88" s="3" t="inlineStr">
         <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AM88" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AN88" s="3" t="inlineStr">
+        <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="AM88" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="AN88" s="3" t="inlineStr">
+      <c r="AO88" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP88" s="3" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="AQ88" s="3" t="inlineStr">
+        <is>
+          <t>电子设备制造</t>
+        </is>
+      </c>
+      <c r="AR88" s="3" t="inlineStr">
+        <is>
+          <t>综合电子设备</t>
+        </is>
+      </c>
+      <c r="AS88" s="3" t="inlineStr">
+        <is>
+          <t>综合电子设备</t>
+        </is>
+      </c>
+      <c r="AT88" s="3" t="inlineStr">
+        <is>
+          <t>计算机设备</t>
+        </is>
+      </c>
+      <c r="AU88" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV88" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW88" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX88" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY88" s="3" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="AO88" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP88" s="3" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="AQ88" s="3" t="inlineStr">
-        <is>
-          <t>建筑施工</t>
-        </is>
-      </c>
-      <c r="AR88" s="3" t="inlineStr">
-        <is>
-          <t>专业工程</t>
-        </is>
-      </c>
-      <c r="AS88" s="3" t="inlineStr">
-        <is>
-          <t>其他专业工程</t>
-        </is>
-      </c>
-      <c r="AT88" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU88" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AV88" s="3" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AW88" s="3" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AX88" s="3" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AY88" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="AZ88" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ88" s="3"/>
     </row>
     <row r="89" customHeight="true" ht="18.0">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>26华为MTN004</t>
+          <t>26信阳建投MTN003</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -20798,49 +20796,49 @@
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>102683368.IB</t>
+          <t>102683365.IB</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E89" s="4" t="n">
-        <v>40.0</v>
+        <v>6.0</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>40.0</v>
+        <v>6.0</v>
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>1.35 ~ 1.95</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H89" s="4" t="n">
-        <v>1.5</v>
+        <v>1.79</v>
       </c>
       <c r="I89" s="4" t="n">
-        <v>23.61</v>
+        <v>53.95</v>
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>26华为MTN003</t>
+          <t>24信阳建投MTN002</t>
         </is>
       </c>
       <c r="L89" s="3" t="inlineStr">
         <is>
-          <t>2.98Y</t>
+          <t>2.66Y</t>
         </is>
       </c>
       <c r="M89" s="3" t="inlineStr">
         <is>
-          <t>1.6621</t>
+          <t>1.9127</t>
         </is>
       </c>
       <c r="N89" s="3" t="inlineStr">
@@ -20850,12 +20848,12 @@
       </c>
       <c r="O89" s="3" t="inlineStr">
         <is>
-          <t>华为投资控股有限公司</t>
+          <t>信阳建投投资集团有限责任公司</t>
         </is>
       </c>
       <c r="P89" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.52</t>
+          <t>B- 45.09</t>
         </is>
       </c>
       <c r="Q89" s="3" t="inlineStr">
@@ -20879,40 +20877,40 @@
         </is>
       </c>
       <c r="U89" s="4" t="n">
-        <v>2.6675</v>
+        <v>4.375</v>
       </c>
       <c r="V89" s="4" t="n">
-        <v>1.52</v>
+        <v>1.538</v>
       </c>
       <c r="W89" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X89" s="3" t="inlineStr">
         <is>
-          <t>1.60%~1.70%</t>
+          <t>1.84%~1.94%</t>
         </is>
       </c>
       <c r="Y89" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z89" s="3"/>
       <c r="AA89" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>河南省-信阳市</t>
         </is>
       </c>
       <c r="AB89" s="3" t="inlineStr">
         <is>
-          <t>公司本次拟发行40亿元中期票据,将用于补充公司本部及下属子公司营运资金</t>
+          <t>本期中期票据发行金额上限6.00亿元,基础发行规模0.00亿元,拟全部用于偿还债务融资工具。[23信阳建投MTN007]</t>
         </is>
       </c>
       <c r="AC89" s="3" t="inlineStr">
         <is>
-          <t>中国银行股份有限公司,中国工商银行股份有限公司,中国建设银行股份有限公司</t>
+          <t>中信银行股份有限公司,中信建投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD89" s="3"/>
@@ -20923,7 +20921,7 @@
       </c>
       <c r="AF89" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG89" s="3" t="inlineStr">
@@ -20933,7 +20931,7 @@
       </c>
       <c r="AH89" s="3" t="inlineStr">
         <is>
-          <t>华为投资控股有限公司2026年度第四期中期票据</t>
+          <t>信阳建投投资集团有限责任公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI89" s="3" t="inlineStr">
@@ -20943,10 +20941,14 @@
       </c>
       <c r="AJ89" s="3" t="inlineStr">
         <is>
-          <t>2029-08-27</t>
-        </is>
-      </c>
-      <c r="AK89" s="3"/>
+          <t>2028-08-27</t>
+        </is>
+      </c>
+      <c r="AK89" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL89" s="3" t="inlineStr">
         <is>
           <t>2026-08-28</t>
@@ -20964,32 +20966,32 @@
       </c>
       <c r="AO89" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP89" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ89" s="3" t="inlineStr">
         <is>
-          <t>电子设备制造</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR89" s="3" t="inlineStr">
         <is>
-          <t>综合电子设备</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS89" s="3" t="inlineStr">
         <is>
-          <t>综合电子设备</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT89" s="3" t="inlineStr">
         <is>
-          <t>计算机设备</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU89" s="3" t="inlineStr">
@@ -21022,59 +21024,59 @@
     <row r="90" customHeight="true" ht="18.0">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>26信阳建投MTN003</t>
+          <t>青铁KY03</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>08-26 18:00</t>
+          <t>08-25 19:00</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>102683365.IB</t>
+          <t>245920.SH</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E90" s="4" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="F90" s="4" t="n">
         <v>6.0</v>
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H90" s="4" t="n">
         <v>1.79</v>
       </c>
       <c r="I90" s="4" t="n">
-        <v>53.95</v>
+        <v>53.67</v>
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="K90" s="3" t="inlineStr">
         <is>
-          <t>24信阳建投MTN002</t>
+          <t>青铁KY01</t>
         </is>
       </c>
       <c r="L90" s="3" t="inlineStr">
         <is>
-          <t>2.66Y</t>
+          <t>2.54Y+N</t>
         </is>
       </c>
       <c r="M90" s="3" t="inlineStr">
         <is>
-          <t>1.9127</t>
+          <t>1.8085</t>
         </is>
       </c>
       <c r="N90" s="3" t="inlineStr">
@@ -21084,12 +21086,12 @@
       </c>
       <c r="O90" s="3" t="inlineStr">
         <is>
-          <t>信阳建投投资集团有限责任公司</t>
+          <t>青岛地铁集团有限公司</t>
         </is>
       </c>
       <c r="P90" s="3" t="inlineStr">
         <is>
-          <t>B- 45.09</t>
+          <t>B- 37.78</t>
         </is>
       </c>
       <c r="Q90" s="3" t="inlineStr">
@@ -21099,7 +21101,7 @@
       </c>
       <c r="R90" s="3" t="inlineStr">
         <is>
-          <t>08-25 09:00</t>
+          <t>08-25 15:00</t>
         </is>
       </c>
       <c r="S90" s="3" t="inlineStr">
@@ -21113,46 +21115,44 @@
         </is>
       </c>
       <c r="U90" s="4" t="n">
-        <v>4.375</v>
-      </c>
-      <c r="V90" s="4" t="n">
-        <v>1.538</v>
-      </c>
+        <v>4.77</v>
+      </c>
+      <c r="V90" s="3"/>
       <c r="W90" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X90" s="3" t="inlineStr">
         <is>
-          <t>1.84%~1.94%</t>
+          <t>1.77%~1.87%</t>
         </is>
       </c>
       <c r="Y90" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3" t="inlineStr">
         <is>
-          <t>河南省-信阳市</t>
+          <t>山东省-青岛市</t>
         </is>
       </c>
       <c r="AB90" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额上限6.00亿元,基础发行规模0.00亿元,拟全部用于偿还债务融资工具。[23信阳建投MTN007]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟用于偿还有息债务。[25青铁Y2]</t>
         </is>
       </c>
       <c r="AC90" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,中信建投证券股份有限公司</t>
+          <t>中国国际金融股份有限公司,中信证券股份有限公司,华泰联合证券有限责任公司,广发证券股份有限公司,国投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF90" s="3" t="inlineStr">
@@ -21162,12 +21162,12 @@
       </c>
       <c r="AG90" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH90" s="3" t="inlineStr">
         <is>
-          <t>信阳建投投资集团有限责任公司2026年度第三期中期票据</t>
+          <t>青岛地铁集团有限公司2026年面向专业投资者公开发行科技创新可续期公司债券(第二期)(品种一)</t>
         </is>
       </c>
       <c r="AI90" s="3" t="inlineStr">
@@ -21177,22 +21177,18 @@
       </c>
       <c r="AJ90" s="3" t="inlineStr">
         <is>
-          <t>2028-08-27</t>
-        </is>
-      </c>
-      <c r="AK90" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-08-27</t>
+        </is>
+      </c>
+      <c r="AK90" s="3"/>
       <c r="AL90" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t/>
         </is>
       </c>
       <c r="AM90" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AN90" s="3" t="inlineStr">
@@ -21207,7 +21203,7 @@
       </c>
       <c r="AP90" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ90" s="3" t="inlineStr">
@@ -21217,12 +21213,12 @@
       </c>
       <c r="AR90" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AS90" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AT90" s="3" t="inlineStr">
@@ -21242,7 +21238,7 @@
       </c>
       <c r="AW90" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX90" s="3" t="inlineStr">
@@ -21252,7 +21248,7 @@
       </c>
       <c r="AY90" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AZ90" s="3"/>
@@ -21260,7 +21256,7 @@
     <row r="91" customHeight="true" ht="18.0">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>青铁KY03</t>
+          <t>青铁KY04</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -21270,49 +21266,49 @@
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>245920.SH</t>
+          <t>245921.SH</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E91" s="4" t="n">
         <v>5.0</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H91" s="4" t="n">
-        <v>1.79</v>
+        <v>1.93</v>
       </c>
       <c r="I91" s="4" t="n">
-        <v>53.67</v>
+        <v>54.28</v>
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="K91" s="3" t="inlineStr">
         <is>
-          <t>青铁KY01</t>
+          <t>青铁KY02</t>
         </is>
       </c>
       <c r="L91" s="3" t="inlineStr">
         <is>
-          <t>2.54Y+N</t>
+          <t>4.54Y+N</t>
         </is>
       </c>
       <c r="M91" s="3" t="inlineStr">
         <is>
-          <t>1.8085</t>
+          <t>1.9129</t>
         </is>
       </c>
       <c r="N91" s="3" t="inlineStr">
@@ -21351,7 +21347,7 @@
         </is>
       </c>
       <c r="U91" s="4" t="n">
-        <v>4.77</v>
+        <v>5.68</v>
       </c>
       <c r="V91" s="3"/>
       <c r="W91" s="3" t="inlineStr">
@@ -21361,7 +21357,7 @@
       </c>
       <c r="X91" s="3" t="inlineStr">
         <is>
-          <t>1.77%~1.87%</t>
+          <t>1.88%~1.98%</t>
         </is>
       </c>
       <c r="Y91" s="3" t="inlineStr">
@@ -21403,7 +21399,7 @@
       </c>
       <c r="AH91" s="3" t="inlineStr">
         <is>
-          <t>青岛地铁集团有限公司2026年面向专业投资者公开发行科技创新可续期公司债券(第二期)(品种一)</t>
+          <t>青岛地铁集团有限公司2026年面向专业投资者公开发行科技创新可续期公司债券(第二期)(品种二)</t>
         </is>
       </c>
       <c r="AI91" s="3" t="inlineStr">
@@ -21413,7 +21409,7 @@
       </c>
       <c r="AJ91" s="3" t="inlineStr">
         <is>
-          <t>2029-08-27</t>
+          <t>2031-08-27</t>
         </is>
       </c>
       <c r="AK91" s="3"/>
@@ -21492,7 +21488,7 @@
     <row r="92" customHeight="true" ht="18.0">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>青铁KY04</t>
+          <t>26化学K3</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -21502,64 +21498,64 @@
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>245921.SH</t>
+          <t>245897.SH</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E92" s="4" t="n">
-        <v>5.0</v>
+        <v>7.5</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.10 ~ 2.10</t>
         </is>
       </c>
       <c r="H92" s="4" t="n">
-        <v>1.93</v>
+        <v>1.58</v>
       </c>
       <c r="I92" s="4" t="n">
-        <v>54.28</v>
+        <v>32.67</v>
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="K92" s="3" t="inlineStr">
         <is>
-          <t>青铁KY02</t>
+          <t>26化学K1</t>
         </is>
       </c>
       <c r="L92" s="3" t="inlineStr">
         <is>
-          <t>4.54Y+N</t>
+          <t>2.81Y</t>
         </is>
       </c>
       <c r="M92" s="3" t="inlineStr">
         <is>
-          <t>1.9129</t>
+          <t>1.6442</t>
         </is>
       </c>
       <c r="N92" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6900/--</t>
         </is>
       </c>
       <c r="O92" s="3" t="inlineStr">
         <is>
-          <t>青岛地铁集团有限公司</t>
+          <t>中国化学工程集团有限公司</t>
         </is>
       </c>
       <c r="P92" s="3" t="inlineStr">
         <is>
-          <t>B- 37.78</t>
+          <t>C- 24.39</t>
         </is>
       </c>
       <c r="Q92" s="3" t="inlineStr">
@@ -21569,7 +21565,7 @@
       </c>
       <c r="R92" s="3" t="inlineStr">
         <is>
-          <t>08-25 15:00</t>
+          <t>08-25 16:00</t>
         </is>
       </c>
       <c r="S92" s="3" t="inlineStr">
@@ -21583,17 +21579,17 @@
         </is>
       </c>
       <c r="U92" s="4" t="n">
-        <v>5.68</v>
+        <v>4.37</v>
       </c>
       <c r="V92" s="3"/>
       <c r="W92" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X92" s="3" t="inlineStr">
         <is>
-          <t>1.88%~1.98%</t>
+          <t>1.60%~1.70%</t>
         </is>
       </c>
       <c r="Y92" s="3" t="inlineStr">
@@ -21601,20 +21597,24 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z92" s="3"/>
+      <c r="Z92" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA92" s="3" t="inlineStr">
         <is>
-          <t>山东省-青岛市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB92" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟用于偿还有息债务。[25青铁Y2]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟将用于生产性支出,包括项目建设、偿还有息债务、补充流动资金或其他符合法律法规的用途。</t>
         </is>
       </c>
       <c r="AC92" s="3" t="inlineStr">
         <is>
-          <t>中国国际金融股份有限公司,中信证券股份有限公司,华泰联合证券有限责任公司,广发证券股份有限公司,国投证券股份有限公司</t>
+          <t>中信证券股份有限公司,中信建投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD92" s="3"/>
@@ -21625,7 +21625,7 @@
       </c>
       <c r="AF92" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>中央国有企业</t>
         </is>
       </c>
       <c r="AG92" s="3" t="inlineStr">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="AH92" s="3" t="inlineStr">
         <is>
-          <t>青岛地铁集团有限公司2026年面向专业投资者公开发行科技创新可续期公司债券(第二期)(品种二)</t>
+          <t>中国化学工程集团有限公司2026年面向专业投资者公开发行科技创新公司债券(第二期)(品种一)</t>
         </is>
       </c>
       <c r="AI92" s="3" t="inlineStr">
@@ -21645,60 +21645,60 @@
       </c>
       <c r="AJ92" s="3" t="inlineStr">
         <is>
-          <t>2031-08-27</t>
+          <t>2029-08-27</t>
         </is>
       </c>
       <c r="AK92" s="3"/>
       <c r="AL92" s="3" t="inlineStr">
         <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="AM92" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AN92" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AO92" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP92" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AQ92" s="3" t="inlineStr">
+        <is>
+          <t>建筑施工</t>
+        </is>
+      </c>
+      <c r="AR92" s="3" t="inlineStr">
+        <is>
+          <t>专业工程</t>
+        </is>
+      </c>
+      <c r="AS92" s="3" t="inlineStr">
+        <is>
+          <t>其他专业工程</t>
+        </is>
+      </c>
+      <c r="AT92" s="3" t="inlineStr">
+        <is>
+          <t>石油化工</t>
+        </is>
+      </c>
+      <c r="AU92" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM92" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="AN92" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AO92" s="3" t="inlineStr">
-        <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP92" s="3" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="AQ92" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR92" s="3" t="inlineStr">
-        <is>
-          <t>轨道交通</t>
-        </is>
-      </c>
-      <c r="AS92" s="3" t="inlineStr">
-        <is>
-          <t>轨道交通</t>
-        </is>
-      </c>
-      <c r="AT92" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AU92" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV92" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -21706,7 +21706,7 @@
       </c>
       <c r="AW92" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX92" s="3" t="inlineStr">
@@ -21724,74 +21724,74 @@
     <row r="93" customHeight="true" ht="18.0">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>26化学K3</t>
+          <t>26华阳新材MTN009</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>08-25 19:00</t>
+          <t>08-26 18:00</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>245897.SH</t>
+          <t>102690006.IB</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E93" s="4" t="n">
-        <v>7.5</v>
+        <v>10.0</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>7.0</v>
+        <v>10.0</v>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>1.10 ~ 2.10</t>
+          <t>1.48 ~ 1.98</t>
         </is>
       </c>
       <c r="H93" s="4" t="n">
-        <v>1.58</v>
+        <v>1.93</v>
       </c>
       <c r="I93" s="4" t="n">
-        <v>32.67</v>
+        <v>66.61</v>
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="K93" s="3" t="inlineStr">
         <is>
-          <t>26化学K1</t>
+          <t>26华阳新材MTN007</t>
         </is>
       </c>
       <c r="L93" s="3" t="inlineStr">
         <is>
-          <t>2.81Y</t>
+          <t>2.82Y+N</t>
         </is>
       </c>
       <c r="M93" s="3" t="inlineStr">
         <is>
-          <t>1.6442</t>
+          <t>1.9637</t>
         </is>
       </c>
       <c r="N93" s="3" t="inlineStr">
         <is>
-          <t>1.6900/--</t>
+          <t>1.9600/--</t>
         </is>
       </c>
       <c r="O93" s="3" t="inlineStr">
         <is>
-          <t>中国化学工程集团有限公司</t>
+          <t>华阳新材料科技集团有限公司</t>
         </is>
       </c>
       <c r="P93" s="3" t="inlineStr">
         <is>
-          <t>C- 24.39</t>
+          <t>C- 24.26</t>
         </is>
       </c>
       <c r="Q93" s="3" t="inlineStr">
@@ -21801,7 +21801,7 @@
       </c>
       <c r="R93" s="3" t="inlineStr">
         <is>
-          <t>08-25 16:00</t>
+          <t>08-25 09:00</t>
         </is>
       </c>
       <c r="S93" s="3" t="inlineStr">
@@ -21815,17 +21815,17 @@
         </is>
       </c>
       <c r="U93" s="4" t="n">
-        <v>4.37</v>
+        <v>2.07</v>
       </c>
       <c r="V93" s="3"/>
       <c r="W93" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X93" s="3" t="inlineStr">
         <is>
-          <t>1.60%~1.70%</t>
+          <t>1.94%~2.04%</t>
         </is>
       </c>
       <c r="Y93" s="3" t="inlineStr">
@@ -21833,45 +21833,41 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z93" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z93" s="3"/>
       <c r="AA93" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>山西省-阳泉市</t>
         </is>
       </c>
       <c r="AB93" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟将用于生产性支出,包括项目建设、偿还有息债务、补充流动资金或其他符合法律法规的用途。</t>
+          <t>发行人本期中期票据基础发行规模0亿元,发行金额上限10亿元,用于偿还发行人有息债务。</t>
         </is>
       </c>
       <c r="AC93" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,中信建投证券股份有限公司</t>
+          <t>中信证券股份有限公司,国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD93" s="3"/>
       <c r="AE93" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF93" s="3" t="inlineStr">
         <is>
-          <t>中央国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG93" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH93" s="3" t="inlineStr">
         <is>
-          <t>中国化学工程集团有限公司2026年面向专业投资者公开发行科技创新公司债券(第二期)(品种一)</t>
+          <t>华阳新材料科技集团有限公司2026年度第九期中期票据</t>
         </is>
       </c>
       <c r="AI93" s="3" t="inlineStr">
@@ -21887,12 +21883,12 @@
       <c r="AK93" s="3"/>
       <c r="AL93" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AM93" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AN93" s="3" t="inlineStr">
@@ -21907,27 +21903,27 @@
       </c>
       <c r="AP93" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ93" s="3" t="inlineStr">
         <is>
-          <t>建筑施工</t>
+          <t>化石能源</t>
         </is>
       </c>
       <c r="AR93" s="3" t="inlineStr">
         <is>
-          <t>专业工程</t>
+          <t>煤炭</t>
         </is>
       </c>
       <c r="AS93" s="3" t="inlineStr">
         <is>
-          <t>其他专业工程</t>
+          <t>其他煤炭</t>
         </is>
       </c>
       <c r="AT93" s="3" t="inlineStr">
         <is>
-          <t>石油化工</t>
+          <t>煤炭开采</t>
         </is>
       </c>
       <c r="AU93" s="3" t="inlineStr">
@@ -21942,7 +21938,7 @@
       </c>
       <c r="AW93" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX93" s="3" t="inlineStr">
@@ -21952,82 +21948,84 @@
       </c>
       <c r="AY93" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="AZ93" s="3"/>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AZ93" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="94" customHeight="true" ht="18.0">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>26华阳新材MTN009</t>
+          <t>26虞交03</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>08-26 18:00</t>
+          <t>08-25 19:00</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>102690006.IB</t>
+          <t>283772.SH</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E94" s="4" t="n">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>1.48 ~ 1.98</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="H94" s="4" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="I94" s="4" t="n">
-        <v>66.61</v>
+        <v>57.28</v>
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="K94" s="3" t="inlineStr">
         <is>
-          <t>26华阳新材MTN007</t>
+          <t>26虞交01</t>
         </is>
       </c>
       <c r="L94" s="3" t="inlineStr">
         <is>
-          <t>2.82Y+N</t>
+          <t>2.66Y+2.00Y</t>
         </is>
       </c>
       <c r="M94" s="3" t="inlineStr">
         <is>
-          <t>1.9637</t>
+          <t>1.7488</t>
         </is>
       </c>
       <c r="N94" s="3" t="inlineStr">
         <is>
-          <t>1.9600/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O94" s="3" t="inlineStr">
         <is>
-          <t>华阳新材料科技集团有限公司</t>
+          <t>绍兴上虞交通集团有限公司</t>
         </is>
       </c>
       <c r="P94" s="3" t="inlineStr">
         <is>
-          <t>C- 24.26</t>
+          <t>C+ 31.25</t>
         </is>
       </c>
       <c r="Q94" s="3" t="inlineStr">
@@ -22037,7 +22035,7 @@
       </c>
       <c r="R94" s="3" t="inlineStr">
         <is>
-          <t>08-25 09:00</t>
+          <t>08-25 16:00</t>
         </is>
       </c>
       <c r="S94" s="3" t="inlineStr">
@@ -22047,48 +22045,48 @@
       </c>
       <c r="T94" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="U94" s="4" t="n">
-        <v>2.07</v>
+        <v>2.77</v>
       </c>
       <c r="V94" s="3"/>
       <c r="W94" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X94" s="3" t="inlineStr">
         <is>
-          <t>1.94%~2.04%</t>
+          <t>1.82%~1.92%</t>
         </is>
       </c>
       <c r="Y94" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z94" s="3"/>
       <c r="AA94" s="3" t="inlineStr">
         <is>
-          <t>山西省-阳泉市</t>
+          <t>浙江省-绍兴市</t>
         </is>
       </c>
       <c r="AB94" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据基础发行规模0亿元,发行金额上限10亿元,用于偿还发行人有息债务。</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟将3亿元用于偿还到期公司债券本金[23虞交02]</t>
         </is>
       </c>
       <c r="AC94" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,国泰海通证券股份有限公司</t>
+          <t>中信证券股份有限公司,天风证券股份有限公司</t>
         </is>
       </c>
       <c r="AD94" s="3"/>
       <c r="AE94" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF94" s="3" t="inlineStr">
@@ -22098,28 +22096,28 @@
       </c>
       <c r="AG94" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH94" s="3" t="inlineStr">
         <is>
-          <t>华阳新材料科技集团有限公司2026年度第九期中期票据</t>
+          <t>绍兴上虞交通集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI94" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ94" s="3" t="inlineStr">
         <is>
-          <t>2029-08-27</t>
+          <t>2031-08-26</t>
         </is>
       </c>
       <c r="AK94" s="3"/>
       <c r="AL94" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AM94" s="3" t="inlineStr">
@@ -22129,37 +22127,37 @@
       </c>
       <c r="AN94" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="AO94" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP94" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ94" s="3" t="inlineStr">
         <is>
-          <t>化石能源</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR94" s="3" t="inlineStr">
         <is>
-          <t>煤炭</t>
+          <t>其他交运基础设施</t>
         </is>
       </c>
       <c r="AS94" s="3" t="inlineStr">
         <is>
-          <t>其他煤炭</t>
+          <t>其他交运基础设施</t>
         </is>
       </c>
       <c r="AT94" s="3" t="inlineStr">
         <is>
-          <t>煤炭开采</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU94" s="3" t="inlineStr">
@@ -22174,7 +22172,7 @@
       </c>
       <c r="AW94" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX94" s="3" t="inlineStr">
@@ -22184,84 +22182,82 @@
       </c>
       <c r="AY94" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="AZ94" s="4" t="n">
-        <v>0.01</v>
-      </c>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AZ94" s="3"/>
     </row>
     <row r="95" customHeight="true" ht="18.0">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>26虞交03</t>
+          <t>26重庆三峡银行三农债01</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>08-25 19:00</t>
+          <t>08-25 18:00</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>283772.SH</t>
+          <t>212680023.IB</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E95" s="4" t="n">
-        <v>3.0</v>
+        <v>20.0</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>3.0</v>
+        <v>20.0</v>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H95" s="4" t="n">
-        <v>1.96</v>
+        <v>1.65</v>
       </c>
       <c r="I95" s="4" t="n">
-        <v>57.28</v>
+        <v>39.67</v>
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="K95" s="3" t="inlineStr">
         <is>
-          <t>26虞交01</t>
+          <t>25三峡银行绿色债01</t>
         </is>
       </c>
       <c r="L95" s="3" t="inlineStr">
         <is>
-          <t>2.66Y+2.00Y</t>
+          <t>2.24Y</t>
         </is>
       </c>
       <c r="M95" s="3" t="inlineStr">
         <is>
-          <t>1.7488</t>
+          <t>1.6147</t>
         </is>
       </c>
       <c r="N95" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.6000</t>
         </is>
       </c>
       <c r="O95" s="3" t="inlineStr">
         <is>
-          <t>绍兴上虞交通集团有限公司</t>
+          <t>重庆三峡银行股份有限公司</t>
         </is>
       </c>
       <c r="P95" s="3" t="inlineStr">
         <is>
-          <t>C+ 31.25</t>
+          <t>B- 44.61</t>
         </is>
       </c>
       <c r="Q95" s="3" t="inlineStr">
@@ -22271,7 +22267,7 @@
       </c>
       <c r="R95" s="3" t="inlineStr">
         <is>
-          <t>08-25 16:00</t>
+          <t>08-25 09:00</t>
         </is>
       </c>
       <c r="S95" s="3" t="inlineStr">
@@ -22281,48 +22277,48 @@
       </c>
       <c r="T95" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="U95" s="4" t="n">
-        <v>2.77</v>
+        <v>3.18</v>
       </c>
       <c r="V95" s="3"/>
       <c r="W95" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X95" s="3" t="inlineStr">
         <is>
-          <t>1.82%~1.92%</t>
+          <t>1.61%~1.71%</t>
         </is>
       </c>
       <c r="Y95" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z95" s="3"/>
-      <c r="AA95" s="3" t="inlineStr">
-        <is>
-          <t>浙江省-绍兴市</t>
-        </is>
-      </c>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z95" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="AA95" s="3"/>
       <c r="AB95" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟将3亿元用于偿还到期公司债券本金[23虞交02]</t>
+          <t>本期债券募集资金将全部专项用于发放涉农贷款,支持乡村振兴业务发展</t>
         </is>
       </c>
       <c r="AC95" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,天风证券股份有限公司</t>
+          <t>中信证券股份有限公司,国泰海通证券股份有限公司,中信建投证券股份有限公司,中国国际金融股份有限公司,申万宏源证券有限公司,国开证券股份有限公司,西南证券股份有限公司,重庆银行股份有限公司,恒丰银行股份有限公司,兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>商业银行普通债券</t>
         </is>
       </c>
       <c r="AF95" s="3" t="inlineStr">
@@ -22332,68 +22328,68 @@
       </c>
       <c r="AG95" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH95" s="3" t="inlineStr">
         <is>
-          <t>绍兴上虞交通集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>重庆三峡银行股份有限公司2026年"三农"专项金融债券</t>
         </is>
       </c>
       <c r="AI95" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ95" s="3" t="inlineStr">
         <is>
-          <t>2031-08-26</t>
+          <t>2029-08-27</t>
         </is>
       </c>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AM95" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="AN95" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AO95" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP95" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ95" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AR95" s="3" t="inlineStr">
         <is>
-          <t>其他交运基础设施</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AS95" s="3" t="inlineStr">
         <is>
-          <t>其他交运基础设施</t>
+          <t>城商行</t>
         </is>
       </c>
       <c r="AT95" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AU95" s="3" t="inlineStr">
@@ -22426,17 +22422,17 @@
     <row r="96" customHeight="true" ht="18.0">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>26重庆三峡银行三农债01</t>
+          <t>26北部湾银行02</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>08-25 18:00</t>
+          <t>08-25 16:00</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>212680023.IB</t>
+          <t>2620006.IB</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
@@ -22445,14 +22441,14 @@
         </is>
       </c>
       <c r="E96" s="4" t="n">
-        <v>20.0</v>
+        <v>30.0</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>20.0</v>
+        <v>30.0</v>
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>1.40 ~ 1.80</t>
         </is>
       </c>
       <c r="H96" s="4" t="n">
@@ -22463,37 +22459,37 @@
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="K96" s="3" t="inlineStr">
         <is>
-          <t>25三峡银行绿色债01</t>
+          <t>26北部湾银行01</t>
         </is>
       </c>
       <c r="L96" s="3" t="inlineStr">
         <is>
-          <t>2.24Y</t>
+          <t>2.98Y</t>
         </is>
       </c>
       <c r="M96" s="3" t="inlineStr">
         <is>
-          <t>1.6147</t>
+          <t>1.6468</t>
         </is>
       </c>
       <c r="N96" s="3" t="inlineStr">
         <is>
-          <t>--/1.6000</t>
+          <t>--/1.6400</t>
         </is>
       </c>
       <c r="O96" s="3" t="inlineStr">
         <is>
-          <t>重庆三峡银行股份有限公司</t>
+          <t>广西北部湾银行股份有限公司</t>
         </is>
       </c>
       <c r="P96" s="3" t="inlineStr">
         <is>
-          <t>B- 44.61</t>
+          <t>B 54.01</t>
         </is>
       </c>
       <c r="Q96" s="3" t="inlineStr">
@@ -22516,18 +22512,16 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="U96" s="4" t="n">
-        <v>3.18</v>
-      </c>
+      <c r="U96" s="3"/>
       <c r="V96" s="3"/>
       <c r="W96" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X96" s="3" t="inlineStr">
         <is>
-          <t>1.61%~1.71%</t>
+          <t>1.64%~1.74%</t>
         </is>
       </c>
       <c r="Y96" s="3" t="inlineStr">
@@ -22540,15 +22534,19 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="AA96" s="3"/>
+      <c r="AA96" s="3" t="inlineStr">
+        <is>
+          <t>广西壮族自治区-南宁市</t>
+        </is>
+      </c>
       <c r="AB96" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金将全部专项用于发放涉农贷款,支持乡村振兴业务发展</t>
+          <t>本期债券募集资金将严格遵循法律法规及监管批复要求，专项用于补充本行投放向海经济领域信贷业务所需的资金，优化负债期限结构，促进业务的稳健发展。</t>
         </is>
       </c>
       <c r="AC96" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,国泰海通证券股份有限公司,中信建投证券股份有限公司,中国国际金融股份有限公司,申万宏源证券有限公司,国开证券股份有限公司,西南证券股份有限公司,重庆银行股份有限公司,恒丰银行股份有限公司,兴业银行股份有限公司</t>
+          <t>国泰海通证券股份有限公司,中信建投证券股份有限公司,中信证券股份有限公司,光大证券股份有限公司,国海证券股份有限公司,中国银河证券股份有限公司</t>
         </is>
       </c>
       <c r="AD96" s="3"/>
@@ -22569,7 +22567,7 @@
       </c>
       <c r="AH96" s="3" t="inlineStr">
         <is>
-          <t>重庆三峡银行股份有限公司2026年"三农"专项金融债券</t>
+          <t>广西北部湾银行股份有限公司2026年金融债券(第二期)</t>
         </is>
       </c>
       <c r="AI96" s="3" t="inlineStr">
@@ -22590,7 +22588,7 @@
       </c>
       <c r="AM96" s="3" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AN96" s="3" t="inlineStr">
@@ -22605,7 +22603,7 @@
       </c>
       <c r="AP96" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ96" s="3" t="inlineStr">
@@ -22658,74 +22656,74 @@
     <row r="97" customHeight="true" ht="18.0">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>26北部湾银行02</t>
+          <t>26威高MTN003(科创债)</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>08-25 16:00</t>
+          <t>08-26 18:00</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>2620006.IB</t>
+          <t>102683369.IB</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E97" s="4" t="n">
-        <v>30.0</v>
+        <v>5.0</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>30.0</v>
+        <v>5.0</v>
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.80</t>
+          <t>2.40 ~ 3.00</t>
         </is>
       </c>
       <c r="H97" s="4" t="n">
-        <v>1.65</v>
+        <v>2.9</v>
       </c>
       <c r="I97" s="4" t="n">
-        <v>39.67</v>
+        <v>150.16</v>
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="K97" s="3" t="inlineStr">
         <is>
-          <t>26北部湾银行01</t>
+          <t>26威高MTN002(科创债)</t>
         </is>
       </c>
       <c r="L97" s="3" t="inlineStr">
         <is>
-          <t>2.98Y</t>
+          <t>2.66Y</t>
         </is>
       </c>
       <c r="M97" s="3" t="inlineStr">
         <is>
-          <t>1.6468</t>
+          <t>2.7328</t>
         </is>
       </c>
       <c r="N97" s="3" t="inlineStr">
         <is>
-          <t>--/1.6400</t>
+          <t>--/2.7000</t>
         </is>
       </c>
       <c r="O97" s="3" t="inlineStr">
         <is>
-          <t>广西北部湾银行股份有限公司</t>
+          <t>威高集团有限公司</t>
         </is>
       </c>
       <c r="P97" s="3" t="inlineStr">
         <is>
-          <t>B 54.01</t>
+          <t>C- 17.60</t>
         </is>
       </c>
       <c r="Q97" s="3" t="inlineStr">
@@ -22748,52 +22746,50 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="U97" s="3"/>
+      <c r="U97" s="4" t="n">
+        <v>1.44</v>
+      </c>
       <c r="V97" s="3"/>
       <c r="W97" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X97" s="3" t="inlineStr">
         <is>
-          <t>1.64%~1.74%</t>
+          <t>3.10%~3.20%</t>
         </is>
       </c>
       <c r="Y97" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z97" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z97" s="3"/>
       <c r="AA97" s="3" t="inlineStr">
         <is>
-          <t>广西壮族自治区-南宁市</t>
+          <t>山东省-威海市</t>
         </is>
       </c>
       <c r="AB97" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金将严格遵循法律法规及监管批复要求，专项用于补充本行投放向海经济领域信贷业务所需的资金，优化负债期限结构，促进业务的稳健发展。</t>
+          <t>本次中期票据发行规模不超过人民币5亿元,用途为偿还有息债务</t>
         </is>
       </c>
       <c r="AC97" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,中信建投证券股份有限公司,中信证券股份有限公司,光大证券股份有限公司,国海证券股份有限公司,中国银河证券股份有限公司</t>
+          <t>招商银行股份有限公司,青岛银行股份有限公司,中信银行股份有限公司,华夏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD97" s="3"/>
       <c r="AE97" s="3" t="inlineStr">
         <is>
-          <t>商业银行普通债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF97" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG97" s="3" t="inlineStr">
@@ -22803,7 +22799,7 @@
       </c>
       <c r="AH97" s="3" t="inlineStr">
         <is>
-          <t>广西北部湾银行股份有限公司2026年金融债券(第二期)</t>
+          <t>威高集团有限公司2026年度第三期科技创新债券</t>
         </is>
       </c>
       <c r="AI97" s="3" t="inlineStr">
@@ -22813,7 +22809,7 @@
       </c>
       <c r="AJ97" s="3" t="inlineStr">
         <is>
-          <t>2029-08-27</t>
+          <t>2031-08-27</t>
         </is>
       </c>
       <c r="AK97" s="3"/>
@@ -22834,32 +22830,32 @@
       </c>
       <c r="AO97" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP97" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AQ97" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>医药制造</t>
         </is>
       </c>
       <c r="AR97" s="3" t="inlineStr">
         <is>
-          <t>商业银行</t>
+          <t>医疗器械制造</t>
         </is>
       </c>
       <c r="AS97" s="3" t="inlineStr">
         <is>
-          <t>城商行</t>
+          <t>医疗器械制造</t>
         </is>
       </c>
       <c r="AT97" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>医疗器械</t>
         </is>
       </c>
       <c r="AU97" s="3" t="inlineStr">
@@ -22884,7 +22880,7 @@
       </c>
       <c r="AY97" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="AZ97" s="3"/>
@@ -22892,7 +22888,7 @@
     <row r="98" customHeight="true" ht="18.0">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>26威高MTN003(科创债)</t>
+          <t>26皖投集MTN004</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -22902,12 +22898,12 @@
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>102683369.IB</t>
+          <t>102683367.IB</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>30Y</t>
         </is>
       </c>
       <c r="E98" s="4" t="n">
@@ -22918,103 +22914,103 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2.40 ~ 3.00</t>
+          <t>2.30 ~ 2.70</t>
         </is>
       </c>
       <c r="H98" s="4" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="I98" s="4" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>2.36</t>
+        </is>
+      </c>
+      <c r="K98" s="3" t="inlineStr">
+        <is>
+          <t>25皖投集MTN004(科创债)</t>
+        </is>
+      </c>
+      <c r="L98" s="3" t="inlineStr">
+        <is>
+          <t>19.23Y</t>
+        </is>
+      </c>
+      <c r="M98" s="3" t="inlineStr">
+        <is>
+          <t>2.3597</t>
+        </is>
+      </c>
+      <c r="N98" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O98" s="3" t="inlineStr">
+        <is>
+          <t>安徽省投资集团控股有限公司</t>
+        </is>
+      </c>
+      <c r="P98" s="3" t="inlineStr">
+        <is>
+          <t>C 25.13</t>
+        </is>
+      </c>
+      <c r="Q98" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="R98" s="3" t="inlineStr">
+        <is>
+          <t>08-25 09:00</t>
+        </is>
+      </c>
+      <c r="S98" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="T98" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="U98" s="4" t="n">
         <v>2.9</v>
-      </c>
-      <c r="I98" s="4" t="n">
-        <v>150.16</v>
-      </c>
-      <c r="J98" s="3" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="K98" s="3" t="inlineStr">
-        <is>
-          <t>26威高MTN002(科创债)</t>
-        </is>
-      </c>
-      <c r="L98" s="3" t="inlineStr">
-        <is>
-          <t>2.66Y</t>
-        </is>
-      </c>
-      <c r="M98" s="3" t="inlineStr">
-        <is>
-          <t>2.7328</t>
-        </is>
-      </c>
-      <c r="N98" s="3" t="inlineStr">
-        <is>
-          <t>--/2.7000</t>
-        </is>
-      </c>
-      <c r="O98" s="3" t="inlineStr">
-        <is>
-          <t>威高集团有限公司</t>
-        </is>
-      </c>
-      <c r="P98" s="3" t="inlineStr">
-        <is>
-          <t>C- 17.60</t>
-        </is>
-      </c>
-      <c r="Q98" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="R98" s="3" t="inlineStr">
-        <is>
-          <t>08-25 09:00</t>
-        </is>
-      </c>
-      <c r="S98" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="T98" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="U98" s="4" t="n">
-        <v>1.44</v>
       </c>
       <c r="V98" s="3"/>
       <c r="W98" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X98" s="3" t="inlineStr">
         <is>
-          <t>3.10%~3.20%</t>
+          <t>3.92%~4.02%</t>
         </is>
       </c>
       <c r="Y98" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z98" s="3"/>
       <c r="AA98" s="3" t="inlineStr">
         <is>
-          <t>山东省-威海市</t>
+          <t>安徽省</t>
         </is>
       </c>
       <c r="AB98" s="3" t="inlineStr">
         <is>
-          <t>本次中期票据发行规模不超过人民币5亿元,用途为偿还有息债务</t>
+          <t>本期中期票据募集资金5亿元人民币，其中3亿元用于公司本部偿还金融机构借款，其余2亿元用于偿还发行人即将到期的债券[25皖投集SCP001]</t>
         </is>
       </c>
       <c r="AC98" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司,青岛银行股份有限公司,中信银行股份有限公司,华夏银行股份有限公司</t>
+          <t>招商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD98" s="3"/>
@@ -23025,7 +23021,7 @@
       </c>
       <c r="AF98" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG98" s="3" t="inlineStr">
@@ -23035,7 +23031,7 @@
       </c>
       <c r="AH98" s="3" t="inlineStr">
         <is>
-          <t>威高集团有限公司2026年度第三期科技创新债券</t>
+          <t>安徽省投资集团控股有限公司2026年度第四期中期票据</t>
         </is>
       </c>
       <c r="AI98" s="3" t="inlineStr">
@@ -23045,10 +23041,14 @@
       </c>
       <c r="AJ98" s="3" t="inlineStr">
         <is>
-          <t>2031-08-27</t>
-        </is>
-      </c>
-      <c r="AK98" s="3"/>
+          <t>2056-08-27</t>
+        </is>
+      </c>
+      <c r="AK98" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL98" s="3" t="inlineStr">
         <is>
           <t>2026-08-28</t>
@@ -23066,32 +23066,32 @@
       </c>
       <c r="AO98" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP98" s="3" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ98" s="3" t="inlineStr">
         <is>
-          <t>医药制造</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR98" s="3" t="inlineStr">
         <is>
-          <t>医疗器械制造</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS98" s="3" t="inlineStr">
         <is>
-          <t>医疗器械制造</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT98" s="3" t="inlineStr">
         <is>
-          <t>医疗器械</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU98" s="3" t="inlineStr">
@@ -23124,59 +23124,59 @@
     <row r="99" customHeight="true" ht="18.0">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>26皖投集MTN004</t>
+          <t>26核电K4</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>08-26 18:00</t>
+          <t>08-25 19:00</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>102683367.IB</t>
+          <t>245919.SH</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>30Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E99" s="4" t="n">
-        <v>5.0</v>
+        <v>25.0</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>5.0</v>
+        <v>25.0</v>
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2.30 ~ 2.70</t>
+          <t>1.10 ~ 2.10</t>
         </is>
       </c>
       <c r="H99" s="4" t="n">
-        <v>2.49</v>
+        <v>1.51</v>
       </c>
       <c r="I99" s="4" t="n">
-        <v>35.6</v>
+        <v>25.67</v>
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="K99" s="3" t="inlineStr">
         <is>
-          <t>25皖投集MTN004(科创债)</t>
+          <t>26核电K3</t>
         </is>
       </c>
       <c r="L99" s="3" t="inlineStr">
         <is>
-          <t>19.23Y</t>
+          <t>2.89Y</t>
         </is>
       </c>
       <c r="M99" s="3" t="inlineStr">
         <is>
-          <t>2.3597</t>
+          <t>1.5902</t>
         </is>
       </c>
       <c r="N99" s="3" t="inlineStr">
@@ -23186,12 +23186,12 @@
       </c>
       <c r="O99" s="3" t="inlineStr">
         <is>
-          <t>安徽省投资集团控股有限公司</t>
+          <t>中国核能电力股份有限公司</t>
         </is>
       </c>
       <c r="P99" s="3" t="inlineStr">
         <is>
-          <t>C 25.13</t>
+          <t>C 26.25</t>
         </is>
       </c>
       <c r="Q99" s="3" t="inlineStr">
@@ -23201,7 +23201,7 @@
       </c>
       <c r="R99" s="3" t="inlineStr">
         <is>
-          <t>08-25 09:00</t>
+          <t>08-25 15:00</t>
         </is>
       </c>
       <c r="S99" s="3" t="inlineStr">
@@ -23215,7 +23215,7 @@
         </is>
       </c>
       <c r="U99" s="4" t="n">
-        <v>2.9</v>
+        <v>3.36</v>
       </c>
       <c r="V99" s="3"/>
       <c r="W99" s="3" t="inlineStr">
@@ -23225,7 +23225,7 @@
       </c>
       <c r="X99" s="3" t="inlineStr">
         <is>
-          <t>3.92%~4.02%</t>
+          <t>1.56%~1.66%</t>
         </is>
       </c>
       <c r="Y99" s="3" t="inlineStr">
@@ -23233,41 +23233,45 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z99" s="3"/>
+      <c r="Z99" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA99" s="3" t="inlineStr">
         <is>
-          <t>安徽省</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB99" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据募集资金5亿元人民币，其中3亿元用于公司本部偿还金融机构借款，其余2亿元用于偿还发行人即将到期的债券[25皖投集SCP001]</t>
+          <t>本期债券募集资金扣除发行费用后将全部用于生产性支出,包括科技创新领域相关支出、偿还公司债务、补充流动资金等符合法律法规要求的用途。</t>
         </is>
       </c>
       <c r="AC99" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司</t>
+          <t>中信建投证券股份有限公司,华泰联合证券有限责任公司,中国国际金融股份有限公司,国泰海通证券股份有限公司,中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD99" s="3"/>
       <c r="AE99" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF99" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG99" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH99" s="3" t="inlineStr">
         <is>
-          <t>安徽省投资集团控股有限公司2026年度第四期中期票据</t>
+          <t>中国核能电力股份有限公司2026年面向专业投资者公开发行科技创新公司债券(第四期)</t>
         </is>
       </c>
       <c r="AI99" s="3" t="inlineStr">
@@ -23277,17 +23281,13 @@
       </c>
       <c r="AJ99" s="3" t="inlineStr">
         <is>
-          <t>2056-08-27</t>
-        </is>
-      </c>
-      <c r="AK99" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-08-27</t>
+        </is>
+      </c>
+      <c r="AK99" s="3"/>
       <c r="AL99" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AM99" s="3" t="inlineStr">
@@ -23302,32 +23302,32 @@
       </c>
       <c r="AO99" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP99" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AQ99" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR99" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AS99" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>核电</t>
         </is>
       </c>
       <c r="AT99" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU99" s="3" t="inlineStr">
@@ -23352,7 +23352,7 @@
       </c>
       <c r="AY99" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AZ99" s="3"/>
